--- a/기아_트랜스폰더_칩코드_DBnew.xlsx
+++ b/기아_트랜스폰더_칩코드_DBnew.xlsx
@@ -10,7 +10,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기아 트랜스폰더 DB'!$A$1:$O$380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기아 트랜스폰더 DB'!$A$1:$O$379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <color rgb="ff000000"/>
@@ -132,8 +132,18 @@
       <color rgb="ff000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -168,6 +178,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="ffffd599"/>
         <bgColor rgb="ffffeb9c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD599"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,7 +221,7 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -303,6 +318,24 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -564,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O380"/>
+  <dimension ref="A1:O379"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.2"/>
   <cols>
     <col width="14" customWidth="1" style="15" min="1" max="1"/>
@@ -1511,7 +1544,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G17" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7952A)</t>
         </is>
@@ -1533,15 +1566,15 @@
         </is>
       </c>
       <c r="L17" s="19" t="n"/>
-      <c r="M17" s="19" t="n"/>
+      <c r="M17" s="35" t="n"/>
       <c r="N17" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O17" s="23" t="inlineStr">
-        <is>
-          <t>포르테 쿱(XK) 출시(2009.6.11)로 세단과 합류 — 하위트림은 폴딩키(PN 미확인) 사용 추정</t>
+      <c r="O17" s="35" t="inlineStr">
+        <is>
+          <t>스마트키 ID46(PCF7952A) 확인 — 하위트림 폴딩키 품번·칩 미확인</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1609,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7952A)</t>
         </is>
@@ -1598,15 +1631,15 @@
         </is>
       </c>
       <c r="L18" s="19" t="n"/>
-      <c r="M18" s="19" t="n"/>
+      <c r="M18" s="35" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O18" s="23" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2010.8.1 기준 스마트키 부품번호 전환. 하위트림은 폴딩키(PN 미확인) 사용 추정</t>
+      <c r="O18" s="35" t="inlineStr">
+        <is>
+          <t>스마트키 ID46(PCF7952A) 확인 — 하위트림 폴딩키 품번·칩 미확인</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1674,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G19" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7952A)</t>
         </is>
@@ -1663,15 +1696,15 @@
         </is>
       </c>
       <c r="L19" s="19" t="n"/>
-      <c r="M19" s="19" t="n"/>
+      <c r="M19" s="35" t="n"/>
       <c r="N19" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O19" s="23" t="inlineStr">
-        <is>
-          <t>하위트림은 폴딩키(PN 미확인) 사용 추정</t>
+      <c r="O19" s="35" t="inlineStr">
+        <is>
+          <t>스마트키 ID46(PCF7952A) 확인 — 하위트림 폴딩키 품번·칩 미확인</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1739,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>ID8A[스마트키]</t>
         </is>
@@ -1716,9 +1749,9 @@
           <t>81996-A7020[스마트키용], 81996-A7000[폴딩키용]</t>
         </is>
       </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>ILCO HY15[추정], X280[추정], Lishi HYN14R-HY15[추정]</t>
+      <c r="I20" s="36" t="inlineStr">
+        <is>
+          <t>HY15, KK8</t>
         </is>
       </c>
       <c r="J20" s="19" t="n"/>
@@ -1732,15 +1765,15 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M20" s="19" t="n"/>
+      <c r="M20" s="35" t="n"/>
       <c r="N20" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
-        <is>
-          <t>K3(YD) 국내 출시(2012.9). 출시 당시 버튼시동 스마트키는 프레스티지 이상, 디럭스·럭셔리는 폴딩키(이데일리 사양표). 스마트키 칩: 95440-A7000 한국 시장용 정품 8A Texas Crypto 128bit AES(mk3.com), 이전 ID46 기재는 정정. 폴딩키(A7200) 칩은 확인 못함. 국내 현대모비스 원문: 스마트키 A7000[~2016.3.2]→A7600[2016.3.2~2018.2.26], 폴딩키 A7200[~2017.12.15]→A7201[2017.12.15~2018.2.26]</t>
+      <c r="O20" s="34" t="inlineStr">
+        <is>
+          <t>스마트키는 ID8A 확인 — 폴딩키(95430-A7200) 칩은 판매처마다 4D60·ID46로 다름</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1808,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>ID8A[스마트키]</t>
         </is>
@@ -1785,9 +1818,9 @@
           <t>81996-A7020[스마트키용], 81996-A7000[폴딩키용]</t>
         </is>
       </c>
-      <c r="I21" s="26" t="inlineStr">
-        <is>
-          <t>ILCO HY15[추정], X280[추정], Lishi HYN14R-HY15[추정]</t>
+      <c r="I21" s="36" t="inlineStr">
+        <is>
+          <t>HY15, KK8</t>
         </is>
       </c>
       <c r="J21" s="19" t="n"/>
@@ -1801,13 +1834,17 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M21" s="19" t="n"/>
+      <c r="M21" s="35" t="n"/>
       <c r="N21" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O21" s="19" t="n"/>
+      <c r="O21" s="35" t="inlineStr">
+        <is>
+          <t>스마트키는 ID8A 확인 — 폴딩키(95430-A7200) 칩은 판매처마다 4D60·ID46로 다름</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="15">
       <c r="A22" s="24" t="inlineStr">
@@ -1840,7 +1877,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G22" s="34" t="inlineStr">
         <is>
           <t>ID8A[스마트키]</t>
         </is>
@@ -1850,9 +1887,9 @@
           <t>81996-A7020[스마트키용], 81996-A7000[폴딩키용]</t>
         </is>
       </c>
-      <c r="I22" s="26" t="inlineStr">
-        <is>
-          <t>ILCO HY15[추정], X280[추정], Lishi HYN14R-HY15[추정]</t>
+      <c r="I22" s="36" t="inlineStr">
+        <is>
+          <t>HY15, KK8</t>
         </is>
       </c>
       <c r="J22" s="19" t="n"/>
@@ -1866,13 +1903,17 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M22" s="19" t="n"/>
+      <c r="M22" s="35" t="n"/>
       <c r="N22" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O22" s="19" t="n"/>
+      <c r="O22" s="35" t="inlineStr">
+        <is>
+          <t>스마트키는 ID8A 확인 — 폴딩키(95430-A7200) 칩은 판매처마다 4D60·ID46로 다름</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="15">
       <c r="A23" s="24" t="inlineStr">
@@ -1905,7 +1946,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>ID8A[스마트키]</t>
         </is>
@@ -1915,9 +1956,9 @@
           <t>81996-A7020[스마트키용], 81996-A7000[폴딩키용]</t>
         </is>
       </c>
-      <c r="I23" s="26" t="inlineStr">
-        <is>
-          <t>ILCO HY15[추정], X280[추정], Lishi HYN14R-HY15[추정]</t>
+      <c r="I23" s="36" t="inlineStr">
+        <is>
+          <t>HY15, KK8</t>
         </is>
       </c>
       <c r="J23" s="19" t="n"/>
@@ -1931,15 +1972,15 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M23" s="19" t="n"/>
+      <c r="M23" s="35" t="n"/>
       <c r="N23" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O23" s="19" t="inlineStr">
-        <is>
-          <t>더 뉴 K3(YD 페이스리프트) 출시(2015.11)로 전환되는 해</t>
+      <c r="O23" s="35" t="inlineStr">
+        <is>
+          <t>스마트키는 ID8A 확인 — 폴딩키(95430-A7200) 칩은 판매처마다 4D60·ID46로 다름</t>
         </is>
       </c>
     </row>
@@ -1974,7 +2015,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="G24" s="37" t="inlineStr">
         <is>
           <t>ID8A[스마트키]</t>
         </is>
@@ -1984,9 +2025,9 @@
           <t>81996-A7020[스마트키용], 81996-A7000[폴딩키용]</t>
         </is>
       </c>
-      <c r="I24" s="26" t="inlineStr">
-        <is>
-          <t>ILCO KK12[추정], Lishi K5[추정]</t>
+      <c r="I24" s="36" t="inlineStr">
+        <is>
+          <t>HY15, KK8</t>
         </is>
       </c>
       <c r="J24" s="19" t="n"/>
@@ -2000,17 +2041,13 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M24" s="19" t="n"/>
+      <c r="M24" s="38" t="n"/>
       <c r="N24" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O24" s="24" t="inlineStr">
-        <is>
-          <t>A7600 칩은 Lonsdor 8A 스마트키 PCB 지원 차종(K3 2016-2018)으로 확인</t>
-        </is>
-      </c>
+      <c r="O24" s="37" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="15">
       <c r="A25" s="24" t="inlineStr">
@@ -2043,7 +2080,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G25" s="24" t="inlineStr">
+      <c r="G25" s="37" t="inlineStr">
         <is>
           <t>ID8A[스마트키]</t>
         </is>
@@ -2053,9 +2090,9 @@
           <t>81996-A7020[스마트키용], 81996-A7000[폴딩키용]</t>
         </is>
       </c>
-      <c r="I25" s="26" t="inlineStr">
-        <is>
-          <t>ILCO KK12[추정], Lishi K5[추정]</t>
+      <c r="I25" s="36" t="inlineStr">
+        <is>
+          <t>HY15, KK8</t>
         </is>
       </c>
       <c r="J25" s="19" t="n"/>
@@ -2069,17 +2106,13 @@
           <t>95430-A7200[~12.15], 95430-A7201[12.15~]</t>
         </is>
       </c>
-      <c r="M25" s="19" t="n"/>
+      <c r="M25" s="38" t="n"/>
       <c r="N25" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O25" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 원문 확인</t>
-        </is>
-      </c>
+      <c r="O25" s="38" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="15">
       <c r="A26" s="24" t="inlineStr">
@@ -2319,7 +2352,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G29" s="24" t="inlineStr">
+      <c r="G29" s="37" t="inlineStr">
         <is>
           <t>ID8A[~4.26], ID4A[더 뉴 K3, 4.5~]</t>
         </is>
@@ -2345,17 +2378,13 @@
           <t>95430-M6000[~4.21], 95430-M6400[4.5~]</t>
         </is>
       </c>
-      <c r="M29" s="19" t="n"/>
+      <c r="M29" s="38" t="n"/>
       <c r="N29" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O29" s="27" t="inlineStr">
-        <is>
-          <t>더 뉴 K3(BD PE) 출시(2021.4). 95440-M6800은 한국 시장용 정품 HITAG AES ID4A(NCF29A1M)로 다수 판매처(mk3·abkeys·americankeysupply) 일치 확인 → 기존 'ID8A/ID47 미확정' 해소(PE 이전은 ID8A, PE 이후는 ID4A)</t>
-        </is>
-      </c>
+      <c r="O29" s="38" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="15">
       <c r="A30" s="24" t="inlineStr">
@@ -7948,7 +7977,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G122" s="24" t="inlineStr">
+      <c r="G122" s="37" t="inlineStr">
         <is>
           <t>ID8A</t>
         </is>
@@ -7966,17 +7995,13 @@
         </is>
       </c>
       <c r="L122" s="19" t="n"/>
-      <c r="M122" s="19" t="n"/>
+      <c r="M122" s="38" t="n"/>
       <c r="N122" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O122" s="23" t="inlineStr">
-        <is>
-          <t>스토닉 국내 출시(2017.6.21) — 프라이드(UB)와 같은 플랫폼 공유 크로스오버. 국제 판매처(gskeyae.com) 확인: '2017-2018 KIA Stonic ... 8A Texas Crypto 128-bits AES' — 이전에 'ID47 추정'이라고 했던 건 정정함</t>
-        </is>
-      </c>
+      <c r="O122" s="38" t="n"/>
     </row>
     <row r="123" ht="15" customHeight="1" s="15">
       <c r="A123" s="19" t="inlineStr">
@@ -8542,7 +8567,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G132" s="24" t="inlineStr">
+      <c r="G132" s="34" t="inlineStr">
         <is>
           <t>ID8A, ID6A</t>
         </is>
@@ -8564,15 +8589,15 @@
           <t>95430-Q5000</t>
         </is>
       </c>
-      <c r="M132" s="19" t="n"/>
+      <c r="M132" s="35" t="n"/>
       <c r="N132" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O132" s="23" t="inlineStr">
-        <is>
-          <t>셀토스 국내 출시(2019.7). 국내 현대모비스(hellowcar) 원문: 스마트키 Q5000·Q5010[~2022.7.20, 블레이드 81999J7020] → Q5500·Q5510[2022.7.19~, 81996P1060]. 폴딩키 Q5000·Q5010·Q5700·Q5750(블레이드 81996K0000)은 부품 확인, 연식 구분은 스마트키 전환 시점 기준 추정. 칩: 국제 판매처 다수 확인 Texas AES(8A/6A)</t>
+      <c r="O132" s="35" t="inlineStr">
+        <is>
+          <t>칩(8A/6A) 확인 — 폴딩키 연식 구분은 스마트키 전환 시점 기준 추정</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9405,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G146" s="24" t="inlineStr">
+      <c r="G146" s="37" t="inlineStr">
         <is>
           <t>ID8A</t>
         </is>
@@ -9398,17 +9423,13 @@
           <t>95430-2K301, 95430-B2100</t>
         </is>
       </c>
-      <c r="M146" s="19" t="n"/>
+      <c r="M146" s="38" t="n"/>
       <c r="N146" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O146" s="23" t="inlineStr">
-        <is>
-          <t>칩: 95440-B2000·B2AA0 한국 시장용 정품 8A Texas Crypto 128bit AES, 4버튼(mk3·abkeys·remotesandkeys) — 이전 'ID47 추정'은 정정</t>
-        </is>
-      </c>
+      <c r="O146" s="38" t="n"/>
     </row>
     <row r="147" ht="15" customHeight="1" s="15">
       <c r="A147" s="19" t="inlineStr">
@@ -10881,7 +10902,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G171" s="24" t="inlineStr">
+      <c r="G171" s="37" t="inlineStr">
         <is>
           <t>ID6A[전기차], ID46[가솔린]</t>
         </is>
@@ -10903,17 +10924,13 @@
           <t>95430-A3600, 95430-A3610[6.16~]</t>
         </is>
       </c>
-      <c r="M171" s="19" t="n"/>
+      <c r="M171" s="38" t="n"/>
       <c r="N171" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O171" s="23" t="inlineStr">
-        <is>
-          <t>레이EV 출시(2023) — 가솔린과 전기차 부품 계열 분리 추정</t>
-        </is>
-      </c>
+      <c r="O171" s="38" t="n"/>
     </row>
     <row r="172" ht="15" customHeight="1" s="15">
       <c r="A172" s="19" t="inlineStr">
@@ -12598,7 +12615,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G200" s="26" t="inlineStr">
+      <c r="G200" s="34" t="inlineStr">
         <is>
           <t>ID4A[추정]</t>
         </is>
@@ -12612,15 +12629,15 @@
         </is>
       </c>
       <c r="L200" s="19" t="n"/>
-      <c r="M200" s="19" t="n"/>
+      <c r="M200" s="35" t="n"/>
       <c r="N200" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O200" s="26" t="inlineStr">
-        <is>
-          <t>EV4 국내 출시(2025.3). 스마트키: 정품 95440-EZ000(5버튼, 2025) · 95440-EZ700(4버튼, 2026)(mk3, 시장 표기 없음). 칩은 판매처에 명시 없음 — 같은 시기 같은 계열(K4 95440-GG000)이 HITAG-AES 4A라 ID4A로 추정 유지</t>
+      <c r="O200" s="34" t="inlineStr">
+        <is>
+          <t>95440-EZ000 칩 표기 원문 없음 — 같은 시기 K4(95440-GG000) HITAG AES 4A 기준 추정</t>
         </is>
       </c>
     </row>
@@ -12655,7 +12672,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G201" s="26" t="inlineStr">
+      <c r="G201" s="34" t="inlineStr">
         <is>
           <t>ID4A[추정]</t>
         </is>
@@ -12669,15 +12686,15 @@
         </is>
       </c>
       <c r="L201" s="19" t="n"/>
-      <c r="M201" s="19" t="n"/>
+      <c r="M201" s="35" t="n"/>
       <c r="N201" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O201" s="24" t="inlineStr">
-        <is>
-          <t>'더 EV4' 연식변경(2026.2)</t>
+      <c r="O201" s="34" t="inlineStr">
+        <is>
+          <t>95440-EZ000 칩 표기 원문 없음 — 같은 시기 K4(95440-GG000) HITAG AES 4A 기준 추정</t>
         </is>
       </c>
     </row>
@@ -14444,7 +14461,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G234" s="24" t="inlineStr">
+      <c r="G234" s="37" t="inlineStr">
         <is>
           <t>ID47(NCF2971X)</t>
         </is>
@@ -14466,17 +14483,13 @@
           <t>95430-D9000, 95430-D9100</t>
         </is>
       </c>
-      <c r="M234" s="19" t="n"/>
+      <c r="M234" s="38" t="n"/>
       <c r="N234" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O234" s="23" t="inlineStr">
-        <is>
-          <t>국제 판매처(go-parts.com, americankeysupply) 확인: Hitag3 ID47 - 이전에 ID6E-MA(DST80) 추정이라고 했던 건 정정함</t>
-        </is>
-      </c>
+      <c r="O234" s="38" t="n"/>
     </row>
     <row r="235" ht="15" customHeight="1" s="15">
       <c r="A235" s="19" t="inlineStr">
@@ -16246,7 +16259,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G264" s="24" t="inlineStr">
+      <c r="G264" s="37" t="inlineStr">
         <is>
           <t>ID4A(NCF29AxM)</t>
         </is>
@@ -16268,17 +16281,13 @@
         </is>
       </c>
       <c r="L264" s="19" t="n"/>
-      <c r="M264" s="19" t="n"/>
+      <c r="M264" s="38" t="n"/>
       <c r="N264" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O264" s="23" t="inlineStr">
-        <is>
-          <t>칩: 95440-P2000(5버튼)·P2200(7버튼)·P2AD0(7버튼) 모두 정품 HITAG AES ID4A(mk3·abkeys·royalkeysupply) — 이전 '추정' 해소</t>
-        </is>
-      </c>
+      <c r="O264" s="38" t="n"/>
     </row>
     <row r="265" ht="15" customHeight="1" s="15">
       <c r="A265" s="19" t="inlineStr">
@@ -18007,7 +18016,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G293" s="24" t="inlineStr">
+      <c r="G293" s="37" t="inlineStr">
         <is>
           <t>ID47(NCF2971X)</t>
         </is>
@@ -18029,17 +18038,13 @@
           <t>95430-G5000, 95430-G5200</t>
         </is>
       </c>
-      <c r="M293" s="19" t="n"/>
+      <c r="M293" s="38" t="n"/>
       <c r="N293" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O293" s="23" t="inlineStr">
-        <is>
-          <t>이전 '적용 시점 추정' 해소: G5025는 원문상 22년형</t>
-        </is>
-      </c>
+      <c r="O293" s="38" t="n"/>
     </row>
     <row r="294" ht="15" customHeight="1" s="15">
       <c r="A294" s="19" t="inlineStr">
@@ -18716,7 +18721,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G306" s="24" t="inlineStr">
+      <c r="G306" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18730,11 +18735,11 @@
           <t>954301D100[UN]</t>
         </is>
       </c>
-      <c r="M306" s="19" t="n"/>
+      <c r="M306" s="35" t="n"/>
       <c r="N306" s="19" t="n"/>
-      <c r="O306" s="23" t="inlineStr">
-        <is>
-          <t>뉴 카렌스(UN) 2006년 출시 — 954301D100은 954301D101(2007.7.2~) 이전 부품으로 추정</t>
+      <c r="O306" s="35" t="inlineStr">
+        <is>
+          <t>954301D100 적용 시점은 954301D101(2007.7.2~) 이전 부품으로 추정</t>
         </is>
       </c>
     </row>
@@ -19042,7 +19047,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G312" s="24" t="inlineStr">
+      <c r="G312" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -19060,11 +19065,11 @@
           <t>954301D103[~7.17], 954301D104[7.1~7.17]</t>
         </is>
       </c>
-      <c r="M312" s="19" t="n"/>
+      <c r="M312" s="35" t="n"/>
       <c r="N312" s="19" t="n"/>
-      <c r="O312" s="26" t="inlineStr">
-        <is>
-          <t>954301D104는 부품 존재만 확인, 적용 시점은 D103 종료일 기준 추정</t>
+      <c r="O312" s="34" t="inlineStr">
+        <is>
+          <t>954301D104 적용 시점은 D103 종료일 기준 추정</t>
         </is>
       </c>
     </row>
@@ -22363,22 +22368,22 @@
       </c>
       <c r="B368" s="19" t="inlineStr">
         <is>
-          <t>봉고3 EV (전기차)</t>
+          <t>봉고3 (Bongo3, J)</t>
         </is>
       </c>
       <c r="C368" s="24" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D368" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E368" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D368" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E368" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F368" s="22" t="inlineStr">
@@ -22386,33 +22391,37 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G368" s="24" t="inlineStr">
-        <is>
-          <t>ID6A</t>
-        </is>
-      </c>
-      <c r="H368" s="24" t="inlineStr">
-        <is>
-          <t>81996-CP000</t>
+      <c r="G368" s="28" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
+        </is>
+      </c>
+      <c r="H368" s="19" t="inlineStr">
+        <is>
+          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964F700[C타입 폴딩키용]</t>
         </is>
       </c>
       <c r="I368" s="19" t="n"/>
       <c r="J368" s="19" t="n"/>
-      <c r="K368" s="24" t="inlineStr">
-        <is>
-          <t>95440-CP000[2버튼]</t>
-        </is>
-      </c>
-      <c r="L368" s="19" t="n"/>
-      <c r="M368" s="19" t="n"/>
+      <c r="K368" s="19" t="n"/>
+      <c r="L368" s="24" t="inlineStr">
+        <is>
+          <t>954304E500[C타입 폴딩]</t>
+        </is>
+      </c>
+      <c r="M368" s="28" t="inlineStr">
+        <is>
+          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
+        </is>
+      </c>
       <c r="N368" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O368" s="23" t="inlineStr">
-        <is>
-          <t>봉고3 EV 출시(2020.1, 2020년형). 칩: 95440-CP000 정품 ATMEL AES/6A(auto-keys.eu), 95440-CP500 한국 시장용 정품 AES 6A(vvdi) — 둘 다 2버튼. 이전 'ID4A 추정'은 정정</t>
+      <c r="O368" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
@@ -22424,7 +22433,7 @@
       </c>
       <c r="B369" s="19" t="inlineStr">
         <is>
-          <t>봉고3 (Bongo3, J)</t>
+          <t>봉고3 EV (전기차)</t>
         </is>
       </c>
       <c r="C369" s="24" t="inlineStr">
@@ -22432,14 +22441,14 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D369" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E369" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D369" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E369" s="21" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F369" s="22" t="inlineStr">
@@ -22447,39 +22456,31 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G369" s="28" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
-        </is>
-      </c>
-      <c r="H369" s="19" t="inlineStr">
-        <is>
-          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964F700[C타입 폴딩키용]</t>
+      <c r="G369" s="24" t="inlineStr">
+        <is>
+          <t>ID6A</t>
+        </is>
+      </c>
+      <c r="H369" s="24" t="inlineStr">
+        <is>
+          <t>81996-CP000</t>
         </is>
       </c>
       <c r="I369" s="19" t="n"/>
       <c r="J369" s="19" t="n"/>
-      <c r="K369" s="19" t="n"/>
-      <c r="L369" s="24" t="inlineStr">
-        <is>
-          <t>954304E500[C타입 폴딩]</t>
-        </is>
-      </c>
-      <c r="M369" s="28" t="inlineStr">
-        <is>
-          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
-        </is>
-      </c>
+      <c r="K369" s="24" t="inlineStr">
+        <is>
+          <t>95440-CP000[2버튼]</t>
+        </is>
+      </c>
+      <c r="L369" s="19" t="n"/>
+      <c r="M369" s="19" t="n"/>
       <c r="N369" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O369" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
-        </is>
-      </c>
+      <c r="O369" s="19" t="n"/>
     </row>
     <row r="370" ht="15" customHeight="1" s="15">
       <c r="A370" s="19" t="inlineStr">
@@ -22489,22 +22490,22 @@
       </c>
       <c r="B370" s="19" t="inlineStr">
         <is>
-          <t>봉고3 EV (전기차)</t>
+          <t>봉고3 (Bongo3, J)</t>
         </is>
       </c>
       <c r="C370" s="24" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D370" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E370" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D370" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E370" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F370" s="22" t="inlineStr">
@@ -22512,31 +22513,39 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G370" s="24" t="inlineStr">
-        <is>
-          <t>ID6A</t>
-        </is>
-      </c>
-      <c r="H370" s="24" t="inlineStr">
-        <is>
-          <t>81996-CP000</t>
+      <c r="G370" s="28" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
+        </is>
+      </c>
+      <c r="H370" s="19" t="inlineStr">
+        <is>
+          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964F700[C타입 폴딩키용]</t>
         </is>
       </c>
       <c r="I370" s="19" t="n"/>
       <c r="J370" s="19" t="n"/>
-      <c r="K370" s="24" t="inlineStr">
-        <is>
-          <t>95440-CP000[2버튼]</t>
-        </is>
-      </c>
-      <c r="L370" s="19" t="n"/>
-      <c r="M370" s="19" t="n"/>
+      <c r="K370" s="19" t="n"/>
+      <c r="L370" s="24" t="inlineStr">
+        <is>
+          <t>954304E500[C타입 폴딩, ~12.2]</t>
+        </is>
+      </c>
+      <c r="M370" s="28" t="inlineStr">
+        <is>
+          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
+        </is>
+      </c>
       <c r="N370" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O370" s="19" t="n"/>
+      <c r="O370" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="15" customHeight="1" s="15">
       <c r="A371" s="19" t="inlineStr">
@@ -22546,7 +22555,7 @@
       </c>
       <c r="B371" s="19" t="inlineStr">
         <is>
-          <t>봉고3 (Bongo3, J)</t>
+          <t>봉고3 EV (전기차)</t>
         </is>
       </c>
       <c r="C371" s="24" t="inlineStr">
@@ -22554,14 +22563,14 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D371" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E371" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D371" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E371" s="21" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F371" s="22" t="inlineStr">
@@ -22569,37 +22578,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G371" s="28" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
-        </is>
-      </c>
-      <c r="H371" s="19" t="inlineStr">
-        <is>
-          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964F700[C타입 폴딩키용]</t>
+      <c r="G371" s="24" t="inlineStr">
+        <is>
+          <t>ID6A</t>
+        </is>
+      </c>
+      <c r="H371" s="24" t="inlineStr">
+        <is>
+          <t>81996-CP000</t>
         </is>
       </c>
       <c r="I371" s="19" t="n"/>
       <c r="J371" s="19" t="n"/>
-      <c r="K371" s="19" t="n"/>
-      <c r="L371" s="24" t="inlineStr">
-        <is>
-          <t>954304E500[C타입 폴딩, ~12.2]</t>
-        </is>
-      </c>
-      <c r="M371" s="28" t="inlineStr">
-        <is>
-          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
-        </is>
-      </c>
+      <c r="K371" s="24" t="inlineStr">
+        <is>
+          <t>95440-CP000[2버튼, ~7.5], 95440-CP500[2버튼, 7.5~]</t>
+        </is>
+      </c>
+      <c r="L371" s="19" t="n"/>
+      <c r="M371" s="19" t="n"/>
       <c r="N371" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O371" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O371" s="19" t="inlineStr">
+        <is>
+          <t>국내 현대모비스 원문: CP000[~2021.7.5, 블레이드 81996CP000] → CP500[2021.7.5~] → CP600[2023.5.18~, 블레이드 81996CP100]</t>
         </is>
       </c>
     </row>
@@ -22611,22 +22616,22 @@
       </c>
       <c r="B372" s="19" t="inlineStr">
         <is>
-          <t>봉고3 EV (전기차)</t>
+          <t>봉고3 (Bongo3, J)</t>
         </is>
       </c>
       <c r="C372" s="24" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D372" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E372" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D372" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E372" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F372" s="22" t="inlineStr">
@@ -22634,33 +22639,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G372" s="24" t="inlineStr">
-        <is>
-          <t>ID6A</t>
-        </is>
-      </c>
-      <c r="H372" s="24" t="inlineStr">
-        <is>
-          <t>81996-CP000</t>
+      <c r="G372" s="28" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
+        </is>
+      </c>
+      <c r="H372" s="19" t="inlineStr">
+        <is>
+          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964F700[C타입 폴딩키용, ~2021.12.2]</t>
         </is>
       </c>
       <c r="I372" s="19" t="n"/>
       <c r="J372" s="19" t="n"/>
-      <c r="K372" s="24" t="inlineStr">
-        <is>
-          <t>95440-CP000[2버튼, ~7.5], 95440-CP500[2버튼, 7.5~]</t>
-        </is>
-      </c>
+      <c r="K372" s="19" t="n"/>
       <c r="L372" s="19" t="n"/>
-      <c r="M372" s="19" t="n"/>
+      <c r="M372" s="28" t="inlineStr">
+        <is>
+          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
+        </is>
+      </c>
       <c r="N372" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O372" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 원문: CP000[~2021.7.5, 블레이드 81996CP000] → CP500[2021.7.5~] → CP600[2023.5.18~, 블레이드 81996CP100]</t>
+      <c r="O372" s="24" t="inlineStr">
+        <is>
+          <t>2021.12.2~2023.12 구간 폴딩키 PN은 국내 원문에서 확인하지 못해 공란</t>
         </is>
       </c>
     </row>
@@ -22672,7 +22677,7 @@
       </c>
       <c r="B373" s="19" t="inlineStr">
         <is>
-          <t>봉고3 (Bongo3, J)</t>
+          <t>봉고3 EV (전기차)</t>
         </is>
       </c>
       <c r="C373" s="24" t="inlineStr">
@@ -22680,14 +22685,14 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D373" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E373" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D373" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E373" s="21" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F373" s="22" t="inlineStr">
@@ -22695,33 +22700,33 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G373" s="28" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
-        </is>
-      </c>
-      <c r="H373" s="19" t="inlineStr">
-        <is>
-          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964F700[C타입 폴딩키용, ~2021.12.2]</t>
+      <c r="G373" s="24" t="inlineStr">
+        <is>
+          <t>ID6A</t>
+        </is>
+      </c>
+      <c r="H373" s="24" t="inlineStr">
+        <is>
+          <t>81996-CP000</t>
         </is>
       </c>
       <c r="I373" s="19" t="n"/>
       <c r="J373" s="19" t="n"/>
-      <c r="K373" s="19" t="n"/>
+      <c r="K373" s="24" t="inlineStr">
+        <is>
+          <t>95440-CP500[2버튼]</t>
+        </is>
+      </c>
       <c r="L373" s="19" t="n"/>
-      <c r="M373" s="28" t="inlineStr">
-        <is>
-          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
-        </is>
-      </c>
+      <c r="M373" s="19" t="n"/>
       <c r="N373" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O373" s="24" t="inlineStr">
-        <is>
-          <t>2021.12.2~2023.12 구간 폴딩키 PN은 국내 원문에서 확인하지 못해 공란</t>
+      <c r="O373" s="19" t="inlineStr">
+        <is>
+          <t>이전에 2022년에 CP600을 함께 적었으나 원문상 CP600은 2023.5.18부터라 정정</t>
         </is>
       </c>
     </row>
@@ -22733,22 +22738,22 @@
       </c>
       <c r="B374" s="19" t="inlineStr">
         <is>
-          <t>봉고3 EV (전기차)</t>
+          <t>봉고3 (Bongo3, J)</t>
         </is>
       </c>
       <c r="C374" s="24" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D374" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E374" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D374" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E374" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F374" s="22" t="inlineStr">
@@ -22756,33 +22761,37 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G374" s="24" t="inlineStr">
-        <is>
-          <t>ID6A</t>
-        </is>
-      </c>
-      <c r="H374" s="24" t="inlineStr">
-        <is>
-          <t>81996-CP000</t>
+      <c r="G374" s="28" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
+        </is>
+      </c>
+      <c r="H374" s="19" t="inlineStr">
+        <is>
+          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964F700[C타입 폴딩키용], 819964E950[폴딩키용, 12월~]</t>
         </is>
       </c>
       <c r="I374" s="19" t="n"/>
       <c r="J374" s="19" t="n"/>
-      <c r="K374" s="24" t="inlineStr">
-        <is>
-          <t>95440-CP500[2버튼]</t>
-        </is>
-      </c>
-      <c r="L374" s="19" t="n"/>
-      <c r="M374" s="19" t="n"/>
+      <c r="K374" s="19" t="n"/>
+      <c r="L374" s="24" t="inlineStr">
+        <is>
+          <t>954304E700[2023.12~]</t>
+        </is>
+      </c>
+      <c r="M374" s="28" t="inlineStr">
+        <is>
+          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
+        </is>
+      </c>
       <c r="N374" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O374" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2022년에 CP600을 함께 적었으나 원문상 CP600은 2023.5.18부터라 정정</t>
+      <c r="O374" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
@@ -22794,7 +22803,7 @@
       </c>
       <c r="B375" s="19" t="inlineStr">
         <is>
-          <t>봉고3 (Bongo3, J)</t>
+          <t>봉고3 EV (전기차)</t>
         </is>
       </c>
       <c r="C375" s="24" t="inlineStr">
@@ -22802,14 +22811,14 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D375" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E375" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D375" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E375" s="21" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F375" s="22" t="inlineStr">
@@ -22817,39 +22826,31 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G375" s="28" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
-        </is>
-      </c>
-      <c r="H375" s="19" t="inlineStr">
-        <is>
-          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964F700[C타입 폴딩키용], 819964E950[폴딩키용, 12월~]</t>
+      <c r="G375" s="24" t="inlineStr">
+        <is>
+          <t>ID6A</t>
+        </is>
+      </c>
+      <c r="H375" s="24" t="inlineStr">
+        <is>
+          <t>81996-CP000[CP500용], 81996-CP100[CP600용]</t>
         </is>
       </c>
       <c r="I375" s="19" t="n"/>
       <c r="J375" s="19" t="n"/>
-      <c r="K375" s="19" t="n"/>
-      <c r="L375" s="24" t="inlineStr">
-        <is>
-          <t>954304E700[2023.12~]</t>
-        </is>
-      </c>
-      <c r="M375" s="28" t="inlineStr">
-        <is>
-          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
-        </is>
-      </c>
+      <c r="K375" s="24" t="inlineStr">
+        <is>
+          <t>95440-CP500[2버튼], 95440-CP600[5.18~]</t>
+        </is>
+      </c>
+      <c r="L375" s="19" t="n"/>
+      <c r="M375" s="19" t="n"/>
       <c r="N375" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O375" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
-        </is>
-      </c>
+      <c r="O375" s="19" t="n"/>
     </row>
     <row r="376" ht="15" customHeight="1" s="15">
       <c r="A376" s="19" t="inlineStr">
@@ -22859,22 +22860,22 @@
       </c>
       <c r="B376" s="19" t="inlineStr">
         <is>
-          <t>봉고3 EV (전기차)</t>
+          <t>봉고3 (Bongo3, J)</t>
         </is>
       </c>
       <c r="C376" s="24" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D376" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E376" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D376" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E376" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F376" s="22" t="inlineStr">
@@ -22882,31 +22883,43 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G376" s="24" t="inlineStr">
-        <is>
-          <t>ID6A</t>
-        </is>
-      </c>
-      <c r="H376" s="24" t="inlineStr">
-        <is>
-          <t>81996-CP000[CP500용], 81996-CP100[CP600용]</t>
+      <c r="G376" s="28" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
+        </is>
+      </c>
+      <c r="H376" s="19" t="inlineStr">
+        <is>
+          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964E950[폴딩키용, 2023.12~], 81996-CP100[스마트키용]</t>
         </is>
       </c>
       <c r="I376" s="19" t="n"/>
       <c r="J376" s="19" t="n"/>
       <c r="K376" s="24" t="inlineStr">
         <is>
-          <t>95440-CP500[2버튼], 95440-CP600[5.18~]</t>
-        </is>
-      </c>
-      <c r="L376" s="19" t="n"/>
-      <c r="M376" s="19" t="n"/>
+          <t>95440-4EGA0</t>
+        </is>
+      </c>
+      <c r="L376" s="24" t="inlineStr">
+        <is>
+          <t>954304E700</t>
+        </is>
+      </c>
+      <c r="M376" s="28" t="inlineStr">
+        <is>
+          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
+        </is>
+      </c>
       <c r="N376" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O376" s="19" t="n"/>
+      <c r="O376" s="19" t="inlineStr">
+        <is>
+          <t>국내 현대모비스(hellowcar): 내연 봉고3 스마트키 954404EGA0·블레이드 81996CP100 리스팅 확인. 버튼시동 스마트키는 LPG 터보 10.25인치 내비 패키지 옵션으로 확인(카눈 가격표)</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="15" customHeight="1" s="15">
       <c r="A377" s="19" t="inlineStr">
@@ -22916,7 +22929,7 @@
       </c>
       <c r="B377" s="19" t="inlineStr">
         <is>
-          <t>봉고3 (Bongo3, J)</t>
+          <t>봉고3 EV (전기차)</t>
         </is>
       </c>
       <c r="C377" s="24" t="inlineStr">
@@ -22924,14 +22937,14 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D377" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E377" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D377" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E377" s="21" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F377" s="22" t="inlineStr">
@@ -22939,43 +22952,31 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G377" s="28" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
-        </is>
-      </c>
-      <c r="H377" s="19" t="inlineStr">
-        <is>
-          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964E950[폴딩키용, 2023.12~], 81996-CP100[스마트키용]</t>
+      <c r="G377" s="24" t="inlineStr">
+        <is>
+          <t>ID6A</t>
+        </is>
+      </c>
+      <c r="H377" s="24" t="inlineStr">
+        <is>
+          <t>81996-CP000[CP500용], 81996-CP100[CP600용]</t>
         </is>
       </c>
       <c r="I377" s="19" t="n"/>
       <c r="J377" s="19" t="n"/>
       <c r="K377" s="24" t="inlineStr">
         <is>
-          <t>95440-4EGA0</t>
-        </is>
-      </c>
-      <c r="L377" s="24" t="inlineStr">
-        <is>
-          <t>954304E700</t>
-        </is>
-      </c>
-      <c r="M377" s="28" t="inlineStr">
-        <is>
-          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
-        </is>
-      </c>
+          <t>95440-CP500[2버튼], 95440-CP600</t>
+        </is>
+      </c>
+      <c r="L377" s="19" t="n"/>
+      <c r="M377" s="19" t="n"/>
       <c r="N377" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O377" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar): 내연 봉고3 스마트키 954404EGA0·블레이드 81996CP100 리스팅 확인. 버튼시동 스마트키는 LPG 터보 10.25인치 내비 패키지 옵션으로 확인(카눈 가격표)</t>
-        </is>
-      </c>
+      <c r="O377" s="19" t="n"/>
     </row>
     <row r="378" ht="15" customHeight="1" s="15">
       <c r="A378" s="19" t="inlineStr">
@@ -22985,22 +22986,22 @@
       </c>
       <c r="B378" s="19" t="inlineStr">
         <is>
-          <t>봉고3 EV (전기차)</t>
+          <t>봉고3 (Bongo3, J)</t>
         </is>
       </c>
       <c r="C378" s="24" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D378" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E378" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D378" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E378" s="22" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F378" s="22" t="inlineStr">
@@ -23008,31 +23009,43 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G378" s="24" t="inlineStr">
-        <is>
-          <t>ID6A</t>
-        </is>
-      </c>
-      <c r="H378" s="24" t="inlineStr">
-        <is>
-          <t>81996-CP000[CP500용], 81996-CP100[CP600용]</t>
+      <c r="G378" s="34" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
+        </is>
+      </c>
+      <c r="H378" s="19" t="inlineStr">
+        <is>
+          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964E950[폴딩키용, 2023.12~], 81996-CP100[스마트키용]</t>
         </is>
       </c>
       <c r="I378" s="19" t="n"/>
       <c r="J378" s="19" t="n"/>
       <c r="K378" s="24" t="inlineStr">
         <is>
-          <t>95440-CP500[2버튼], 95440-CP600</t>
-        </is>
-      </c>
-      <c r="L378" s="19" t="n"/>
-      <c r="M378" s="19" t="n"/>
+          <t>95440-4EGA0</t>
+        </is>
+      </c>
+      <c r="L378" s="24" t="inlineStr">
+        <is>
+          <t>954304E700</t>
+        </is>
+      </c>
+      <c r="M378" s="34" t="inlineStr">
+        <is>
+          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
+        </is>
+      </c>
       <c r="N378" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O378" s="19" t="n"/>
+      <c r="O378" s="35" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(819964E010)·46(819964E020) 키 구분 연식 매칭 원문 없음(2025년형 LPG 터보 판매 확인)</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="15" customHeight="1" s="15">
       <c r="A379" s="19" t="inlineStr">
@@ -23042,7 +23055,7 @@
       </c>
       <c r="B379" s="19" t="inlineStr">
         <is>
-          <t>봉고3 (Bongo3, J)</t>
+          <t>봉고3 EV (전기차)</t>
         </is>
       </c>
       <c r="C379" s="24" t="inlineStr">
@@ -23050,14 +23063,14 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D379" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E379" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="D379" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E379" s="21" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F379" s="22" t="inlineStr">
@@ -23065,103 +23078,35 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G379" s="28" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
-        </is>
-      </c>
-      <c r="H379" s="19" t="inlineStr">
-        <is>
-          <t>819964E010[이모빌라이저키, ID60], 819964E020[이모빌라이저키, ID46], 819964E800[이모빌라이저키], 819964E960[이모빌라이저키], 819964E950[폴딩키용, 2023.12~], 81996-CP100[스마트키용]</t>
+      <c r="G379" s="24" t="inlineStr">
+        <is>
+          <t>ID6A</t>
+        </is>
+      </c>
+      <c r="H379" s="24" t="inlineStr">
+        <is>
+          <t>81996-CP000[CP500용], 81996-CP100[CP600용]</t>
         </is>
       </c>
       <c r="I379" s="19" t="n"/>
       <c r="J379" s="19" t="n"/>
       <c r="K379" s="24" t="inlineStr">
         <is>
-          <t>95440-4EGA0</t>
-        </is>
-      </c>
-      <c r="L379" s="24" t="inlineStr">
-        <is>
-          <t>954304E700</t>
-        </is>
-      </c>
-      <c r="M379" s="28" t="inlineStr">
-        <is>
-          <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
-        </is>
-      </c>
+          <t>95440-CP500[2버튼], 95440-CP600</t>
+        </is>
+      </c>
+      <c r="L379" s="19" t="n"/>
+      <c r="M379" s="19" t="n"/>
       <c r="N379" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O379" s="23" t="inlineStr">
-        <is>
-          <t>내연기관형 지속 판매 추정 — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
-        </is>
-      </c>
-    </row>
-    <row r="380" ht="15" customHeight="1" s="15">
-      <c r="A380" s="19" t="inlineStr">
-        <is>
-          <t>기아</t>
-        </is>
-      </c>
-      <c r="B380" s="19" t="inlineStr">
-        <is>
-          <t>봉고3 EV (전기차)</t>
-        </is>
-      </c>
-      <c r="C380" s="24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D380" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E380" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F380" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G380" s="24" t="inlineStr">
-        <is>
-          <t>ID6A</t>
-        </is>
-      </c>
-      <c r="H380" s="24" t="inlineStr">
-        <is>
-          <t>81996-CP000[CP500용], 81996-CP100[CP600용]</t>
-        </is>
-      </c>
-      <c r="I380" s="19" t="n"/>
-      <c r="J380" s="19" t="n"/>
-      <c r="K380" s="24" t="inlineStr">
-        <is>
-          <t>95440-CP500[2버튼], 95440-CP600</t>
-        </is>
-      </c>
-      <c r="L380" s="19" t="n"/>
-      <c r="M380" s="19" t="n"/>
-      <c r="N380" s="19" t="inlineStr">
-        <is>
-          <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
-        </is>
-      </c>
-      <c r="O380" s="19" t="n"/>
-    </row>
+      <c r="O379" s="19" t="n"/>
+    </row>
+    <row r="380" ht="15" customHeight="1" s="15"/>
   </sheetData>
-  <autoFilter ref="A1:O380"/>
+  <autoFilter ref="A1:O379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805534362793" footer="0.511805534362793"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" usePrinterDefaults="1" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
@@ -23181,7 +23126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.2"/>
   <cols>
     <col width="118" customWidth="1" style="15" min="1" max="1"/>
@@ -23282,7 +23227,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
@@ -23396,6 +23341,79 @@
       <c r="A32" s="33" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="inlineStr">
+        <is>
+          <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>- K3 (Forte, YD 페이스리프트) 2016: A7600 칩은 Lonsdor 8A 스마트키 PCB 지원 차종(K3 2016-2018)으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>- K3 (Forte, YD 페이스리프트) 2017: 국내 현대모비스 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>- K3 (Forte, BD) 2021: 더 뉴 K3(BD PE) 출시(2021.4). 95440-M6800은 한국 시장용 정품 HITAG AES ID4A(NCF29A1M)로 다수 판매처(mk3·abkeys·americankeysupply) 일치 확인 → 기존 'ID8A/ID47 미확정' 해소(PE 이전은 ID8A, PE 이후는 ID4A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>- 스토닉 2017: 스토닉 국내 출시(2017.6.21) — 프라이드(UB)와 같은 플랫폼 공유 크로스오버. 국제 판매처(gskeyae.com) 확인: '2017-2018 KIA Stonic ... 8A Texas Crypto 128-bits AES' — 이전에 'ID47 추정'이라고 했던 건 정정함</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>- 쏘울 (Soul, PS) 2014: 칩: 95440-B2000·B2AA0 한국 시장용 정품 8A Texas Crypto 128bit AES, 4버튼(mk3·abkeys·remotesandkeys) — 이전 'ID47 추정'은 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, QL) 2016: 국제 판매처(go-parts.com, americankeysupply) 확인: Hitag3 ID47 - 이전에 ID6E-MA(DST80) 추정이라고 했던 건 정정함</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, MQ4) 2021: 칩: 95440-P2000(5버튼)·P2200(7버튼)·P2AD0(7버튼) 모두 정품 HITAG AES ID4A(mk3·abkeys·royalkeysupply) — 이전 '추정' 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, DE) 2021: 이전 '적용 시점 추정' 해소: G5025는 원문상 22년형</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>- 레이 2023: 95440-A3600(2022.8.31~)은 DST-AES ID6A 4버튼, 2023-2024 레이 적용(mk3·abkeys·vvdi)</t>
         </is>
       </c>
     </row>

--- a/기아_트랜스폰더_칩코드_DBnew.xlsx
+++ b/기아_트랜스폰더_칩코드_DBnew.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <color rgb="ff000000"/>
@@ -142,8 +142,31 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF9C6500"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +208,21 @@
         <fgColor rgb="FFFFD599"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -221,7 +259,7 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -335,6 +373,33 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -710,30 +775,26 @@
           <t>1995-1997</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F2" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G2" s="19" t="n"/>
+      <c r="D2" s="40" t="n"/>
+      <c r="E2" s="40" t="n"/>
+      <c r="F2" s="40" t="n"/>
+      <c r="G2" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H2" s="19" t="n"/>
       <c r="I2" s="19" t="n"/>
       <c r="J2" s="19" t="n"/>
       <c r="K2" s="19" t="n"/>
       <c r="L2" s="19" t="n"/>
-      <c r="M2" s="19" t="n"/>
+      <c r="M2" s="47" t="n"/>
       <c r="N2" s="19" t="n"/>
-      <c r="O2" s="19" t="n"/>
+      <c r="O2" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="15">
       <c r="A3" s="19" t="inlineStr">
@@ -751,30 +812,26 @@
           <t>1998-2001</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E3" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="n"/>
+      <c r="D3" s="42" t="n"/>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="42" t="n"/>
+      <c r="G3" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H3" s="19" t="n"/>
       <c r="I3" s="19" t="n"/>
       <c r="J3" s="19" t="n"/>
       <c r="K3" s="19" t="n"/>
       <c r="L3" s="19" t="n"/>
-      <c r="M3" s="19" t="n"/>
+      <c r="M3" s="47" t="n"/>
       <c r="N3" s="19" t="n"/>
-      <c r="O3" s="19" t="n"/>
+      <c r="O3" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="15">
       <c r="A4" s="19" t="inlineStr">
@@ -792,22 +849,26 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G4" s="19" t="n"/>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E4" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F4" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
+        </is>
+      </c>
       <c r="H4" s="19" t="n"/>
       <c r="I4" s="19" t="n"/>
       <c r="J4" s="19" t="n"/>
@@ -1060,11 +1121,7 @@
       <c r="L9" s="19" t="n"/>
       <c r="M9" s="19" t="n"/>
       <c r="N9" s="19" t="n"/>
-      <c r="O9" s="19" t="inlineStr">
-        <is>
-          <t>옵티마 국내 마지막 연식(2005.10 단종, 로체로 세대교체). 국제 판매처(abkeys.com) 확인: PN 81996-3C010, 4D-60/HYN7R, 'KIA OPTIMA 2000-2005' 명시 — 나무위키 확인: EF쏘나타와 완전히 동일한 모델(플랫폼·전자장비 100% 공유)</t>
-        </is>
-      </c>
+      <c r="O9" s="19" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="15">
       <c r="A10" s="19" t="inlineStr">
@@ -1125,11 +1182,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O10" s="19" t="inlineStr">
-        <is>
-          <t>로체 국내 출시(2005.10). 국내 현대모비스(hellowcar) 스마트키 원문: 954402G000[~2008.5.28, 블랭킹 819962G020] → 954401M010[2008.8.28~2009.8.10, 819962G520] → 954402G100[2010.8.10~, 819962G030]. 2009.8.10~2010.8.10 사이 품번은 원문에 없음</t>
-        </is>
-      </c>
+      <c r="O10" s="19" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="15">
       <c r="A11" s="19" t="inlineStr">
@@ -1312,11 +1365,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2008년 안에 폴딩키·스마트키 부품 모두 전환</t>
-        </is>
-      </c>
+      <c r="O13" s="19" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="15">
       <c r="A14" s="19" t="inlineStr">
@@ -1377,11 +1426,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 폴딩키 날짜 구간이 일부 겹쳐 표기됨(트림별 차이 가능성), 원문 그대로 병기</t>
-        </is>
-      </c>
+      <c r="O14" s="19" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="15">
       <c r="A15" s="19" t="inlineStr">
@@ -1442,11 +1487,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O15" s="19" t="inlineStr">
-        <is>
-          <t>로체 마지막 연식(2010) — K5로 세대교체. 국내 현대모비스(hellowcar) 스마트키 원문: 954402G000[~2008.5.28, 블랭킹 819962G020] → 954401M010[2008.8.28~2009.8.10, 819962G520] → 954402G100[2010.8.10~, 819962G030]. 2009.8.10~2010.8.10 사이 품번은 원문에 없음</t>
-        </is>
-      </c>
+      <c r="O15" s="19" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="15">
       <c r="A16" s="19" t="inlineStr">
@@ -1507,11 +1548,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O16" s="19" t="inlineStr">
-        <is>
-          <t>포르테 세단(TD) 국내 출시(2008.8.21) — 이 해엔 세단만 있었고 쿠페는 아직 출시 전. 출시 당시 디럭스 트림은 '폴딩타입 무선도어 리모컨키' 기본(다나와 2008년형 트림표). 버튼시동 스마트키가 어느 트림부터 기본인지와 폴딩키 부품번호는 국내 원문에서 확인 못함</t>
-        </is>
-      </c>
+      <c r="O16" s="19" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="15">
       <c r="A17" s="19" t="inlineStr">
@@ -1566,7 +1603,7 @@
         </is>
       </c>
       <c r="L17" s="19" t="n"/>
-      <c r="M17" s="35" t="n"/>
+      <c r="M17" s="38" t="n"/>
       <c r="N17" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -1631,7 +1668,7 @@
         </is>
       </c>
       <c r="L18" s="19" t="n"/>
-      <c r="M18" s="35" t="n"/>
+      <c r="M18" s="38" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -1696,7 +1733,7 @@
         </is>
       </c>
       <c r="L19" s="19" t="n"/>
-      <c r="M19" s="35" t="n"/>
+      <c r="M19" s="38" t="n"/>
       <c r="N19" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -1765,7 +1802,7 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M20" s="35" t="n"/>
+      <c r="M20" s="38" t="n"/>
       <c r="N20" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -1834,7 +1871,7 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M21" s="35" t="n"/>
+      <c r="M21" s="38" t="n"/>
       <c r="N21" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -1903,7 +1940,7 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M22" s="35" t="n"/>
+      <c r="M22" s="38" t="n"/>
       <c r="N22" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -1972,7 +2009,7 @@
           <t>95430-A7200</t>
         </is>
       </c>
-      <c r="M23" s="35" t="n"/>
+      <c r="M23" s="38" t="n"/>
       <c r="N23" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -2177,11 +2214,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O26" s="24" t="inlineStr">
-        <is>
-          <t>K3(BD) 완전변경 출시(2018.2). 국내 현대모비스 원문: BD 스마트키 M6000[2018.1.8~8.30] → M6011[2018.8.30~2021.4.26] · M6501[2018.9.18~2021.3.24] → M6800[2021.4.5~2024.2.8] → M6801[2024.2.8~], 블레이드 81996M6020. BD 초기 스마트키(M6000/M6011/M6501, FCC CQOFD00430) 칩은 정품 기준 DST-AES ID8A(abkeys·tlkeys)</t>
-        </is>
-      </c>
+      <c r="O26" s="24" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="15">
       <c r="A27" s="24" t="inlineStr">
@@ -2199,24 +2232,24 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="44" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="45" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>ID8A</t>
+      <c r="F27" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G27" s="34" t="inlineStr">
+        <is>
+          <t>ID8A[자료 상충], ID47[자료 상충]</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -2240,15 +2273,15 @@
           <t>95430-M6000</t>
         </is>
       </c>
-      <c r="M27" s="19" t="n"/>
+      <c r="M27" s="38" t="n"/>
       <c r="N27" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O27" s="19" t="inlineStr">
-        <is>
-          <t>출처 상충: remotesandkeys.com은 '2020 Forte...TEXAS ID8A'라고 명시하는 반면, dfwkeys4cars.com 종합표는 'Forte 2019-2023: Hitag3 ID47'이라고 명시. 트림별로 다른 칩 공급사(NXP Hitag vs Texas)를 썼을 가능성이 있으나 확정 못함 - 실제 작업 전 VIN 기반 재확인 필수</t>
+      <c r="O27" s="35" t="inlineStr">
+        <is>
+          <t>칩 자료 상충 — remotesandkeys는 2020 Forte TEXAS ID8A, dfwkeys4cars 종합표는 Forte 2019-2023 Hitag3 ID47</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2348,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O28" s="24" t="inlineStr">
-        <is>
-          <t>2021년형(2020년 출시)부터 버튼시동 스마트키 전 트림 기본(모터그래프·엔카)</t>
-        </is>
-      </c>
+      <c r="O28" s="24" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="15">
       <c r="A29" s="24" t="inlineStr">
@@ -2449,11 +2478,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O30" s="19" t="inlineStr">
-        <is>
-          <t>스마트키 전 트림 기본화 이후 폴딩키(M6400)의 적용 대상은 원문 미확인</t>
-        </is>
-      </c>
+      <c r="O30" s="19" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="15">
       <c r="A31" s="24" t="inlineStr">
@@ -2583,11 +2608,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O32" s="24" t="inlineStr">
-        <is>
-          <t>K3 국내 최종 연식 — 2024년 7월 완전 단종. 후속 K4는 국내 미출시(해외 전략형 모델), 국내 준중형 세단 수요는 셀토스·EV3·EV4로 대체됨</t>
-        </is>
-      </c>
+      <c r="O32" s="24" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="15">
       <c r="A33" s="24" t="inlineStr">
@@ -2648,11 +2669,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O33" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 폴딩키 원문: TF 954302T500[~2012.7.6, 블랭킹 819962L000] → 954302T501[2012.7.6~, 819962L001] / JF 954302T570(블랭킹 81996A4000)·95430D4010 / DL3 95430L2000·L2010(블랭킹 81996L2000). 이전에 TF에 넣었던 2T570은 원문상 JF용이라 이동</t>
-        </is>
-      </c>
+      <c r="O33" s="19" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="15">
       <c r="A34" s="24" t="inlineStr">
@@ -2713,11 +2730,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O34" s="24" t="inlineStr">
-        <is>
-          <t>K5 하이브리드(TFE) 출시(2011)</t>
-        </is>
-      </c>
+      <c r="O34" s="24" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="15">
       <c r="A35" s="24" t="inlineStr">
@@ -2839,11 +2852,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O36" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2013.6.10 기준 스마트키·비상키 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O36" s="19" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="15">
       <c r="A37" s="24" t="inlineStr">
@@ -2965,11 +2974,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O38" s="24" t="inlineStr">
-        <is>
-          <t>K5(JF, 올 뉴 K5) 완전변경 출시(2015)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O38" s="24" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="15">
       <c r="A39" s="24" t="inlineStr">
@@ -3091,11 +3096,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O40" s="19" t="inlineStr">
-        <is>
-          <t>더 뉴 K5(JF 페이스리프트) 출시(2017)</t>
-        </is>
-      </c>
+      <c r="O40" s="19" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="15">
       <c r="A41" s="24" t="inlineStr">
@@ -3156,11 +3157,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O41" s="19" t="inlineStr">
-        <is>
-          <t>더뉴K5 하이브리드 2세대(JFE) 출시(2018)</t>
-        </is>
-      </c>
+      <c r="O41" s="19" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="15">
       <c r="A42" s="24" t="inlineStr">
@@ -3221,11 +3218,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O42" s="24" t="inlineStr">
-        <is>
-          <t>JF 마지막 연식</t>
-        </is>
-      </c>
+      <c r="O42" s="24" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="15">
       <c r="A43" s="24" t="inlineStr">
@@ -3286,11 +3279,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O43" s="24" t="inlineStr">
-        <is>
-          <t>K5(DL3) 완전변경 출시(2019.9)로 같은 해 전환 — 하이브리드 3세대(DL3KH)도 2019년 출시</t>
-        </is>
-      </c>
+      <c r="O43" s="24" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="15">
       <c r="A44" s="24" t="inlineStr">
@@ -3351,11 +3340,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O44" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문: L3010·L2200은 연식 라벨 없는 초기 품번, L2320·L2300은 21년형, L2420·L2400은 22년형</t>
-        </is>
-      </c>
+      <c r="O44" s="19" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="15">
       <c r="A45" s="24" t="inlineStr">
@@ -3538,11 +3523,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O47" s="19" t="inlineStr">
-        <is>
-          <t>더 뉴 K5(DL3 페이스리프트) 출시(2023.9)로 전환되는 해 — 95440-L2520은 하이브리드와 공용</t>
-        </is>
-      </c>
+      <c r="O47" s="19" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="15">
       <c r="A48" s="24" t="inlineStr">
@@ -3725,11 +3706,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O50" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문상 PE 스마트키 L2500·L2510·L2520은 종료일 없는 현행 품번</t>
-        </is>
-      </c>
+      <c r="O50" s="19" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="15">
       <c r="A51" s="24" t="inlineStr">
@@ -3790,11 +3767,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O51" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
-        </is>
-      </c>
+      <c r="O51" s="19" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="15">
       <c r="A52" s="24" t="inlineStr">
@@ -3855,11 +3828,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O52" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
-        </is>
-      </c>
+      <c r="O52" s="19" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="15">
       <c r="A53" s="24" t="inlineStr">
@@ -3920,11 +3889,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O53" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
-        </is>
-      </c>
+      <c r="O53" s="19" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="15">
       <c r="A54" s="24" t="inlineStr">
@@ -3989,11 +3954,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O54" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2012.11.5 기준 스마트키 전환. 카드키 원문: 954403R800[2012.10.30~2013.2.28, 블레이드 819963T100] → 954403R801[2013.2.28~2015.12.31] → 95443F6000[2015.12.9~2019.6.27, 블레이드 81996F6110] → 95443F6010[2019.5.30~]</t>
-        </is>
-      </c>
+      <c r="O54" s="19" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="15">
       <c r="A55" s="24" t="inlineStr">
@@ -4058,11 +4019,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O55" s="19" t="inlineStr">
-        <is>
-          <t>이전에 VG 카드키 블레이드를 81996-F6110으로, 카드키에 95443-F6000을 적었으나 둘 다 YG용이라 정정(VG 카드키 블레이드는 819963T100)</t>
-        </is>
-      </c>
+      <c r="O55" s="19" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="15">
       <c r="A56" s="24" t="inlineStr">
@@ -4196,11 +4153,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O57" s="24" t="inlineStr">
-        <is>
-          <t>K7(YG) 완전변경 출시(2016.1)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O57" s="24" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="15">
       <c r="A58" s="24" t="inlineStr">
@@ -4269,11 +4222,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O58" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 이모빌라이저 모듈(95420D4000)은 포터2·그랜드스타렉스와 공유</t>
-        </is>
-      </c>
+      <c r="O58" s="19" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="15">
       <c r="A59" s="24" t="inlineStr">
@@ -4480,11 +4429,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O61" s="24" t="inlineStr">
-        <is>
-          <t>'K7 프리미어' 페이스리프트(2019.6)로 전환되는 해. 이전에 81996-F6110을 프리미어 스마트키 블레이드로 적었으나 원문상 카드키 블레이드라 정정(F6510 스마트키 블레이드는 원문 미확인). 스마트키 모듈(제어기) 95480-F6500</t>
-        </is>
-      </c>
+      <c r="O61" s="24" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="15">
       <c r="A62" s="24" t="inlineStr">
@@ -4553,11 +4498,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O62" s="19" t="inlineStr">
-        <is>
-          <t>스마트키 모듈(제어기): 95480-F6500</t>
-        </is>
-      </c>
+      <c r="O62" s="19" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1" s="15">
       <c r="A63" s="24" t="inlineStr">
@@ -4626,11 +4567,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O63" s="24" t="inlineStr">
-        <is>
-          <t>K7 국내 마지막 연식(2021.1 단종) — 후속 K8으로 이어짐. 스마트키 모듈: 95480-F6500(2019.6-2021.4 적용 확인)</t>
-        </is>
-      </c>
+      <c r="O63" s="24" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1" s="15">
       <c r="A64" s="24" t="inlineStr">
@@ -4695,11 +4632,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O64" s="24" t="inlineStr">
-        <is>
-          <t>K8 국내 출시(2021.4). 국내 현대모비스(hellowcar) 원문: L8000(주차보조X)/L8010(주차보조O)은 ~2024.2.13, 이후 L8001/L8011로 전환. 블레이드 S9000=주차보조X, L2020=주차보조O, 폴딩키용 81996-L2000</t>
-        </is>
-      </c>
+      <c r="O64" s="24" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="15">
       <c r="A65" s="24" t="inlineStr">
@@ -4894,11 +4827,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O67" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar): 2024.2.13은 초기형 L8000·L8010 → L8001·L8011 품번 개정일이고, 페이스리프트(2024.8.9 공개, 위키백과)부터 L8500·L8510·L8520·L8530 적용 — 이전에 2.13을 페이스리프트 전환일로 적었던 것 정정. NFC 카드키 AT954AP000·GZ954AP000(K8GL3/EV6/스포티지NQ5/쏘렌토MQ4/카니발KA4 공용 리스팅)</t>
-        </is>
-      </c>
+      <c r="O67" s="19" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="15">
       <c r="A68" s="24" t="inlineStr">
@@ -5028,11 +4957,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O69" s="19" t="inlineStr">
-        <is>
-          <t>원문상 PE 스마트키 4종은 종료일 없는 현행 품번</t>
-        </is>
-      </c>
+      <c r="O69" s="19" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1" s="15">
       <c r="A70" s="24" t="inlineStr">
@@ -5093,11 +5018,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O70" s="24" t="inlineStr">
-        <is>
-          <t>K9(KH) 국내 출시(2012.3.27). 국내 현대모비스(hellowcar) 원문: 스마트키 954403T200[2012.3.27~2017.12.30]→819963T000, 카드키 954433T000[~2013.7.1, 버튼X]→954433T100[2013.7.1~2014.11.15]→954433T200[2014.11.10~2017.12.30, 버튼X], 카드키 블레이드 819963T100</t>
-        </is>
-      </c>
+      <c r="O70" s="24" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1" s="15">
       <c r="A71" s="24" t="inlineStr">
@@ -5158,11 +5079,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O71" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문: 3T200[2012.3.27~2017.12.30], 3T300[2013.9.1~2014.1.1]. 카드키 날짜도 원문 확인</t>
-        </is>
-      </c>
+      <c r="O71" s="19" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="15">
       <c r="A72" s="24" t="inlineStr">
@@ -5345,11 +5262,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O74" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2016년 카드키 블레이드를 81996-3T200으로 적었으나 원문상 카드키 블레이드는 819963T100이라 정정</t>
-        </is>
-      </c>
+      <c r="O74" s="19" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1" s="15">
       <c r="A75" s="24" t="inlineStr">
@@ -5471,11 +5384,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O76" s="24" t="inlineStr">
-        <is>
-          <t>K9(RJ, '더 K9') 완전변경 출시(2018.4)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O76" s="24" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="15">
       <c r="A77" s="24" t="inlineStr">
@@ -5658,11 +5567,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O79" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2021.5.21 기준 '더뉴 K9'로 부품 전환</t>
-        </is>
-      </c>
+      <c r="O79" s="19" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" s="15">
       <c r="A80" s="24" t="inlineStr">
@@ -5894,11 +5799,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O83" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문: 'K9RJ [2021.5.21 이후~] 95440J6610·J6600·81996J6000·J6100' — 종료일 없는 현행 품번</t>
-        </is>
-      </c>
+      <c r="O83" s="19" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="15">
       <c r="A84" s="24" t="inlineStr">
@@ -5977,30 +5878,26 @@
           <t>1997-2000</t>
         </is>
       </c>
-      <c r="D85" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E85" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F85" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G85" s="19" t="n"/>
+      <c r="D85" s="42" t="n"/>
+      <c r="E85" s="42" t="n"/>
+      <c r="F85" s="42" t="n"/>
+      <c r="G85" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H85" s="19" t="n"/>
       <c r="I85" s="19" t="n"/>
       <c r="J85" s="19" t="n"/>
       <c r="K85" s="19" t="n"/>
       <c r="L85" s="19" t="n"/>
-      <c r="M85" s="19" t="n"/>
+      <c r="M85" s="47" t="n"/>
       <c r="N85" s="19" t="n"/>
-      <c r="O85" s="19" t="n"/>
+      <c r="O85" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="15">
       <c r="A86" s="19" t="inlineStr">
@@ -6018,30 +5915,26 @@
           <t>2000-2003</t>
         </is>
       </c>
-      <c r="D86" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E86" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F86" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G86" s="19" t="n"/>
+      <c r="D86" s="40" t="n"/>
+      <c r="E86" s="40" t="n"/>
+      <c r="F86" s="40" t="n"/>
+      <c r="G86" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H86" s="19" t="n"/>
       <c r="I86" s="19" t="n"/>
       <c r="J86" s="19" t="n"/>
       <c r="K86" s="19" t="n"/>
       <c r="L86" s="19" t="n"/>
-      <c r="M86" s="19" t="n"/>
+      <c r="M86" s="47" t="n"/>
       <c r="N86" s="19" t="n"/>
-      <c r="O86" s="19" t="n"/>
+      <c r="O86" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="15">
       <c r="A87" s="19" t="inlineStr">
@@ -6059,30 +5952,26 @@
           <t>2004-2009</t>
         </is>
       </c>
-      <c r="D87" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E87" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F87" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G87" s="19" t="n"/>
+      <c r="D87" s="42" t="n"/>
+      <c r="E87" s="42" t="n"/>
+      <c r="F87" s="42" t="n"/>
+      <c r="G87" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H87" s="19" t="n"/>
       <c r="I87" s="19" t="n"/>
       <c r="J87" s="19" t="n"/>
       <c r="K87" s="19" t="n"/>
       <c r="L87" s="19" t="n"/>
-      <c r="M87" s="19" t="n"/>
+      <c r="M87" s="47" t="n"/>
       <c r="N87" s="19" t="n"/>
-      <c r="O87" s="19" t="n"/>
+      <c r="O87" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="15">
       <c r="A88" s="19" t="inlineStr">
@@ -6100,30 +5989,26 @@
           <t>2004-2008</t>
         </is>
       </c>
-      <c r="D88" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E88" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F88" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G88" s="19" t="n"/>
+      <c r="D88" s="42" t="n"/>
+      <c r="E88" s="42" t="n"/>
+      <c r="F88" s="42" t="n"/>
+      <c r="G88" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H88" s="19" t="n"/>
       <c r="I88" s="19" t="n"/>
       <c r="J88" s="19" t="n"/>
       <c r="K88" s="19" t="n"/>
       <c r="L88" s="19" t="n"/>
-      <c r="M88" s="19" t="n"/>
+      <c r="M88" s="47" t="n"/>
       <c r="N88" s="19" t="n"/>
-      <c r="O88" s="19" t="n"/>
+      <c r="O88" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="15">
       <c r="A89" s="19" t="inlineStr">
@@ -6141,30 +6026,26 @@
           <t>1994-1999</t>
         </is>
       </c>
-      <c r="D89" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E89" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F89" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G89" s="19" t="n"/>
+      <c r="D89" s="40" t="n"/>
+      <c r="E89" s="40" t="n"/>
+      <c r="F89" s="40" t="n"/>
+      <c r="G89" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H89" s="19" t="n"/>
       <c r="I89" s="19" t="n"/>
       <c r="J89" s="19" t="n"/>
       <c r="K89" s="19" t="n"/>
       <c r="L89" s="19" t="n"/>
-      <c r="M89" s="19" t="n"/>
+      <c r="M89" s="47" t="n"/>
       <c r="N89" s="19" t="n"/>
-      <c r="O89" s="19" t="n"/>
+      <c r="O89" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="15">
       <c r="A90" s="19" t="inlineStr">
@@ -6213,11 +6094,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O90" s="19" t="inlineStr">
-        <is>
-          <t>프라이드(JB) 국내 출시(2005.4.7) — 리오(BC) 후속, 국내 차명이 '프라이드'로 부활. 기본트림(LX)은 무선도어리모콘키만 제공</t>
-        </is>
-      </c>
+      <c r="O90" s="19" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1" s="15">
       <c r="A91" s="19" t="inlineStr">
@@ -6250,7 +6127,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G91" s="24" t="inlineStr">
+      <c r="G91" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -6260,15 +6137,15 @@
       <c r="J91" s="19" t="n"/>
       <c r="K91" s="19" t="n"/>
       <c r="L91" s="19" t="n"/>
-      <c r="M91" s="19" t="n"/>
+      <c r="M91" s="38" t="n"/>
       <c r="N91" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O91" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O91" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6180,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G92" s="24" t="inlineStr">
+      <c r="G92" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -6313,15 +6190,15 @@
       <c r="J92" s="19" t="n"/>
       <c r="K92" s="19" t="n"/>
       <c r="L92" s="19" t="n"/>
-      <c r="M92" s="19" t="n"/>
+      <c r="M92" s="38" t="n"/>
       <c r="N92" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O92" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O92" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6233,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G93" s="24" t="inlineStr">
+      <c r="G93" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -6366,15 +6243,15 @@
       <c r="J93" s="19" t="n"/>
       <c r="K93" s="19" t="n"/>
       <c r="L93" s="19" t="n"/>
-      <c r="M93" s="19" t="n"/>
+      <c r="M93" s="38" t="n"/>
       <c r="N93" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O93" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O93" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6286,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G94" s="24" t="inlineStr">
+      <c r="G94" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -6419,15 +6296,15 @@
       <c r="J94" s="19" t="n"/>
       <c r="K94" s="19" t="n"/>
       <c r="L94" s="19" t="n"/>
-      <c r="M94" s="19" t="n"/>
+      <c r="M94" s="38" t="n"/>
       <c r="N94" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O94" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O94" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6339,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G95" s="24" t="inlineStr">
+      <c r="G95" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -6472,15 +6349,15 @@
       <c r="J95" s="19" t="n"/>
       <c r="K95" s="19" t="n"/>
       <c r="L95" s="19" t="n"/>
-      <c r="M95" s="19" t="n"/>
+      <c r="M95" s="38" t="n"/>
       <c r="N95" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O95" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O95" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -6531,11 +6408,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O96" s="19" t="inlineStr">
-        <is>
-          <t>올 뉴 프라이드(UB) 완전변경 출시(2011.9.28)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O96" s="19" t="n"/>
     </row>
     <row r="97" ht="15" customHeight="1" s="15">
       <c r="A97" s="19" t="inlineStr">
@@ -6568,7 +6441,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G97" s="24" t="inlineStr">
+      <c r="G97" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA, ID46(PCF7952)</t>
         </is>
@@ -6578,15 +6451,15 @@
       <c r="J97" s="19" t="n"/>
       <c r="K97" s="19" t="n"/>
       <c r="L97" s="19" t="n"/>
-      <c r="M97" s="19" t="n"/>
+      <c r="M97" s="38" t="n"/>
       <c r="N97" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O97" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O97" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -6641,11 +6514,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O98" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인</t>
-        </is>
-      </c>
+      <c r="O98" s="19" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1" s="15">
       <c r="A99" s="19" t="inlineStr">
@@ -6706,11 +6575,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O99" s="19" t="inlineStr">
-        <is>
-          <t>더 뉴 프라이드 페이스리프트(2014.12) 출시. 국내 현대모비스(hellowcar) 재확인 — 비상키 접두사가 81996이 아니라 81999인 경우가 2개 있어서 정정함</t>
-        </is>
-      </c>
+      <c r="O99" s="19" t="n"/>
     </row>
     <row r="100" ht="15" customHeight="1" s="15">
       <c r="A100" s="19" t="inlineStr">
@@ -6893,11 +6758,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O102" s="19" t="inlineStr">
-        <is>
-          <t>프라이드 국내 마지막 연식(2017.9 단종) — 4세대(리오 YB)는 국내 출시가 백지화되고 같은 플랫폼의 크로스오버 스토닉(SP2)으로 대체, 국내 후속 없음(위키백과 확인)</t>
-        </is>
-      </c>
+      <c r="O102" s="19" t="n"/>
     </row>
     <row r="103" ht="15" customHeight="1" s="15">
       <c r="A103" s="19" t="inlineStr">
@@ -6915,30 +6776,26 @@
           <t>1992-2002</t>
         </is>
       </c>
-      <c r="D103" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E103" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F103" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G103" s="19" t="n"/>
+      <c r="D103" s="40" t="n"/>
+      <c r="E103" s="40" t="n"/>
+      <c r="F103" s="40" t="n"/>
+      <c r="G103" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H103" s="19" t="n"/>
       <c r="I103" s="19" t="n"/>
       <c r="J103" s="19" t="n"/>
       <c r="K103" s="19" t="n"/>
       <c r="L103" s="19" t="n"/>
-      <c r="M103" s="19" t="n"/>
+      <c r="M103" s="47" t="n"/>
       <c r="N103" s="19" t="n"/>
-      <c r="O103" s="19" t="n"/>
+      <c r="O103" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="15">
       <c r="A104" s="19" t="inlineStr">
@@ -6956,30 +6813,26 @@
           <t>1997-2002</t>
         </is>
       </c>
-      <c r="D104" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E104" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F104" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G104" s="19" t="n"/>
+      <c r="D104" s="40" t="n"/>
+      <c r="E104" s="40" t="n"/>
+      <c r="F104" s="40" t="n"/>
+      <c r="G104" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H104" s="19" t="n"/>
       <c r="I104" s="19" t="n"/>
       <c r="J104" s="19" t="n"/>
       <c r="K104" s="19" t="n"/>
       <c r="L104" s="19" t="n"/>
-      <c r="M104" s="19" t="n"/>
+      <c r="M104" s="47" t="n"/>
       <c r="N104" s="19" t="n"/>
-      <c r="O104" s="19" t="n"/>
+      <c r="O104" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="15">
       <c r="A105" s="19" t="inlineStr">
@@ -6997,34 +6850,38 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="D105" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E105" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F105" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G105" s="19" t="n"/>
-      <c r="H105" s="19" t="n"/>
+      <c r="D105" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E105" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F105" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G105" s="38" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
+        </is>
+      </c>
+      <c r="H105" s="19" t="inlineStr">
+        <is>
+          <t>81996-3FA10[막대키]</t>
+        </is>
+      </c>
       <c r="I105" s="19" t="n"/>
       <c r="J105" s="19" t="n"/>
       <c r="K105" s="19" t="n"/>
       <c r="L105" s="19" t="n"/>
-      <c r="M105" s="19" t="n"/>
+      <c r="M105" s="38" t="n"/>
       <c r="N105" s="19" t="n"/>
-      <c r="O105" s="19" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
-        </is>
-      </c>
+      <c r="O105" s="38" t="n"/>
     </row>
     <row r="106" ht="15" customHeight="1" s="15">
       <c r="A106" s="19" t="inlineStr">
@@ -7077,11 +6934,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O106" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처(remotesandkeys.com, key4.com) 확인: PN 81996-3FA10, ILCO KK7-PT, 4D60 — 리모컨 없는 막대형 키(2003-2006 공용)</t>
-        </is>
-      </c>
+      <c r="O106" s="19" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1" s="15">
       <c r="A107" s="19" t="inlineStr">
@@ -7134,11 +6987,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O107" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처 확인 — 막대형 키</t>
-        </is>
-      </c>
+      <c r="O107" s="19" t="n"/>
     </row>
     <row r="108" ht="15" customHeight="1" s="15">
       <c r="A108" s="19" t="inlineStr">
@@ -7191,11 +7040,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O108" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처 확인 — 막대형 키</t>
-        </is>
-      </c>
+      <c r="O108" s="19" t="n"/>
     </row>
     <row r="109" ht="15" customHeight="1" s="15">
       <c r="A109" s="19" t="inlineStr">
@@ -7248,11 +7093,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O109" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처(remotesandkeys.com) 확인: PN 81996-3F050, ILCO KK9-PT, ID46 — 리모컨 없는 막대형 키</t>
-        </is>
-      </c>
+      <c r="O109" s="19" t="n"/>
     </row>
     <row r="110" ht="15" customHeight="1" s="15">
       <c r="A110" s="19" t="inlineStr">
@@ -7305,11 +7146,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O110" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처 확인 — 막대형 키</t>
-        </is>
-      </c>
+      <c r="O110" s="19" t="n"/>
     </row>
     <row r="111" ht="15" customHeight="1" s="15">
       <c r="A111" s="19" t="inlineStr">
@@ -7362,11 +7199,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O111" s="19" t="inlineStr">
-        <is>
-          <t>오피러스 프리미엄 페이스리프트(2009.5) 출시 — 국내 현대모비스 확인</t>
-        </is>
-      </c>
+      <c r="O111" s="19" t="n"/>
     </row>
     <row r="112" ht="15" customHeight="1" s="15">
       <c r="A112" s="19" t="inlineStr">
@@ -7525,11 +7358,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O114" s="19" t="inlineStr">
-        <is>
-          <t>오피러스 국내 마지막 연식(2012.5) — K7(Cadenza)로 세대교체, 직접적 후속 없음</t>
-        </is>
-      </c>
+      <c r="O114" s="19" t="n"/>
     </row>
     <row r="115" ht="15" customHeight="1" s="15">
       <c r="A115" s="19" t="inlineStr">
@@ -7586,11 +7415,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O115" s="19" t="inlineStr">
-        <is>
-          <t>스팅어 국내 출시(2017.5) — 제네시스 G70(IK)와 플랫폼 공유</t>
-        </is>
-      </c>
+      <c r="O115" s="19" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1" s="15">
       <c r="A116" s="19" t="inlineStr">
@@ -7647,11 +7472,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O116" s="19" t="inlineStr">
-        <is>
-          <t>국내 판매처(모터스K) 확인: 2018년 7월 이후 생산된 19년형은 95440-J5200이 맞지 않을 수 있고 95440-J5210 적용. 국내 현대모비스(hellowcar): J5200·J5210은 ~2020.7.28, 이후 J5700·J5710, 블레이드 81996J5000</t>
-        </is>
-      </c>
+      <c r="O116" s="19" t="n"/>
     </row>
     <row r="117" ht="15" customHeight="1" s="15">
       <c r="A117" s="19" t="inlineStr">
@@ -7765,11 +7586,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O118" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2020.7.28 기준 페이스리프트 부품 전환</t>
-        </is>
-      </c>
+      <c r="O118" s="19" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1" s="15">
       <c r="A119" s="19" t="inlineStr">
@@ -7940,11 +7757,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O121" s="19" t="inlineStr">
-        <is>
-          <t>스팅어 국내외 단종(2023.4) — 직접적 후속 없음</t>
-        </is>
-      </c>
+      <c r="O121" s="19" t="n"/>
     </row>
     <row r="122" ht="15" customHeight="1" s="15">
       <c r="A122" s="19" t="inlineStr">
@@ -8172,11 +7985,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O125" s="19" t="inlineStr">
-        <is>
-          <t>페이스리프트('더 뉴 스토닉') 출시(2020)</t>
-        </is>
-      </c>
+      <c r="O125" s="19" t="n"/>
     </row>
     <row r="126" ht="15" customHeight="1" s="15">
       <c r="A126" s="19" t="inlineStr">
@@ -8347,11 +8156,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O128" s="19" t="inlineStr">
-        <is>
-          <t>생산지 이관(광명→서산 동희오토), 국내 부품번호는 초기형과 동일 계열로 확인, 페이스리프트 이후 세부 개정 여부는 미확인</t>
-        </is>
-      </c>
+      <c r="O128" s="19" t="n"/>
     </row>
     <row r="129" ht="15" customHeight="1" s="15">
       <c r="A129" s="19" t="inlineStr">
@@ -8408,11 +8213,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O129" s="19" t="inlineStr">
-        <is>
-          <t>국내 판매처(모터스K)·헬로우카 원문: 스마트키 95440H8000·블랭킹 81999H8300 '적용시점 2017.6.21~'(종료일·개정품번 없음) → 같은 PN이므로 칩도 ID8A</t>
-        </is>
-      </c>
+      <c r="O129" s="19" t="n"/>
     </row>
     <row r="130" ht="15" customHeight="1" s="15">
       <c r="A130" s="19" t="inlineStr">
@@ -8445,7 +8246,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G130" s="24" t="inlineStr">
+      <c r="G130" s="34" t="inlineStr">
         <is>
           <t>ID8A</t>
         </is>
@@ -8463,15 +8264,15 @@
         </is>
       </c>
       <c r="L130" s="19" t="n"/>
-      <c r="M130" s="19" t="n"/>
+      <c r="M130" s="38" t="n"/>
       <c r="N130" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O130" s="24" t="inlineStr">
-        <is>
-          <t>2차 페이스리프트 출시(2025.9.1) — 세부 전자장비 변경 여부 미확인, 재확인 필요</t>
+      <c r="O130" s="34" t="inlineStr">
+        <is>
+          <t>2차 페이스리프트(2025.9) 이후 스마트키 개정 여부 원문 없음 — 기존 95440-H8000(ID8A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8307,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G131" s="24" t="inlineStr">
+      <c r="G131" s="34" t="inlineStr">
         <is>
           <t>ID8A</t>
         </is>
@@ -8524,15 +8325,15 @@
         </is>
       </c>
       <c r="L131" s="19" t="n"/>
-      <c r="M131" s="19" t="n"/>
+      <c r="M131" s="38" t="n"/>
       <c r="N131" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O131" s="24" t="inlineStr">
-        <is>
-          <t>2026년형 마일드하이브리드 출력 상향 확인(나무위키) — 전자장비 변경 여부는 미확인</t>
+      <c r="O131" s="34" t="inlineStr">
+        <is>
+          <t>2차 페이스리프트(2025.9) 이후 스마트키 개정 여부 원문 없음 — 기존 95440-H8000(ID8A) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8390,7 @@
           <t>95430-Q5000</t>
         </is>
       </c>
-      <c r="M132" s="35" t="n"/>
+      <c r="M132" s="38" t="n"/>
       <c r="N132" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -8660,11 +8461,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O133" s="19" t="inlineStr">
-        <is>
-          <t>연식변경(2020.7.1) — 전방충돌방지보조 등 안전사양 추가</t>
-        </is>
-      </c>
+      <c r="O133" s="19" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1" s="15">
       <c r="A134" s="19" t="inlineStr">
@@ -8786,11 +8583,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O135" s="24" t="inlineStr">
-        <is>
-          <t>'더 뉴 셀토스'(SP2 PE) 페이스리프트 출시(2022.7)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O135" s="24" t="n"/>
     </row>
     <row r="136" ht="15" customHeight="1" s="15">
       <c r="A136" s="19" t="inlineStr">
@@ -9006,7 +8799,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G139" s="24" t="inlineStr">
+      <c r="G139" s="34" t="inlineStr">
         <is>
           <t>ID8A, ID6A[SP2 PE]</t>
         </is>
@@ -9028,15 +8821,15 @@
           <t>95430-Q5700[SP2, PE], 95430-Q5750[SP2, PE]</t>
         </is>
       </c>
-      <c r="M139" s="19" t="n"/>
+      <c r="M139" s="38" t="n"/>
       <c r="N139" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O139" s="24" t="inlineStr">
-        <is>
-          <t>SP2 판매 종료(2026.1), '디 올 뉴 셀토스'(SP3) 2026.1.27 계약·출고 시작(나무위키·다나와). SP3 스마트키 부품번호·칩은 국내 원문에서 아직 확인 못함</t>
+      <c r="O139" s="34" t="inlineStr">
+        <is>
+          <t>디 올 뉴 셀토스(SP3, 2026.1) 스마트키 품번·칩 원문 없음 — SP2 PE 기준</t>
         </is>
       </c>
     </row>
@@ -9056,22 +8849,26 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="D140" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E140" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F140" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G140" s="19" t="n"/>
+      <c r="D140" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E140" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F140" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G140" s="19" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952A)</t>
+        </is>
+      </c>
       <c r="H140" s="19" t="n"/>
       <c r="I140" s="19" t="n"/>
       <c r="J140" s="19" t="n"/>
@@ -9079,11 +8876,7 @@
       <c r="L140" s="19" t="n"/>
       <c r="M140" s="19" t="n"/>
       <c r="N140" s="19" t="n"/>
-      <c r="O140" s="19" t="inlineStr">
-        <is>
-          <t>쏘울 국내 출시(2008)</t>
-        </is>
-      </c>
+      <c r="O140" s="19" t="n"/>
     </row>
     <row r="141" ht="15" customHeight="1" s="15">
       <c r="A141" s="19" t="inlineStr">
@@ -9140,11 +8933,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O141" s="19" t="inlineStr">
-        <is>
-          <t>칩: transpondery.com 'KIA SOUL 2008-2013: Philips PCF7952A / ID46 / Hitag 2', 2013 정품 폴딩키 '46 Chip'(vvdi)</t>
-        </is>
-      </c>
+      <c r="O141" s="19" t="n"/>
     </row>
     <row r="142" ht="15" customHeight="1" s="15">
       <c r="A142" s="19" t="inlineStr">
@@ -9771,11 +9560,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O152" s="19" t="inlineStr">
-        <is>
-          <t>쏘울 부스터(SK3) 완전변경 출시(2019). 국내 현대모비스(hellowcar) 확인 — 연식별 세부 날짜는 추가 확인 필요</t>
-        </is>
-      </c>
+      <c r="O152" s="19" t="n"/>
     </row>
     <row r="153" ht="15" customHeight="1" s="15">
       <c r="A153" s="19" t="inlineStr">
@@ -10117,11 +9902,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O158" s="19" t="inlineStr">
-        <is>
-          <t>쏘울 국내외 최종 단종 연식(2025) — 후속 없음(나무위키 확인)</t>
-        </is>
-      </c>
+      <c r="O158" s="19" t="n"/>
     </row>
     <row r="159" ht="15" customHeight="1" s="15">
       <c r="A159" s="19" t="inlineStr">
@@ -10182,11 +9963,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O159" s="19" t="inlineStr">
-        <is>
-          <t>레이 국내 출시(2011.11) — 국내 현대모비스(hellowcar) 날짜별 원문 재확인</t>
-        </is>
-      </c>
+      <c r="O159" s="19" t="n"/>
     </row>
     <row r="160" ht="15" customHeight="1" s="15">
       <c r="A160" s="19" t="inlineStr">
@@ -10430,11 +10207,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O163" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2015-2016 폴딩키를 A3100/A3110으로 적었으나 원문상 A3001 구간(2012.9.10~2017.12.12)이라 정정</t>
-        </is>
-      </c>
+      <c r="O163" s="19" t="n"/>
     </row>
     <row r="164" ht="15" customHeight="1" s="15">
       <c r="A164" s="19" t="inlineStr">
@@ -10556,11 +10329,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O165" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2017년 하반기 스마트키 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O165" s="19" t="n"/>
     </row>
     <row r="166" ht="15" customHeight="1" s="15">
       <c r="A166" s="19" t="inlineStr">
@@ -10865,11 +10634,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O170" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2022.9.5 기준 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O170" s="19" t="n"/>
     </row>
     <row r="171" ht="15" customHeight="1" s="15">
       <c r="A171" s="19" t="inlineStr">
@@ -11052,11 +10817,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O173" s="19" t="inlineStr">
-        <is>
-          <t>원문상 스마트키 A3600[2022.8.31~], 폴딩키 A3600[2022.8.31~]·A3610[2023.6.16~] 모두 종료일 없는 현행 품번</t>
-        </is>
-      </c>
+      <c r="O173" s="19" t="n"/>
     </row>
     <row r="174" ht="15" customHeight="1" s="15">
       <c r="A174" s="19" t="inlineStr">
@@ -11074,30 +10835,26 @@
           <t>1997-2004</t>
         </is>
       </c>
-      <c r="D174" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E174" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F174" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G174" s="19" t="n"/>
+      <c r="D174" s="40" t="n"/>
+      <c r="E174" s="40" t="n"/>
+      <c r="F174" s="40" t="n"/>
+      <c r="G174" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H174" s="19" t="n"/>
       <c r="I174" s="19" t="n"/>
       <c r="J174" s="19" t="n"/>
       <c r="K174" s="19" t="n"/>
       <c r="L174" s="19" t="n"/>
-      <c r="M174" s="19" t="n"/>
+      <c r="M174" s="47" t="n"/>
       <c r="N174" s="19" t="n"/>
-      <c r="O174" s="19" t="n"/>
+      <c r="O174" s="41" t="inlineStr">
+        <is>
+          <t>연식을 나누지 않은 예전 목록 행 — 칩 조사 대상에서 빠져 있음</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="15" customHeight="1" s="15">
       <c r="A175" s="19" t="inlineStr">
@@ -11146,11 +10903,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O175" s="19" t="inlineStr">
-        <is>
-          <t>모닝 국내 출시(2004)</t>
-        </is>
-      </c>
+      <c r="O175" s="19" t="n"/>
     </row>
     <row r="176" ht="15" customHeight="1" s="15">
       <c r="A176" s="19" t="inlineStr">
@@ -11183,7 +10936,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G176" s="24" t="inlineStr">
+      <c r="G176" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -11193,15 +10946,15 @@
       <c r="J176" s="19" t="n"/>
       <c r="K176" s="19" t="n"/>
       <c r="L176" s="19" t="n"/>
-      <c r="M176" s="19" t="n"/>
+      <c r="M176" s="38" t="n"/>
       <c r="N176" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O176" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O176" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -11236,7 +10989,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G177" s="24" t="inlineStr">
+      <c r="G177" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -11246,15 +10999,15 @@
       <c r="J177" s="19" t="n"/>
       <c r="K177" s="19" t="n"/>
       <c r="L177" s="19" t="n"/>
-      <c r="M177" s="19" t="n"/>
+      <c r="M177" s="38" t="n"/>
       <c r="N177" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O177" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O177" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11042,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G178" s="24" t="inlineStr">
+      <c r="G178" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -11299,15 +11052,15 @@
       <c r="J178" s="19" t="n"/>
       <c r="K178" s="19" t="n"/>
       <c r="L178" s="19" t="n"/>
-      <c r="M178" s="19" t="n"/>
+      <c r="M178" s="38" t="n"/>
       <c r="N178" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O178" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O178" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11095,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G179" s="24" t="inlineStr">
+      <c r="G179" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -11352,15 +11105,15 @@
       <c r="J179" s="19" t="n"/>
       <c r="K179" s="19" t="n"/>
       <c r="L179" s="19" t="n"/>
-      <c r="M179" s="19" t="n"/>
+      <c r="M179" s="38" t="n"/>
       <c r="N179" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O179" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O179" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -11395,7 +11148,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G180" s="24" t="inlineStr">
+      <c r="G180" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
@@ -11405,15 +11158,15 @@
       <c r="J180" s="19" t="n"/>
       <c r="K180" s="19" t="n"/>
       <c r="L180" s="19" t="n"/>
-      <c r="M180" s="19" t="n"/>
+      <c r="M180" s="38" t="n"/>
       <c r="N180" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O180" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O180" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -11472,11 +11225,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O181" s="24" t="inlineStr">
-        <is>
-          <t>TA 완전변경 출시(2011)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O181" s="24" t="n"/>
     </row>
     <row r="182" ht="15" customHeight="1" s="15">
       <c r="A182" s="19" t="inlineStr">
@@ -11537,11 +11286,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O182" s="19" t="inlineStr">
-        <is>
-          <t>올뉴 모닝(TA) 출시(2011.1). 국내 현대모비스(hellowcar) 원문: TA 스마트키 954401Y500[~2013.8.16, 블랭킹 819961Y020] → 954401Y600[2013.8.16~2016.12.29, 819961Y620] / JA 스마트키 95440G6000[2016.10.25~, ~22년식]·95440G6100[22년식~] ~2023.6.27(블랭킹 81996G6020) → 95440G6500[2023.6.27~, 81996P2800]. 이전에 TA에 G6000·G6100, JA에 1Y500·1Y600을 적었던 것은 서로 뒤바뀐 오류라 정정</t>
-        </is>
-      </c>
+      <c r="O182" s="19" t="n"/>
     </row>
     <row r="183" ht="15" customHeight="1" s="15">
       <c r="A183" s="19" t="inlineStr">
@@ -11602,11 +11347,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O183" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2012.9.27 기준 폴딩키 전환</t>
-        </is>
-      </c>
+      <c r="O183" s="19" t="n"/>
     </row>
     <row r="184" ht="15" customHeight="1" s="15">
       <c r="A184" s="19" t="inlineStr">
@@ -11667,11 +11408,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O184" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2013.8.1 기준 폴딩키 전환</t>
-        </is>
-      </c>
+      <c r="O184" s="19" t="n"/>
     </row>
     <row r="185" ht="15" customHeight="1" s="15">
       <c r="A185" s="19" t="inlineStr">
@@ -11887,7 +11624,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G188" s="24" t="inlineStr">
+      <c r="G188" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[TA], ID46[TA], ID6E-MA[JA, 자료 상충], ID75[JA, 자료 상충]</t>
         </is>
@@ -11909,15 +11646,15 @@
           <t>954301Y500[TA, ~2016.12.29], 95430-G6500[JA], 95430-G6600[JA, 3버튼], 95430-G6700[JA]</t>
         </is>
       </c>
-      <c r="M188" s="19" t="n"/>
+      <c r="M188" s="38" t="n"/>
       <c r="N188" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O188" s="19" t="inlineStr">
-        <is>
-          <t>모닝(JA) 완전변경 출시(2017)로 전환되는 해</t>
+      <c r="O188" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11689,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G189" s="24" t="inlineStr">
+      <c r="G189" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
         </is>
@@ -11974,15 +11711,15 @@
           <t>95430-G6500, 95430-G6600[3버튼], 95430-G6700</t>
         </is>
       </c>
-      <c r="M189" s="19" t="n"/>
+      <c r="M189" s="38" t="n"/>
       <c r="N189" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O189" s="19" t="inlineStr">
-        <is>
-          <t>폴딩키 G6500·G6600·G6700(블랭킹 81996G6100)은 부품 확인, 연식별 적용 날짜는 원문에 없음</t>
+      <c r="O189" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
         </is>
       </c>
     </row>
@@ -12017,7 +11754,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G190" s="24" t="inlineStr">
+      <c r="G190" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
         </is>
@@ -12039,13 +11776,17 @@
           <t>95430-G6500, 95430-G6600[3버튼], 95430-G6700</t>
         </is>
       </c>
-      <c r="M190" s="19" t="n"/>
+      <c r="M190" s="38" t="n"/>
       <c r="N190" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O190" s="19" t="n"/>
+      <c r="O190" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="15" customHeight="1" s="15">
       <c r="A191" s="19" t="inlineStr">
@@ -12078,7 +11819,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G191" s="24" t="inlineStr">
+      <c r="G191" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
         </is>
@@ -12100,15 +11841,15 @@
           <t>95430-G6500, 95430-G6600[3버튼], 95430-G6700</t>
         </is>
       </c>
-      <c r="M191" s="19" t="n"/>
+      <c r="M191" s="38" t="n"/>
       <c r="N191" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O191" s="19" t="inlineStr">
-        <is>
-          <t>모닝 어반(페이스리프트) 출시(2020)</t>
+      <c r="O191" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
         </is>
       </c>
     </row>
@@ -12143,7 +11884,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G192" s="24" t="inlineStr">
+      <c r="G192" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
         </is>
@@ -12165,13 +11906,17 @@
           <t>95430-G6500, 95430-G6600[3버튼], 95430-G6700</t>
         </is>
       </c>
-      <c r="M192" s="19" t="n"/>
+      <c r="M192" s="38" t="n"/>
       <c r="N192" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O192" s="19" t="n"/>
+      <c r="O192" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="15" customHeight="1" s="15">
       <c r="A193" s="19" t="inlineStr">
@@ -12204,7 +11949,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G193" s="24" t="inlineStr">
+      <c r="G193" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
         </is>
@@ -12226,13 +11971,17 @@
           <t>95430-G6500, 95430-G6600[3버튼], 95430-G6700</t>
         </is>
       </c>
-      <c r="M193" s="19" t="n"/>
+      <c r="M193" s="38" t="n"/>
       <c r="N193" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O193" s="19" t="n"/>
+      <c r="O193" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="15" customHeight="1" s="15">
       <c r="A194" s="19" t="inlineStr">
@@ -12265,7 +12014,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G194" s="24" t="inlineStr">
+      <c r="G194" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
         </is>
@@ -12287,13 +12036,17 @@
           <t>95430-G6500, 95430-G6600[3버튼], 95430-G6700</t>
         </is>
       </c>
-      <c r="M194" s="19" t="n"/>
+      <c r="M194" s="38" t="n"/>
       <c r="N194" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O194" s="19" t="n"/>
+      <c r="O194" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1" s="15">
       <c r="A195" s="19" t="inlineStr">
@@ -12326,7 +12079,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G195" s="24" t="inlineStr">
+      <c r="G195" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
         </is>
@@ -12348,13 +12101,17 @@
           <t>95430-G6500, 95430-G6600[3버튼], 95430-G6700</t>
         </is>
       </c>
-      <c r="M195" s="19" t="n"/>
+      <c r="M195" s="38" t="n"/>
       <c r="N195" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O195" s="19" t="n"/>
+      <c r="O195" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="15" customHeight="1" s="15">
       <c r="A196" s="19" t="inlineStr">
@@ -12387,7 +12144,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G196" s="24" t="inlineStr">
+      <c r="G196" s="34" t="inlineStr">
         <is>
           <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
         </is>
@@ -12409,13 +12166,17 @@
           <t>95430-G6500, 95430-G6600[3버튼], 95430-G6700</t>
         </is>
       </c>
-      <c r="M196" s="19" t="n"/>
+      <c r="M196" s="38" t="n"/>
       <c r="N196" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O196" s="19" t="n"/>
+      <c r="O196" s="35" t="inlineStr">
+        <is>
+          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="15" customHeight="1" s="15">
       <c r="A197" s="24" t="inlineStr">
@@ -12468,11 +12229,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O197" s="24" t="inlineStr">
-        <is>
-          <t>EV3 국내 출시(2024.7) — K3 플랫폼 기반 E-GMP, 국내 현대모비스 확인. 부품번호는 '주차보조/디지털키' 조합별 4종</t>
-        </is>
-      </c>
+      <c r="O197" s="24" t="n"/>
     </row>
     <row r="198" ht="15" customHeight="1" s="15">
       <c r="A198" s="24" t="inlineStr">
@@ -12578,11 +12335,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O199" s="24" t="inlineStr">
-        <is>
-          <t>'더 EV3' 연식변경(2026.2.2 출시)</t>
-        </is>
-      </c>
+      <c r="O199" s="24" t="n"/>
     </row>
     <row r="200" ht="15" customHeight="1" s="15">
       <c r="A200" s="24" t="inlineStr">
@@ -12629,7 +12382,7 @@
         </is>
       </c>
       <c r="L200" s="19" t="n"/>
-      <c r="M200" s="35" t="n"/>
+      <c r="M200" s="38" t="n"/>
       <c r="N200" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -12686,7 +12439,7 @@
         </is>
       </c>
       <c r="L201" s="19" t="n"/>
-      <c r="M201" s="35" t="n"/>
+      <c r="M201" s="38" t="n"/>
       <c r="N201" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
@@ -12757,11 +12510,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O202" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문: CV000(주차보조X)/CV010(주차보조O) ~2024.2.7, 이후 CV001/CV011. 블레이드 CV000=주차보조X, CV010=주차보조O</t>
-        </is>
-      </c>
+      <c r="O202" s="19" t="n"/>
     </row>
     <row r="203" ht="15" customHeight="1" s="15">
       <c r="A203" s="24" t="inlineStr">
@@ -12944,11 +12693,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O205" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar): 초기형 CV000·CV010[~2024.2.7] → CV001·CV011[2024.2.7~], 페이스리프트 전용 CV500·CV510·CV520 별도 리스팅(적용 시작일 원문 미확인). 칩: 95440-CV000 정품 HITAG AES ID4A(tlkeys)</t>
-        </is>
-      </c>
+      <c r="O205" s="19" t="n"/>
     </row>
     <row r="206" ht="15" customHeight="1" s="15">
       <c r="A206" s="24" t="inlineStr">
@@ -13009,11 +12754,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O206" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2025~2026년에 초기형 CV001·CV011을 적었으나 페이스리프트 전용 CV500·CV510·CV520으로 정정(hellowcar). CV510·CV520 해외 판매처 적용 2025~2026</t>
-        </is>
-      </c>
+      <c r="O206" s="19" t="n"/>
     </row>
     <row r="207" ht="15" customHeight="1" s="15">
       <c r="A207" s="24" t="inlineStr">
@@ -13131,11 +12872,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O208" s="24" t="inlineStr">
-        <is>
-          <t>EV9 국내 출시(2023.5). 국내 현대모비스(hellowcar): 스마트키 DO000·DO010·DO020·DO030(사양 표기 원문 그대로), 블랭킹 81996DO000, 케이스 81995DO000 — 종료일 없는 현행 품번. 이전에 넣었던 DO060은 국내 원문에 없어 삭제</t>
-        </is>
-      </c>
+      <c r="O208" s="24" t="n"/>
     </row>
     <row r="209" ht="15" customHeight="1" s="15">
       <c r="A209" s="24" t="inlineStr">
@@ -13324,32 +13061,24 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="D212" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E212" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F212" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G212" s="19" t="n"/>
+      <c r="D212" s="40" t="n"/>
+      <c r="E212" s="40" t="n"/>
+      <c r="F212" s="40" t="n"/>
+      <c r="G212" s="35" t="inlineStr">
+        <is>
+          <t>해당 없음[추정]</t>
+        </is>
+      </c>
       <c r="H212" s="19" t="n"/>
       <c r="I212" s="19" t="n"/>
       <c r="J212" s="19" t="n"/>
       <c r="K212" s="19" t="n"/>
       <c r="L212" s="19" t="n"/>
-      <c r="M212" s="19" t="n"/>
+      <c r="M212" s="38" t="n"/>
       <c r="N212" s="19" t="n"/>
-      <c r="O212" s="23" t="inlineStr">
-        <is>
-          <t>스포티지 1세대 국내 출시(1993) — 초기형은 트랜스폰더 미탑재 추정</t>
+      <c r="O212" s="35" t="inlineStr">
+        <is>
+          <t>초기형 트랜스폰더 미탑재 추정 — 해외 카탈로그는 1996년부터 ID13</t>
         </is>
       </c>
     </row>
@@ -13369,30 +13098,26 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="D213" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E213" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F213" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G213" s="19" t="n"/>
+      <c r="D213" s="40" t="n"/>
+      <c r="E213" s="40" t="n"/>
+      <c r="F213" s="40" t="n"/>
+      <c r="G213" s="35" t="inlineStr">
+        <is>
+          <t>해당 없음[추정]</t>
+        </is>
+      </c>
       <c r="H213" s="19" t="n"/>
       <c r="I213" s="19" t="n"/>
       <c r="J213" s="19" t="n"/>
       <c r="K213" s="19" t="n"/>
       <c r="L213" s="19" t="n"/>
-      <c r="M213" s="19" t="n"/>
+      <c r="M213" s="38" t="n"/>
       <c r="N213" s="19" t="n"/>
-      <c r="O213" s="19" t="n"/>
+      <c r="O213" s="35" t="inlineStr">
+        <is>
+          <t>초기형 트랜스폰더 미탑재 추정 — 해외 카탈로그는 1996년부터 ID13</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="15" customHeight="1" s="15">
       <c r="A214" s="19" t="inlineStr">
@@ -13410,30 +13135,26 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="D214" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E214" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F214" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G214" s="19" t="n"/>
+      <c r="D214" s="40" t="n"/>
+      <c r="E214" s="40" t="n"/>
+      <c r="F214" s="40" t="n"/>
+      <c r="G214" s="35" t="inlineStr">
+        <is>
+          <t>해당 없음[추정]</t>
+        </is>
+      </c>
       <c r="H214" s="19" t="n"/>
       <c r="I214" s="19" t="n"/>
       <c r="J214" s="19" t="n"/>
       <c r="K214" s="19" t="n"/>
       <c r="L214" s="19" t="n"/>
-      <c r="M214" s="19" t="n"/>
+      <c r="M214" s="38" t="n"/>
       <c r="N214" s="19" t="n"/>
-      <c r="O214" s="19" t="n"/>
+      <c r="O214" s="35" t="inlineStr">
+        <is>
+          <t>초기형 트랜스폰더 미탑재 추정 — 해외 카탈로그는 1996년부터 ID13</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1" s="15">
       <c r="A215" s="19" t="inlineStr">
@@ -13466,7 +13187,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G215" s="24" t="inlineStr">
+      <c r="G215" s="34" t="inlineStr">
         <is>
           <t>ID13</t>
         </is>
@@ -13476,11 +13197,11 @@
       <c r="J215" s="19" t="n"/>
       <c r="K215" s="19" t="n"/>
       <c r="L215" s="19" t="n"/>
-      <c r="M215" s="19" t="n"/>
+      <c r="M215" s="38" t="n"/>
       <c r="N215" s="19" t="n"/>
-      <c r="O215" s="19" t="inlineStr">
-        <is>
-          <t>칩: 트랜스폰더 카탈로그(auto-keys.eu·easycarkeys) 'SPORTAGE 1996-1998 Megamos13/ID13, 1999-2001 Megamos48/ID48, 2001-2003 Texas 4D ID60, 2004~ Philips ID46' + 정품 0K2AC-76201A(48 Megamos, Sportage 2002-2004, abkeys). 유럽 기준 카탈로그, 국내 내수형 원문 확인 못함</t>
+      <c r="O215" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13236,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G216" s="24" t="inlineStr">
+      <c r="G216" s="34" t="inlineStr">
         <is>
           <t>ID13</t>
         </is>
@@ -13525,9 +13246,13 @@
       <c r="J216" s="19" t="n"/>
       <c r="K216" s="19" t="n"/>
       <c r="L216" s="19" t="n"/>
-      <c r="M216" s="19" t="n"/>
+      <c r="M216" s="38" t="n"/>
       <c r="N216" s="19" t="n"/>
-      <c r="O216" s="19" t="n"/>
+      <c r="O216" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="15" customHeight="1" s="15">
       <c r="A217" s="19" t="inlineStr">
@@ -13560,7 +13285,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G217" s="24" t="inlineStr">
+      <c r="G217" s="34" t="inlineStr">
         <is>
           <t>ID13</t>
         </is>
@@ -13570,11 +13295,11 @@
       <c r="J217" s="19" t="n"/>
       <c r="K217" s="19" t="n"/>
       <c r="L217" s="19" t="n"/>
-      <c r="M217" s="19" t="n"/>
+      <c r="M217" s="38" t="n"/>
       <c r="N217" s="19" t="n"/>
-      <c r="O217" s="23" t="inlineStr">
-        <is>
-          <t>이모빌라이저 도입 추정 시기(1990년대 후반)</t>
+      <c r="O217" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13334,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G218" s="24" t="inlineStr">
+      <c r="G218" s="34" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -13619,9 +13344,13 @@
       <c r="J218" s="19" t="n"/>
       <c r="K218" s="19" t="n"/>
       <c r="L218" s="19" t="n"/>
-      <c r="M218" s="19" t="n"/>
+      <c r="M218" s="38" t="n"/>
       <c r="N218" s="19" t="n"/>
-      <c r="O218" s="19" t="n"/>
+      <c r="O218" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="15" customHeight="1" s="15">
       <c r="A219" s="19" t="inlineStr">
@@ -13654,7 +13383,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G219" s="24" t="inlineStr">
+      <c r="G219" s="34" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -13664,9 +13393,13 @@
       <c r="J219" s="19" t="n"/>
       <c r="K219" s="19" t="n"/>
       <c r="L219" s="19" t="n"/>
-      <c r="M219" s="19" t="n"/>
+      <c r="M219" s="38" t="n"/>
       <c r="N219" s="19" t="n"/>
-      <c r="O219" s="19" t="n"/>
+      <c r="O219" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1" s="15">
       <c r="A220" s="19" t="inlineStr">
@@ -13699,7 +13432,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G220" s="24" t="inlineStr">
+      <c r="G220" s="34" t="inlineStr">
         <is>
           <t>ID48, ID60(4D60)</t>
         </is>
@@ -13709,9 +13442,13 @@
       <c r="J220" s="19" t="n"/>
       <c r="K220" s="19" t="n"/>
       <c r="L220" s="19" t="n"/>
-      <c r="M220" s="19" t="n"/>
+      <c r="M220" s="38" t="n"/>
       <c r="N220" s="19" t="n"/>
-      <c r="O220" s="19" t="n"/>
+      <c r="O220" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="15" customHeight="1" s="15">
       <c r="A221" s="19" t="inlineStr">
@@ -13744,7 +13481,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G221" s="24" t="inlineStr">
+      <c r="G221" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60), ID48[0K2AC-76201A 키]</t>
         </is>
@@ -13758,11 +13495,11 @@
       <c r="J221" s="19" t="n"/>
       <c r="K221" s="19" t="n"/>
       <c r="L221" s="19" t="n"/>
-      <c r="M221" s="19" t="n"/>
+      <c r="M221" s="38" t="n"/>
       <c r="N221" s="19" t="n"/>
-      <c r="O221" s="24" t="inlineStr">
-        <is>
-          <t>1세대 국내 마지막 연식(2002) — 이후 후속 공백기</t>
+      <c r="O221" s="34" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -13809,11 +13546,7 @@
       <c r="L222" s="19" t="n"/>
       <c r="M222" s="19" t="n"/>
       <c r="N222" s="19" t="n"/>
-      <c r="O222" s="19" t="inlineStr">
-        <is>
-          <t>칩: 트랜스폰더 카탈로그 'SPORTAGE 2004~ Philips Crypto2 ID46', 247geek 'Kia Sportage 25.08.2004-01.11.2012 ID46(PCF7936)'</t>
-        </is>
-      </c>
+      <c r="O222" s="19" t="n"/>
     </row>
     <row r="223" ht="15" customHeight="1" s="15">
       <c r="A223" s="19" t="inlineStr">
@@ -13846,7 +13579,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G223" s="24" t="inlineStr">
+      <c r="G223" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -13856,11 +13589,11 @@
       <c r="J223" s="19" t="n"/>
       <c r="K223" s="19" t="n"/>
       <c r="L223" s="19" t="n"/>
-      <c r="M223" s="19" t="n"/>
+      <c r="M223" s="38" t="n"/>
       <c r="N223" s="19" t="n"/>
-      <c r="O223" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O223" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13628,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G224" s="24" t="inlineStr">
+      <c r="G224" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -13905,11 +13638,11 @@
       <c r="J224" s="19" t="n"/>
       <c r="K224" s="19" t="n"/>
       <c r="L224" s="19" t="n"/>
-      <c r="M224" s="19" t="n"/>
+      <c r="M224" s="38" t="n"/>
       <c r="N224" s="19" t="n"/>
-      <c r="O224" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O224" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -13944,7 +13677,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G225" s="24" t="inlineStr">
+      <c r="G225" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -13954,11 +13687,11 @@
       <c r="J225" s="19" t="n"/>
       <c r="K225" s="19" t="n"/>
       <c r="L225" s="19" t="n"/>
-      <c r="M225" s="19" t="n"/>
+      <c r="M225" s="38" t="n"/>
       <c r="N225" s="19" t="n"/>
-      <c r="O225" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O225" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -13993,7 +13726,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G226" s="24" t="inlineStr">
+      <c r="G226" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -14003,11 +13736,11 @@
       <c r="J226" s="19" t="n"/>
       <c r="K226" s="19" t="n"/>
       <c r="L226" s="19" t="n"/>
-      <c r="M226" s="19" t="n"/>
+      <c r="M226" s="38" t="n"/>
       <c r="N226" s="19" t="n"/>
-      <c r="O226" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O226" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -14042,7 +13775,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G227" s="24" t="inlineStr">
+      <c r="G227" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -14052,11 +13785,11 @@
       <c r="J227" s="19" t="n"/>
       <c r="K227" s="19" t="n"/>
       <c r="L227" s="19" t="n"/>
-      <c r="M227" s="19" t="n"/>
+      <c r="M227" s="38" t="n"/>
       <c r="N227" s="19" t="n"/>
-      <c r="O227" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O227" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -14103,11 +13836,7 @@
       <c r="L228" s="19" t="n"/>
       <c r="M228" s="19" t="n"/>
       <c r="N228" s="19" t="n"/>
-      <c r="O228" s="24" t="inlineStr">
-        <is>
-          <t>SL 완전변경 출시(2010)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O228" s="24" t="n"/>
     </row>
     <row r="229" ht="15" customHeight="1" s="15">
       <c r="A229" s="19" t="inlineStr">
@@ -14168,11 +13897,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O229" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 및 국제 판매처(gskeyae) 확인. transpondery.com 카탈로그 원문 확인: SL세대는 트림별로 DST80/ID6E-MA(플립) 또는 ID46/PCF7952A(스마트) 혼재 — 폴딩키 PN 국내 확인, 이전에 누락됐던 것 추가</t>
-        </is>
-      </c>
+      <c r="O229" s="19" t="n"/>
     </row>
     <row r="230" ht="15" customHeight="1" s="15">
       <c r="A230" s="19" t="inlineStr">
@@ -14233,11 +13958,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O230" s="24" t="inlineStr">
-        <is>
-          <t>transpondery.com 카탈로그 확인</t>
-        </is>
-      </c>
+      <c r="O230" s="24" t="n"/>
     </row>
     <row r="231" ht="15" customHeight="1" s="15">
       <c r="A231" s="19" t="inlineStr">
@@ -14270,7 +13991,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G231" s="24" t="inlineStr">
+      <c r="G231" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)[플립키], ID6E-MA[일부 자료]</t>
         </is>
@@ -14292,15 +14013,15 @@
           <t>954303W200[플립키], 954303W500, 954303W501, 954303W250</t>
         </is>
       </c>
-      <c r="M231" s="19" t="n"/>
+      <c r="M231" s="38" t="n"/>
       <c r="N231" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O231" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2013.6.29~7.2 기준 스마트키·비상키 전환. 더 뉴 스포티지 R 페이스리프트(2013). 국제 판매처(lockdecoders) 확인: 플립키 PN 954303W200, ID46 PCF7936</t>
+      <c r="O231" s="35" t="inlineStr">
+        <is>
+          <t>플립키 ID6E-MA는 일부 자료에만 나옴(국제 판매처는 플립키 95430-3W200 ID46 PCF7936)</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14056,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G232" s="24" t="inlineStr">
+      <c r="G232" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)[플립키], ID6E-MA[일부 자료]</t>
         </is>
@@ -14357,13 +14078,17 @@
           <t>954303W200, 954303W500, 954303W501, 954303W250</t>
         </is>
       </c>
-      <c r="M232" s="19" t="n"/>
+      <c r="M232" s="38" t="n"/>
       <c r="N232" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O232" s="19" t="n"/>
+      <c r="O232" s="35" t="inlineStr">
+        <is>
+          <t>플립키 ID6E-MA는 일부 자료에만 나옴(국제 판매처는 플립키 95430-3W200 ID46 PCF7936)</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="15" customHeight="1" s="15">
       <c r="A233" s="19" t="inlineStr">
@@ -14424,11 +14149,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O233" s="19" t="inlineStr">
-        <is>
-          <t>올 뉴 스포티지(QL) 완전변경 출시(2015)로 전환되는 해 — QL 초기부터 확정 ID47(NCF2971X) 확인됨(americankeysupply)</t>
-        </is>
-      </c>
+      <c r="O233" s="19" t="n"/>
     </row>
     <row r="234" ht="15" customHeight="1" s="15">
       <c r="A234" s="19" t="inlineStr">
@@ -14611,11 +14332,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O236" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2018년 중반 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O236" s="19" t="n"/>
     </row>
     <row r="237" ht="15" customHeight="1" s="15">
       <c r="A237" s="19" t="inlineStr">
@@ -14676,11 +14393,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O237" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문: D9000[2015.8.3~2018.8.7] → D9500[2018.6.26~] → D9600[2019.2.26~], 블랭킹 81996A4040</t>
-        </is>
-      </c>
+      <c r="O237" s="19" t="n"/>
     </row>
     <row r="238" ht="15" customHeight="1" s="15">
       <c r="A238" s="19" t="inlineStr">
@@ -14802,11 +14515,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O239" s="19" t="inlineStr">
-        <is>
-          <t>디 올 뉴 스포티지(NQ5) 완전변경 출시(2021)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O239" s="19" t="n"/>
     </row>
     <row r="240" ht="15" customHeight="1" s="15">
       <c r="A240" s="19" t="inlineStr">
@@ -14871,11 +14580,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O240" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문: 주차보조X P1100→P1110[2023.1.31~], 블랭킹 81999J7020 / 주차보조O P1200→P1210[2023.1.31~], 블랭킹 81996P1060. 이전 블레이드 기재(81926-J7000, 81996-K0000)는 원문과 달라 정정. 칩 ID4A(keyshop-online 등)</t>
-        </is>
-      </c>
+      <c r="O240" s="19" t="n"/>
     </row>
     <row r="241" ht="15" customHeight="1" s="15">
       <c r="A241" s="19" t="inlineStr">
@@ -14940,11 +14645,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O241" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2023.1.31 기준 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O241" s="19" t="n"/>
     </row>
     <row r="242" ht="15" customHeight="1" s="15">
       <c r="A242" s="19" t="inlineStr">
@@ -15009,11 +14710,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O242" s="19" t="inlineStr">
-        <is>
-          <t>더 뉴 스포티지(NQ5 PE) 출시(2024.11.5, 나무위키). 국내 현대모비스(hellowcar): PE 스마트키 P1AB0·P1AC0·P1AE0·P1AF0, 블랭킹 81996S9600(사양별 구분은 원문 미확인)</t>
-        </is>
-      </c>
+      <c r="O242" s="19" t="n"/>
     </row>
     <row r="243" ht="15" customHeight="1" s="15">
       <c r="A243" s="19" t="inlineStr">
@@ -15078,11 +14775,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O243" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2025~2026년에 초기형 PN(P1110·P1210)을 적었으나 2024.11 페이스리프트 이후 PE 부품으로 정정. 폴딩키 P1000의 PE 적용 여부는 원문 미확인</t>
-        </is>
-      </c>
+      <c r="O243" s="19" t="n"/>
     </row>
     <row r="244" ht="15" customHeight="1" s="15">
       <c r="A244" s="19" t="inlineStr">
@@ -15229,7 +14922,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G246" s="24" t="inlineStr">
+      <c r="G246" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -15239,11 +14932,11 @@
       <c r="J246" s="19" t="n"/>
       <c r="K246" s="19" t="n"/>
       <c r="L246" s="19" t="n"/>
-      <c r="M246" s="19" t="n"/>
+      <c r="M246" s="38" t="n"/>
       <c r="N246" s="19" t="n"/>
-      <c r="O246" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O246" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -15278,7 +14971,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G247" s="24" t="inlineStr">
+      <c r="G247" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -15288,11 +14981,11 @@
       <c r="J247" s="19" t="n"/>
       <c r="K247" s="19" t="n"/>
       <c r="L247" s="19" t="n"/>
-      <c r="M247" s="19" t="n"/>
+      <c r="M247" s="38" t="n"/>
       <c r="N247" s="19" t="n"/>
-      <c r="O247" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O247" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15020,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G248" s="24" t="inlineStr">
+      <c r="G248" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -15337,11 +15030,11 @@
       <c r="J248" s="19" t="n"/>
       <c r="K248" s="19" t="n"/>
       <c r="L248" s="19" t="n"/>
-      <c r="M248" s="19" t="n"/>
+      <c r="M248" s="38" t="n"/>
       <c r="N248" s="19" t="n"/>
-      <c r="O248" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O248" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15069,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G249" s="24" t="inlineStr">
+      <c r="G249" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -15386,11 +15079,11 @@
       <c r="J249" s="19" t="n"/>
       <c r="K249" s="19" t="n"/>
       <c r="L249" s="19" t="n"/>
-      <c r="M249" s="19" t="n"/>
+      <c r="M249" s="38" t="n"/>
       <c r="N249" s="19" t="n"/>
-      <c r="O249" s="19" t="inlineStr">
-        <is>
-          <t>페이스리프트 시점(2006.4) 전후로 전자장비 개정 가능성</t>
+      <c r="O249" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15118,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G250" s="24" t="inlineStr">
+      <c r="G250" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -15435,11 +15128,11 @@
       <c r="J250" s="19" t="n"/>
       <c r="K250" s="19" t="n"/>
       <c r="L250" s="19" t="n"/>
-      <c r="M250" s="19" t="n"/>
+      <c r="M250" s="38" t="n"/>
       <c r="N250" s="19" t="n"/>
-      <c r="O250" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O250" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15167,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G251" s="24" t="inlineStr">
+      <c r="G251" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -15484,11 +15177,11 @@
       <c r="J251" s="19" t="n"/>
       <c r="K251" s="19" t="n"/>
       <c r="L251" s="19" t="n"/>
-      <c r="M251" s="19" t="n"/>
+      <c r="M251" s="38" t="n"/>
       <c r="N251" s="19" t="n"/>
-      <c r="O251" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O251" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -15543,11 +15236,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O252" s="19" t="inlineStr">
-        <is>
-          <t>쏘렌토R(XM) 완전변경 출시(2009.5)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O252" s="19" t="n"/>
     </row>
     <row r="253" ht="15" customHeight="1" s="15">
       <c r="A253" s="19" t="inlineStr">
@@ -15608,11 +15297,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O253" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2010.7.1 기준 스마트키 전환. 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
-        </is>
-      </c>
+      <c r="O253" s="19" t="n"/>
     </row>
     <row r="254" ht="15" customHeight="1" s="15">
       <c r="A254" s="19" t="inlineStr">
@@ -15734,11 +15419,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O255" s="19" t="inlineStr">
-        <is>
-          <t>뉴 쏘렌토R(페이스리프트) 출시(2012.7)</t>
-        </is>
-      </c>
+      <c r="O255" s="19" t="n"/>
     </row>
     <row r="256" ht="15" customHeight="1" s="15">
       <c r="A256" s="19" t="inlineStr">
@@ -15799,11 +15480,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O256" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 재확인 — 954402P500용 블레이드는 819962P300(이전 819962J700은 오기)</t>
-        </is>
-      </c>
+      <c r="O256" s="19" t="n"/>
     </row>
     <row r="257" ht="15" customHeight="1" s="15">
       <c r="A257" s="19" t="inlineStr">
@@ -15864,11 +15541,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O257" s="19" t="inlineStr">
-        <is>
-          <t>쏘렌토(UM) 완전변경 출시(2014.8)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O257" s="19" t="n"/>
     </row>
     <row r="258" ht="15" customHeight="1" s="15">
       <c r="A258" s="19" t="inlineStr">
@@ -15925,11 +15598,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O258" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문: 95440C5000[2014.8.16~2017.7.24, 블레이드 81996C5040] → 95440C5500(더뉴쏘렌토)[2017.6.29~, 블레이드 81996C5050]. 칩: C5000·C5500 모두 HITAG3 ID47(한국 시장용 정품 mk3·tlkeys), 4버튼</t>
-        </is>
-      </c>
+      <c r="O258" s="19" t="n"/>
     </row>
     <row r="259" ht="15" customHeight="1" s="15">
       <c r="A259" s="19" t="inlineStr">
@@ -16043,11 +15712,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O260" s="19" t="inlineStr">
-        <is>
-          <t>더 뉴 쏘렌토(UM 페이스리프트) 출시(2017.7)</t>
-        </is>
-      </c>
+      <c r="O260" s="19" t="n"/>
     </row>
     <row r="261" ht="15" customHeight="1" s="15">
       <c r="A261" s="19" t="inlineStr">
@@ -16104,11 +15769,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O261" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 원문: 95440C5500[2017.6.29~] 적용</t>
-        </is>
-      </c>
+      <c r="O261" s="19" t="n"/>
     </row>
     <row r="262" ht="15" customHeight="1" s="15">
       <c r="A262" s="19" t="inlineStr">
@@ -16222,11 +15883,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O263" s="19" t="inlineStr">
-        <is>
-          <t>쏘렌토(MQ4) 완전변경 출시(2020.3)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O263" s="19" t="n"/>
     </row>
     <row r="264" ht="15" customHeight="1" s="15">
       <c r="A264" s="19" t="inlineStr">
@@ -16409,11 +16066,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O266" s="24" t="inlineStr">
-        <is>
-          <t>2023.8 페이스리프트('더 뉴 쏘렌토')로 전환되는 해 — 하이브리드 공용 신형 스마트키(95440-P2AD0) 등장</t>
-        </is>
-      </c>
+      <c r="O266" s="24" t="n"/>
     </row>
     <row r="267" ht="15" customHeight="1" s="15">
       <c r="A267" s="19" t="inlineStr">
@@ -16474,11 +16127,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O267" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar): 더 뉴 쏘렌토(MQ4 PE) 스마트키 P2AA0·P2AB0·P2AC0·P2AD0 4종 확인(사양별 구분은 원문 미확인). 카폼: P2AD0 적용 '더 뉴 쏘렌토 2023.8 이후'(종료일 없음). 칩 ID4A</t>
-        </is>
-      </c>
+      <c r="O267" s="19" t="n"/>
     </row>
     <row r="268" ht="15" customHeight="1" s="15">
       <c r="A268" s="19" t="inlineStr">
@@ -16657,11 +16306,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O270" s="19" t="inlineStr">
-        <is>
-          <t>모하비 국내 출시(2008.1). 국내 현대모비스(hellowcar) 원문: 2J800[~2010.12.13] → 2J860[2010.12.13~2011.6.1] → 2J870[2011.6.1~2015.12.23] (블레이드 819962J700) / 1W000[2016.1.15~2019.6.13, 819962J700] / 2J200(더뉴 모하비)[2016.11.15~2019.6.13, 819962J800]</t>
-        </is>
-      </c>
+      <c r="O270" s="19" t="n"/>
     </row>
     <row r="271" ht="15" customHeight="1" s="15">
       <c r="A271" s="19" t="inlineStr">
@@ -16775,11 +16420,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O272" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2010.12.13 기준 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O272" s="19" t="n"/>
     </row>
     <row r="273" ht="15" customHeight="1" s="15">
       <c r="A273" s="19" t="inlineStr">
@@ -16836,11 +16477,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O273" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2011.6.1 기준 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O273" s="19" t="n"/>
     </row>
     <row r="274" ht="15" customHeight="1" s="15">
       <c r="A274" s="19" t="inlineStr">
@@ -16897,11 +16534,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O274" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2012~2013년에 1W000·2J200을 함께 적었으나 원문상 둘 다 2016년부터라 정정</t>
-        </is>
-      </c>
+      <c r="O274" s="19" t="n"/>
     </row>
     <row r="275" ht="15" customHeight="1" s="15">
       <c r="A275" s="19" t="inlineStr">
@@ -17015,11 +16648,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O276" s="19" t="inlineStr">
-        <is>
-          <t>모하비 더 마스터(1차 페이스리프트) 출시(2014.5)</t>
-        </is>
-      </c>
+      <c r="O276" s="19" t="n"/>
     </row>
     <row r="277" ht="15" customHeight="1" s="15">
       <c r="A277" s="19" t="inlineStr">
@@ -17247,11 +16876,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O280" s="19" t="inlineStr">
-        <is>
-          <t>모하비 더 마스터(2차 완전변경급 페이스리프트) 출시(2019)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O280" s="19" t="n"/>
     </row>
     <row r="281" ht="15" customHeight="1" s="15">
       <c r="A281" s="19" t="inlineStr">
@@ -17308,11 +16933,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O281" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처(abkeys.com) 확인 — 더마스터부터 ID46에서 ID47로 칩 세대 전환. 초기형(2008-2018)은 abkeys 확인 PCF7952A ID46</t>
-        </is>
-      </c>
+      <c r="O281" s="19" t="n"/>
     </row>
     <row r="282" ht="15" customHeight="1" s="15">
       <c r="A282" s="19" t="inlineStr">
@@ -17426,11 +17047,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O283" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2021.6.8 기준 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O283" s="19" t="n"/>
     </row>
     <row r="284" ht="15" customHeight="1" s="15">
       <c r="A284" s="19" t="inlineStr">
@@ -17658,11 +17275,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O287" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 원문: 모하비 더마스터[2019.8.22~] 2J500[~2021.6.8] → 2J550·2JAA0[2021.6.8~, 종료일 없음], 블랭킹 819962J900</t>
-        </is>
-      </c>
+      <c r="O287" s="19" t="n"/>
     </row>
     <row r="288" ht="15" customHeight="1" s="15">
       <c r="A288" s="19" t="inlineStr">
@@ -17719,11 +17332,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O288" s="19" t="inlineStr">
-        <is>
-          <t>니로(DE) 국내 출시(2016.3.7, 95440-G5000 출시일과 일치). 칩: 같은 PN(95440-G5000) 정품 Hitag3 ID47 확인. 국내 현대모비스(hellowcar) 원문: G5000[~2019.2.28, 블랭킹 81996G5A20] → G5010[2019.2.28~] · G5025[22년형] · DB000[니로 플러스], 이후 블랭킹 81999J7020</t>
-        </is>
-      </c>
+      <c r="O288" s="19" t="n"/>
     </row>
     <row r="289" ht="15" customHeight="1" s="15">
       <c r="A289" s="19" t="inlineStr">
@@ -17784,11 +17393,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O289" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처(keyshop-online, dfwkeys4cars) 확인 — Hitag3 ID47</t>
-        </is>
-      </c>
+      <c r="O289" s="19" t="n"/>
     </row>
     <row r="290" ht="15" customHeight="1" s="15">
       <c r="A290" s="19" t="inlineStr">
@@ -17849,11 +17454,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O290" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2018년에 G5010을 함께 적었으나 원문상 G5010은 2019.2.28부터라 정정</t>
-        </is>
-      </c>
+      <c r="O290" s="19" t="n"/>
     </row>
     <row r="291" ht="15" customHeight="1" s="15">
       <c r="A291" s="19" t="inlineStr">
@@ -17914,11 +17515,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O291" s="19" t="inlineStr">
-        <is>
-          <t>니로 플러스(택시형) 출시 — 별도 스마트키 PN(95440-DB000)</t>
-        </is>
-      </c>
+      <c r="O291" s="19" t="n"/>
     </row>
     <row r="292" ht="15" customHeight="1" s="15">
       <c r="A292" s="19" t="inlineStr">
@@ -17979,11 +17576,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O292" s="19" t="inlineStr">
-        <is>
-          <t>니로(DE) 페이스리프트(2019.7)</t>
-        </is>
-      </c>
+      <c r="O292" s="19" t="n"/>
     </row>
     <row r="293" ht="15" customHeight="1" s="15">
       <c r="A293" s="19" t="inlineStr">
@@ -18101,11 +17694,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O294" s="19" t="inlineStr">
-        <is>
-          <t>디 올 뉴 니로(SG2) 완전변경 출시(2022.1)로 전환되는 해 — 이때 칩이 ID47(Hitag3)에서 ID4A(Hitag AES)로 세대 전환. 디지털키2 터치 옵션 최초 도입</t>
-        </is>
-      </c>
+      <c r="O294" s="19" t="n"/>
     </row>
     <row r="295" ht="15" customHeight="1" s="15">
       <c r="A295" s="19" t="inlineStr">
@@ -18162,11 +17751,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O295" s="19" t="inlineStr">
-        <is>
-          <t>블레이드 매칭: 원문 옵션 순서(주차보조X→81999J7020, 주차보조O→81996P1060), 셀토스·스포티지 NQ5 원문과 동일 구성</t>
-        </is>
-      </c>
+      <c r="O295" s="19" t="n"/>
     </row>
     <row r="296" ht="15" customHeight="1" s="15">
       <c r="A296" s="19" t="inlineStr">
@@ -18223,11 +17808,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O296" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 확인 — 2024.2.7 기준 부품번호 전환</t>
-        </is>
-      </c>
+      <c r="O296" s="19" t="n"/>
     </row>
     <row r="297" ht="15" customHeight="1" s="15">
       <c r="A297" s="19" t="inlineStr">
@@ -18317,7 +17898,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G298" s="24" t="inlineStr">
+      <c r="G298" s="34" t="inlineStr">
         <is>
           <t>ID4A(NCF29A1M)[초기형]</t>
         </is>
@@ -18335,15 +17916,15 @@
         </is>
       </c>
       <c r="L298" s="19" t="n"/>
-      <c r="M298" s="19" t="n"/>
+      <c r="M298" s="38" t="n"/>
       <c r="N298" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O298" s="24" t="inlineStr">
-        <is>
-          <t>'더 뉴 니로'(SG2 PE) 2026.1.20 공개, 3.10 계약 시작(나무위키). PE 전용 스마트키·블레이드 부품번호와 칩은 국내 원문에서 아직 확인 못해 초기형 정보만 기재</t>
+      <c r="O298" s="34" t="inlineStr">
+        <is>
+          <t>더 뉴 니로(SG2 PE, 2026.3) 스마트키 품번·칩 원문 없음 — 초기형 기준</t>
         </is>
       </c>
     </row>
@@ -18390,11 +17971,7 @@
       <c r="L299" s="19" t="n"/>
       <c r="M299" s="19" t="n"/>
       <c r="N299" s="19" t="n"/>
-      <c r="O299" s="19" t="inlineStr">
-        <is>
-          <t>카렌스(RS) 국내 출시(1999)</t>
-        </is>
-      </c>
+      <c r="O299" s="19" t="n"/>
     </row>
     <row r="300" ht="15" customHeight="1" s="15">
       <c r="A300" s="19" t="inlineStr">
@@ -18427,7 +18004,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G300" s="24" t="inlineStr">
+      <c r="G300" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)</t>
         </is>
@@ -18437,11 +18014,11 @@
       <c r="J300" s="19" t="n"/>
       <c r="K300" s="19" t="n"/>
       <c r="L300" s="19" t="n"/>
-      <c r="M300" s="19" t="n"/>
+      <c r="M300" s="38" t="n"/>
       <c r="N300" s="19" t="n"/>
-      <c r="O300" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O300" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -18476,7 +18053,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G301" s="24" t="inlineStr">
+      <c r="G301" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)</t>
         </is>
@@ -18486,11 +18063,11 @@
       <c r="J301" s="19" t="n"/>
       <c r="K301" s="19" t="n"/>
       <c r="L301" s="19" t="n"/>
-      <c r="M301" s="19" t="n"/>
+      <c r="M301" s="38" t="n"/>
       <c r="N301" s="19" t="n"/>
-      <c r="O301" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O301" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -18537,11 +18114,7 @@
       <c r="L302" s="19" t="n"/>
       <c r="M302" s="19" t="n"/>
       <c r="N302" s="19" t="n"/>
-      <c r="O302" s="19" t="inlineStr">
-        <is>
-          <t>카렌스2/엑스트렉 페이스리프트(2002)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O302" s="19" t="n"/>
     </row>
     <row r="303" ht="15" customHeight="1" s="15">
       <c r="A303" s="19" t="inlineStr">
@@ -18574,7 +18147,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G303" s="24" t="inlineStr">
+      <c r="G303" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18584,11 +18157,11 @@
       <c r="J303" s="19" t="n"/>
       <c r="K303" s="19" t="n"/>
       <c r="L303" s="19" t="n"/>
-      <c r="M303" s="19" t="n"/>
+      <c r="M303" s="38" t="n"/>
       <c r="N303" s="19" t="n"/>
-      <c r="O303" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O303" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -18623,7 +18196,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G304" s="24" t="inlineStr">
+      <c r="G304" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18633,11 +18206,11 @@
       <c r="J304" s="19" t="n"/>
       <c r="K304" s="19" t="n"/>
       <c r="L304" s="19" t="n"/>
-      <c r="M304" s="19" t="n"/>
+      <c r="M304" s="38" t="n"/>
       <c r="N304" s="19" t="n"/>
-      <c r="O304" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O304" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -18672,7 +18245,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G305" s="24" t="inlineStr">
+      <c r="G305" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18682,11 +18255,11 @@
       <c r="J305" s="19" t="n"/>
       <c r="K305" s="19" t="n"/>
       <c r="L305" s="19" t="n"/>
-      <c r="M305" s="19" t="n"/>
+      <c r="M305" s="38" t="n"/>
       <c r="N305" s="19" t="n"/>
-      <c r="O305" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O305" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -18735,7 +18308,7 @@
           <t>954301D100[UN]</t>
         </is>
       </c>
-      <c r="M306" s="35" t="n"/>
+      <c r="M306" s="38" t="n"/>
       <c r="N306" s="19" t="n"/>
       <c r="O306" s="35" t="inlineStr">
         <is>
@@ -18790,11 +18363,7 @@
       </c>
       <c r="M307" s="19" t="n"/>
       <c r="N307" s="19" t="n"/>
-      <c r="O307" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar) 폴딩키 원문: D101[2007.7.2~2008.5.27] → D102[2008.5.27~2010.6.16] → D103[2010.6.1~2012.7.17] → D104[2012.7.1~2012.7.17, 블랭킹 819962L001] / RP 95430A4000[2013.2.28~2016.6.30]. D100은 부품만 확인되고 날짜 옵션이 원문에 없음</t>
-        </is>
-      </c>
+      <c r="O307" s="19" t="n"/>
     </row>
     <row r="308" ht="15" customHeight="1" s="15">
       <c r="A308" s="19" t="inlineStr">
@@ -18827,7 +18396,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G308" s="24" t="inlineStr">
+      <c r="G308" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18841,11 +18410,11 @@
           <t>954301D101[~5.27], 954301D102[5.27~]</t>
         </is>
       </c>
-      <c r="M308" s="19" t="n"/>
+      <c r="M308" s="38" t="n"/>
       <c r="N308" s="19" t="n"/>
-      <c r="O308" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O308" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -18880,7 +18449,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G309" s="24" t="inlineStr">
+      <c r="G309" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18894,11 +18463,11 @@
           <t>954301D102</t>
         </is>
       </c>
-      <c r="M309" s="19" t="n"/>
+      <c r="M309" s="38" t="n"/>
       <c r="N309" s="19" t="n"/>
-      <c r="O309" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O309" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -18933,7 +18502,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G310" s="24" t="inlineStr">
+      <c r="G310" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18951,11 +18520,11 @@
           <t>954301D102[~6.16], 954301D103[6.1~]</t>
         </is>
       </c>
-      <c r="M310" s="19" t="n"/>
+      <c r="M310" s="38" t="n"/>
       <c r="N310" s="19" t="n"/>
-      <c r="O310" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O310" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -18990,7 +18559,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G311" s="24" t="inlineStr">
+      <c r="G311" s="34" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -19008,11 +18577,11 @@
           <t>954301D103</t>
         </is>
       </c>
-      <c r="M311" s="19" t="n"/>
+      <c r="M311" s="38" t="n"/>
       <c r="N311" s="19" t="n"/>
-      <c r="O311" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O311" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
         </is>
       </c>
     </row>
@@ -19065,7 +18634,7 @@
           <t>954301D103[~7.17], 954301D104[7.1~7.17]</t>
         </is>
       </c>
-      <c r="M312" s="35" t="n"/>
+      <c r="M312" s="38" t="n"/>
       <c r="N312" s="19" t="n"/>
       <c r="O312" s="34" t="inlineStr">
         <is>
@@ -19132,11 +18701,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O313" s="19" t="inlineStr">
-        <is>
-          <t>올 뉴 카렌스(RP) 완전변경 출시(2013.3.29). transpondery.com 카탈로그 원문 확인: RP세대는 트림별로 DST80/ID6E-MA(플립) 또는 ID46/PCF7952A(스마트) 혼재 - 이전에 스마트키만 쓰고 플립키 트림을 빠뜨렸던 것 정정</t>
-        </is>
-      </c>
+      <c r="O313" s="19" t="n"/>
     </row>
     <row r="314" ht="15" customHeight="1" s="15">
       <c r="A314" s="19" t="inlineStr">
@@ -19319,11 +18884,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O316" s="19" t="inlineStr">
-        <is>
-          <t>더 뉴 카렌스(RP 페이스리프트) 출시(2016.7)</t>
-        </is>
-      </c>
+      <c r="O316" s="19" t="n"/>
     </row>
     <row r="317" ht="15" customHeight="1" s="15">
       <c r="A317" s="19" t="inlineStr">
@@ -19380,11 +18941,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O317" s="19" t="inlineStr">
-        <is>
-          <t>폴딩키 95430A4000은 원문상 2016.6.30까지 — 더 뉴 카렌스(2016.7~) 폴딩키 품번은 원문에서 확인 못해 공란</t>
-        </is>
-      </c>
+      <c r="O317" s="19" t="n"/>
     </row>
     <row r="318" ht="15" customHeight="1" s="15">
       <c r="A318" s="19" t="inlineStr">
@@ -19441,11 +18998,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O318" s="19" t="inlineStr">
-        <is>
-          <t>카렌스 국내 최종 연식 — 2018년 10월 공식 단종. 4세대(KY, 2022+ 해외)는 인도 등 전략시장 전용, 국내 미판매, 국내 후속 없음(나무위키 확인)</t>
-        </is>
-      </c>
+      <c r="O318" s="19" t="n"/>
     </row>
     <row r="319" ht="15" customHeight="1" s="15">
       <c r="A319" s="19" t="inlineStr">
@@ -19478,7 +19031,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G319" s="24" t="inlineStr">
+      <c r="G319" s="34" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -19488,11 +19041,11 @@
       <c r="J319" s="19" t="n"/>
       <c r="K319" s="19" t="n"/>
       <c r="L319" s="19" t="n"/>
-      <c r="M319" s="19" t="n"/>
+      <c r="M319" s="38" t="n"/>
       <c r="N319" s="19" t="n"/>
-      <c r="O319" s="19" t="inlineStr">
-        <is>
-          <t>카니발 국내 출시(1998.1.12). 칩: transpondery.com 카탈로그 'KIA CARNIVAL 1998-2001 Megamos 48/ID48, 2000-2002 Texas 4D ID60, 2002-2013 Philips ID46' + car-keys-online(0K54A-76201A, ID46 PCF7936, Carnival 2001.6.11~2005.11.1). 유럽 기준 카탈로그라 국내 내수형 원문 확인은 못함</t>
+      <c r="O319" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19080,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G320" s="24" t="inlineStr">
+      <c r="G320" s="34" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -19537,11 +19090,11 @@
       <c r="J320" s="19" t="n"/>
       <c r="K320" s="19" t="n"/>
       <c r="L320" s="19" t="n"/>
-      <c r="M320" s="19" t="n"/>
+      <c r="M320" s="38" t="n"/>
       <c r="N320" s="19" t="n"/>
-      <c r="O320" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O320" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19129,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G321" s="24" t="inlineStr">
+      <c r="G321" s="34" t="inlineStr">
         <is>
           <t>ID48, ID60(4D60)</t>
         </is>
@@ -19586,11 +19139,11 @@
       <c r="J321" s="19" t="n"/>
       <c r="K321" s="19" t="n"/>
       <c r="L321" s="19" t="n"/>
-      <c r="M321" s="19" t="n"/>
+      <c r="M321" s="38" t="n"/>
       <c r="N321" s="19" t="n"/>
-      <c r="O321" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O321" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -19625,7 +19178,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G322" s="24" t="inlineStr">
+      <c r="G322" s="34" t="inlineStr">
         <is>
           <t>ID48, ID60(4D60), ID46(PCF7936)[2001.6.11~]</t>
         </is>
@@ -19635,11 +19188,11 @@
       <c r="J322" s="19" t="n"/>
       <c r="K322" s="19" t="n"/>
       <c r="L322" s="19" t="n"/>
-      <c r="M322" s="19" t="n"/>
+      <c r="M322" s="38" t="n"/>
       <c r="N322" s="19" t="n"/>
-      <c r="O322" s="19" t="inlineStr">
-        <is>
-          <t>카니발2/GQ 페이스리프트(2001)로 전환되는 해</t>
+      <c r="O322" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19227,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G323" s="24" t="inlineStr">
+      <c r="G323" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -19684,11 +19237,11 @@
       <c r="J323" s="19" t="n"/>
       <c r="K323" s="19" t="n"/>
       <c r="L323" s="19" t="n"/>
-      <c r="M323" s="19" t="n"/>
+      <c r="M323" s="38" t="n"/>
       <c r="N323" s="19" t="n"/>
-      <c r="O323" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O323" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -19723,7 +19276,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G324" s="24" t="inlineStr">
+      <c r="G324" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -19733,11 +19286,11 @@
       <c r="J324" s="19" t="n"/>
       <c r="K324" s="19" t="n"/>
       <c r="L324" s="19" t="n"/>
-      <c r="M324" s="19" t="n"/>
+      <c r="M324" s="38" t="n"/>
       <c r="N324" s="19" t="n"/>
-      <c r="O324" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O324" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -19772,7 +19325,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G325" s="24" t="inlineStr">
+      <c r="G325" s="34" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -19782,11 +19335,11 @@
       <c r="J325" s="19" t="n"/>
       <c r="K325" s="19" t="n"/>
       <c r="L325" s="19" t="n"/>
-      <c r="M325" s="19" t="n"/>
+      <c r="M325" s="38" t="n"/>
       <c r="N325" s="19" t="n"/>
-      <c r="O325" s="19" t="inlineStr">
-        <is>
-          <t>국내 부품번호 확인 필요</t>
+      <c r="O325" s="35" t="inlineStr">
+        <is>
+          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준(유럽 기준)</t>
         </is>
       </c>
     </row>
@@ -19833,11 +19386,7 @@
       <c r="L326" s="19" t="n"/>
       <c r="M326" s="19" t="n"/>
       <c r="N326" s="19" t="n"/>
-      <c r="O326" s="19" t="inlineStr">
-        <is>
-          <t>그랜드카니발(VQ) 완전변경 출시(2005.7)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O326" s="19" t="n"/>
     </row>
     <row r="327" ht="15" customHeight="1" s="15">
       <c r="A327" s="19" t="inlineStr">
@@ -19894,11 +19443,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O327" s="19" t="inlineStr">
-        <is>
-          <t>그랜드카니발(VQ). 칩·블레이드: 정품 81996-4D040 PCF7936 ID46(abkeys), 'Sedona 2006-2012 ID46 81996-4D040'(locksmithkeyless). 폴딩키: 2008.6.2 기준 001/011/021 → 002/012/022 계열 전환, 끝자리는 버튼 수(3/5/6버튼) 구분(hellowcar)</t>
-        </is>
-      </c>
+      <c r="O327" s="19" t="n"/>
     </row>
     <row r="328" ht="15" customHeight="1" s="15">
       <c r="A328" s="19" t="inlineStr">
@@ -20126,11 +19671,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O331" s="19" t="inlineStr">
-        <is>
-          <t>타이거노즈 그릴 적용 페이스리프트(2010)</t>
-        </is>
-      </c>
+      <c r="O331" s="19" t="n"/>
     </row>
     <row r="332" ht="15" customHeight="1" s="15">
       <c r="A332" s="19" t="inlineStr">
@@ -20362,11 +19903,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O335" s="19" t="inlineStr">
-        <is>
-          <t>올 뉴 카니발(YP) 출시(2014.6). 국내 현대모비스(hellowcar) 원문: YP 스마트키 A9300(6버튼, 전동도어O)·A9100(4버튼, 전동도어X)[2014.5.26~], 블랭킹 81996A4040 — 이전 기재 95440-A9200은 국내 원문에 없는 번호라 삭제</t>
-        </is>
-      </c>
+      <c r="O335" s="19" t="n"/>
     </row>
     <row r="336" ht="15" customHeight="1" s="15">
       <c r="A336" s="19" t="inlineStr">
@@ -20427,11 +19964,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O336" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처(abkeys.com) 확인 — Hitag3 ID47</t>
-        </is>
-      </c>
+      <c r="O336" s="19" t="n"/>
     </row>
     <row r="337" ht="15" customHeight="1" s="15">
       <c r="A337" s="19" t="inlineStr">
@@ -20614,11 +20147,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O339" s="19" t="inlineStr">
-        <is>
-          <t>더 뉴 카니발(YP PE 페이스리프트) 출시(2018.3.13)</t>
-        </is>
-      </c>
+      <c r="O339" s="19" t="n"/>
     </row>
     <row r="340" ht="15" customHeight="1" s="15">
       <c r="A340" s="19" t="inlineStr">
@@ -20736,11 +20265,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O341" s="19" t="inlineStr">
-        <is>
-          <t>카니발(KA4) 출시(2020.8). 국내 현대모비스(hellowcar) 원문: 슬라이딩도어자동X는 P2000[~2020.7.20]→R0000[2020.7.20~]→R0430(22년형), 블랭킹 81996P2700 / 자동O는 R0100→R0420(22년형), 블랭킹 81996R0710 / 주차보조버튼O는 R0510</t>
-        </is>
-      </c>
+      <c r="O341" s="19" t="n"/>
     </row>
     <row r="342" ht="15" customHeight="1" s="15">
       <c r="A342" s="19" t="inlineStr">
@@ -20862,11 +20387,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O343" s="19" t="inlineStr">
-        <is>
-          <t>국제 판매처(Amazon/KEYECU) 확인 — '4A Chip' 명시</t>
-        </is>
-      </c>
+      <c r="O343" s="19" t="n"/>
     </row>
     <row r="344" ht="15" customHeight="1" s="15">
       <c r="A344" s="19" t="inlineStr">
@@ -20927,11 +20448,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O344" s="24" t="inlineStr">
-        <is>
-          <t>'더 뉴 카니발'(KA4 PE 페이스리프트) 출시(2023.10)로 전환되는 해</t>
-        </is>
-      </c>
+      <c r="O344" s="24" t="n"/>
     </row>
     <row r="345" ht="15" customHeight="1" s="15">
       <c r="A345" s="19" t="inlineStr">
@@ -20992,11 +20509,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O345" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar): 더 뉴 카니발(KA4 PE) 스마트키 R0800·R0810·R0820·R0840·R0850·R0AA0·R0AB0·R0AE0·R0AF0, 블랭킹 81996P2800(케이스 81995P2000). 사양별 구분은 원문 미확인. 이전 기재 R0870은 국내 원문에 없어 삭제, 블레이드도 P2700/R0710 → P2800으로 정정</t>
-        </is>
-      </c>
+      <c r="O345" s="19" t="n"/>
     </row>
     <row r="346" ht="15" customHeight="1" s="15">
       <c r="A346" s="19" t="inlineStr">
@@ -21136,32 +20649,24 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D348" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E348" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F348" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G348" s="19" t="n"/>
+      <c r="D348" s="40" t="n"/>
+      <c r="E348" s="40" t="n"/>
+      <c r="F348" s="40" t="n"/>
+      <c r="G348" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H348" s="19" t="n"/>
       <c r="I348" s="19" t="n"/>
       <c r="J348" s="19" t="n"/>
       <c r="K348" s="19" t="n"/>
       <c r="L348" s="19" t="n"/>
-      <c r="M348" s="19" t="n"/>
+      <c r="M348" s="47" t="n"/>
       <c r="N348" s="19" t="n"/>
-      <c r="O348" s="19" t="inlineStr">
-        <is>
-          <t>봉고3(J) 출시 이전 구형 모델 — 국내 부품번호 확인 필요</t>
+      <c r="O348" s="41" t="inlineStr">
+        <is>
+          <t>칩 종류를 확인할 국내외 자료 없음</t>
         </is>
       </c>
     </row>
@@ -21226,32 +20731,24 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="D350" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E350" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F350" s="21" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G350" s="19" t="n"/>
+      <c r="D350" s="40" t="n"/>
+      <c r="E350" s="40" t="n"/>
+      <c r="F350" s="40" t="n"/>
+      <c r="G350" s="41" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
+        </is>
+      </c>
       <c r="H350" s="19" t="n"/>
       <c r="I350" s="19" t="n"/>
       <c r="J350" s="19" t="n"/>
       <c r="K350" s="19" t="n"/>
       <c r="L350" s="19" t="n"/>
-      <c r="M350" s="19" t="n"/>
+      <c r="M350" s="47" t="n"/>
       <c r="N350" s="19" t="n"/>
-      <c r="O350" s="19" t="inlineStr">
-        <is>
-          <t>봉고3 출시(2003)로 전환되는 해</t>
+      <c r="O350" s="41" t="inlineStr">
+        <is>
+          <t>칩 종류를 확인할 국내외 자료 없음</t>
         </is>
       </c>
     </row>
@@ -21286,7 +20783,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G351" s="28" t="inlineStr">
+      <c r="G351" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21304,7 +20801,7 @@
           <t>954304E000[A타입 리모콘]</t>
         </is>
       </c>
-      <c r="M351" s="28" t="inlineStr">
+      <c r="M351" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21314,9 +20811,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O351" s="19" t="inlineStr">
-        <is>
-          <t>카키넘버원(국내 키 도매) 확인: 81996-4E000 일반키[2004.9.1~2016.8.31], 81996-4E010 이모빌라이저키(4D 칩), 81996-4E020 이모빌라이저키(46 칩), 81996-4E031 폴딩키 블레이드[2013.1.17~2016.8.31], 81996-4F700 폴딩키 블레이드[2016.8.31~]. 이모빌라이저키 4종의 연식 구간은 원문에 없어 차대번호로 확인 필요 — 이전에 연식별로 나눠 적었던 막대키 PN은 근거 없는 배분이라 삭제하고 전 구간 공통 후보로 정리. MK3 릴리즈노트: 봉고3 ID46/BOSCH 95P08</t>
+      <c r="O351" s="35" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21351,7 +20848,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G352" s="28" t="inlineStr">
+      <c r="G352" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21369,7 +20866,7 @@
           <t>954304E000[A타입 리모콘]</t>
         </is>
       </c>
-      <c r="M352" s="28" t="inlineStr">
+      <c r="M352" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력], 이모빌라이저 유니트(954004E100)[2004년식, 특장]</t>
         </is>
@@ -21379,9 +20876,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O352" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O352" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21416,7 +20913,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G353" s="28" t="inlineStr">
+      <c r="G353" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21434,7 +20931,7 @@
           <t>954304E000[A타입 리모콘]</t>
         </is>
       </c>
-      <c r="M353" s="28" t="inlineStr">
+      <c r="M353" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21444,9 +20941,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O353" s="19" t="inlineStr">
-        <is>
-          <t>이모빌라이저: MK3 릴리즈노트는 봉고3를 ID46·BOSCH 95P08로 분류하나, 국내 정비 자료에 봉고3 133마력 델파이 ECU(39111-4A520)와 델파이형 CRDi 인젝터가 확인됨 → 엔진/ECU 사양에 따라 4D·46 키가 나뉘는 것으로 보이나 연식·사양 매칭 원문은 없음</t>
+      <c r="O353" s="35" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21481,7 +20978,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G354" s="28" t="inlineStr">
+      <c r="G354" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21499,7 +20996,7 @@
           <t>954304E000[A타입 리모콘]</t>
         </is>
       </c>
-      <c r="M354" s="28" t="inlineStr">
+      <c r="M354" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21509,9 +21006,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O354" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O354" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21043,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G355" s="28" t="inlineStr">
+      <c r="G355" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21564,7 +21061,7 @@
           <t>954304E000[A타입 리모콘]</t>
         </is>
       </c>
-      <c r="M355" s="28" t="inlineStr">
+      <c r="M355" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21574,9 +21071,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O355" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O355" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21611,7 +21108,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G356" s="28" t="inlineStr">
+      <c r="G356" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21629,7 +21126,7 @@
           <t>954304E000[~3.1], 954304E100[3.1~], 954304E001[8.1~, A타입 리모콘]</t>
         </is>
       </c>
-      <c r="M356" s="28" t="inlineStr">
+      <c r="M356" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21639,9 +21136,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O356" s="19" t="inlineStr">
-        <is>
-          <t>페이스리프트(2008) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O356" s="35" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21676,7 +21173,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G357" s="28" t="inlineStr">
+      <c r="G357" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21694,7 +21191,7 @@
           <t>954304E100[A타입 리모콘], 954304E001[A타입 리모콘], 954314E000[B타입 폴딩]</t>
         </is>
       </c>
-      <c r="M357" s="28" t="inlineStr">
+      <c r="M357" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21704,9 +21201,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O357" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O357" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21741,7 +21238,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G358" s="28" t="inlineStr">
+      <c r="G358" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21759,7 +21256,7 @@
           <t>954304E100[A타입 리모콘], 954304E001[A타입 리모콘], 954314E000[B타입 폴딩]</t>
         </is>
       </c>
-      <c r="M358" s="28" t="inlineStr">
+      <c r="M358" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21769,9 +21266,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O358" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O358" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21806,7 +21303,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G359" s="28" t="inlineStr">
+      <c r="G359" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21824,7 +21321,7 @@
           <t>954304E100[A타입 리모콘], 954304E001[A타입 리모콘], 954314E000[B타입 폴딩]</t>
         </is>
       </c>
-      <c r="M359" s="28" t="inlineStr">
+      <c r="M359" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21834,9 +21331,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O359" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O359" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21368,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G360" s="28" t="inlineStr">
+      <c r="G360" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21889,7 +21386,7 @@
           <t>954304E100[A타입 리모콘], 954304E001[A타입 리모콘], 954314E000[B타입 폴딩]</t>
         </is>
       </c>
-      <c r="M360" s="28" t="inlineStr">
+      <c r="M360" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21899,9 +21396,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O360" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2012~2015년 폴딩키를 954304E500으로 적었으나 원문상 E500(C타입)은 2016.8.31부터라 정정</t>
+      <c r="O360" s="35" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21433,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G361" s="28" t="inlineStr">
+      <c r="G361" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -21954,7 +21451,7 @@
           <t>954314E000[~1.17], 954314E001[1.17~, B타입 폴딩]</t>
         </is>
       </c>
-      <c r="M361" s="28" t="inlineStr">
+      <c r="M361" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -21964,9 +21461,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O361" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O361" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22001,7 +21498,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G362" s="28" t="inlineStr">
+      <c r="G362" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22019,7 +21516,7 @@
           <t>954314E001[B타입 폴딩]</t>
         </is>
       </c>
-      <c r="M362" s="28" t="inlineStr">
+      <c r="M362" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22029,9 +21526,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O362" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O362" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22066,7 +21563,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G363" s="28" t="inlineStr">
+      <c r="G363" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22084,7 +21581,7 @@
           <t>954314E001[B타입 폴딩]</t>
         </is>
       </c>
-      <c r="M363" s="28" t="inlineStr">
+      <c r="M363" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22094,9 +21591,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O363" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O363" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22131,7 +21628,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G364" s="28" t="inlineStr">
+      <c r="G364" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22149,7 +21646,7 @@
           <t>954314E001[B타입], 954304E500[C타입 폴딩, 8.31~]</t>
         </is>
       </c>
-      <c r="M364" s="28" t="inlineStr">
+      <c r="M364" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22159,9 +21656,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O364" s="24" t="inlineStr">
-        <is>
-          <t>3차 페이스리프트(2016) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O364" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22196,7 +21693,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G365" s="28" t="inlineStr">
+      <c r="G365" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22214,7 +21711,7 @@
           <t>954304E500[C타입 폴딩]</t>
         </is>
       </c>
-      <c r="M365" s="28" t="inlineStr">
+      <c r="M365" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22224,9 +21721,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O365" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O365" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22261,7 +21758,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G366" s="28" t="inlineStr">
+      <c r="G366" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22279,7 +21776,7 @@
           <t>954304E500[C타입 폴딩]</t>
         </is>
       </c>
-      <c r="M366" s="28" t="inlineStr">
+      <c r="M366" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22289,9 +21786,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O366" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O366" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22326,7 +21823,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G367" s="28" t="inlineStr">
+      <c r="G367" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22344,7 +21841,7 @@
           <t>954304E500[C타입 폴딩]</t>
         </is>
       </c>
-      <c r="M367" s="28" t="inlineStr">
+      <c r="M367" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22354,9 +21851,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O367" s="24" t="inlineStr">
-        <is>
-          <t>4차 페이스리프트(2019) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O367" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22391,7 +21888,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G368" s="28" t="inlineStr">
+      <c r="G368" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22409,7 +21906,7 @@
           <t>954304E500[C타입 폴딩]</t>
         </is>
       </c>
-      <c r="M368" s="28" t="inlineStr">
+      <c r="M368" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22419,9 +21916,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O368" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O368" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22513,7 +22010,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G370" s="28" t="inlineStr">
+      <c r="G370" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22531,7 +22028,7 @@
           <t>954304E500[C타입 폴딩, ~12.2]</t>
         </is>
       </c>
-      <c r="M370" s="28" t="inlineStr">
+      <c r="M370" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22541,9 +22038,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O370" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O370" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22602,11 +22099,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O371" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스 원문: CP000[~2021.7.5, 블레이드 81996CP000] → CP500[2021.7.5~] → CP600[2023.5.18~, 블레이드 81996CP100]</t>
-        </is>
-      </c>
+      <c r="O371" s="19" t="n"/>
     </row>
     <row r="372" ht="15" customHeight="1" s="15">
       <c r="A372" s="19" t="inlineStr">
@@ -22639,7 +22132,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G372" s="28" t="inlineStr">
+      <c r="G372" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22653,7 +22146,7 @@
       <c r="J372" s="19" t="n"/>
       <c r="K372" s="19" t="n"/>
       <c r="L372" s="19" t="n"/>
-      <c r="M372" s="28" t="inlineStr">
+      <c r="M372" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22663,9 +22156,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O372" s="24" t="inlineStr">
-        <is>
-          <t>2021.12.2~2023.12 구간 폴딩키 PN은 국내 원문에서 확인하지 못해 공란</t>
+      <c r="O372" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22724,11 +22217,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O373" s="19" t="inlineStr">
-        <is>
-          <t>이전에 2022년에 CP600을 함께 적었으나 원문상 CP600은 2023.5.18부터라 정정</t>
-        </is>
-      </c>
+      <c r="O373" s="19" t="n"/>
     </row>
     <row r="374" ht="15" customHeight="1" s="15">
       <c r="A374" s="19" t="inlineStr">
@@ -22761,7 +22250,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G374" s="28" t="inlineStr">
+      <c r="G374" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22779,7 +22268,7 @@
           <t>954304E700[2023.12~]</t>
         </is>
       </c>
-      <c r="M374" s="28" t="inlineStr">
+      <c r="M374" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22789,9 +22278,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O374" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+      <c r="O374" s="34" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22883,7 +22372,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G376" s="28" t="inlineStr">
+      <c r="G376" s="34" t="inlineStr">
         <is>
           <t>ID60(4D60)[819964E010 키], ID46[819964E020 키]</t>
         </is>
@@ -22905,7 +22394,7 @@
           <t>954304E700</t>
         </is>
       </c>
-      <c r="M376" s="28" t="inlineStr">
+      <c r="M376" s="34" t="inlineStr">
         <is>
           <t>BOSCH 95P08, 델파이 ECU(39111-4A520)[133마력]</t>
         </is>
@@ -22915,9 +22404,9 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O376" s="19" t="inlineStr">
-        <is>
-          <t>국내 현대모비스(hellowcar): 내연 봉고3 스마트키 954404EGA0·블레이드 81996CP100 리스팅 확인. 버튼시동 스마트키는 LPG 터보 10.25인치 내비 패키지 옵션으로 확인(카눈 가격표)</t>
+      <c r="O376" s="35" t="inlineStr">
+        <is>
+          <t>엔진·ECU 사양별 4D(81996-4E010)·46(81996-4E020) 키 구분 연식 매칭 원문 없음</t>
         </is>
       </c>
     </row>
@@ -23126,7 +22615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A207"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.2"/>
   <cols>
     <col width="118" customWidth="1" style="15" min="1" max="1"/>
@@ -23227,193 +22716,1337 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="n"/>
+      <c r="A16" s="48" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="48" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="48" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="48" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="n"/>
+      <c r="A24" s="48" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="48" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="A26" s="48" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="A27" s="48" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="A28" s="48" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="A29" s="48" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="inlineStr">
+      <c r="A30" s="48" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="48" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="48" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="39" t="n"/>
+      <c r="A33" s="48" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="A34" s="48" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="A35" s="48" t="inlineStr">
         <is>
           <t>- K3 (Forte, YD 페이스리프트) 2016: A7600 칩은 Lonsdor 8A 스마트키 PCB 지원 차종(K3 2016-2018)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="39" t="inlineStr">
+      <c r="A36" s="48" t="inlineStr">
         <is>
           <t>- K3 (Forte, YD 페이스리프트) 2017: 국내 현대모비스 원문 확인</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="39" t="inlineStr">
+      <c r="A37" s="48" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD) 2021: 더 뉴 K3(BD PE) 출시(2021.4). 95440-M6800은 한국 시장용 정품 HITAG AES ID4A(NCF29A1M)로 다수 판매처(mk3·abkeys·americankeysupply) 일치 확인 → 기존 'ID8A/ID47 미확정' 해소(PE 이전은 ID8A, PE 이후는 ID4A)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="48" t="inlineStr">
         <is>
           <t>- 스토닉 2017: 스토닉 국내 출시(2017.6.21) — 프라이드(UB)와 같은 플랫폼 공유 크로스오버. 국제 판매처(gskeyae.com) 확인: '2017-2018 KIA Stonic ... 8A Texas Crypto 128-bits AES' — 이전에 'ID47 추정'이라고 했던 건 정정함</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="48" t="inlineStr">
         <is>
           <t>- 쏘울 (Soul, PS) 2014: 칩: 95440-B2000·B2AA0 한국 시장용 정품 8A Texas Crypto 128bit AES, 4버튼(mk3·abkeys·remotesandkeys) — 이전 'ID47 추정'은 정정</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="48" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2016: 국제 판매처(go-parts.com, americankeysupply) 확인: Hitag3 ID47 - 이전에 ID6E-MA(DST80) 추정이라고 했던 건 정정함</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="A41" s="48" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, MQ4) 2021: 칩: 95440-P2000(5버튼)·P2200(7버튼)·P2AD0(7버튼) 모두 정품 HITAG AES ID4A(mk3·abkeys·royalkeysupply) — 이전 '추정' 해소</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="A42" s="48" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2021: 이전 '적용 시점 추정' 해소: G5025는 원문상 22년형</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="A43" s="48" t="inlineStr">
         <is>
           <t>- 레이 2023: 95440-A3600(2022.8.31~)은 DST-AES ID6A 4버튼, 2023-2024 레이 적용(mk3·abkeys·vvdi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="48" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="48" t="inlineStr">
+        <is>
+          <t>※ 연식별 참고 메모 (예전 비고 칸 내용 — 색 없는 행이라 비고에서 옮김)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="48" t="inlineStr">
+        <is>
+          <t>- 옵티마 (Optima, MS) 2005(단종): 옵티마 국내 마지막 연식(2005.10 단종, 로체로 세대교체). 국제 판매처(abkeys.com) 확인: PN 81996-3C010, 4D-60/HYN7R, 'KIA OPTIMA 2000-2005' 명시 — 나무위키 확인: EF쏘나타와 완전히 동일한 모델(플랫폼·전자장비 100% 공유)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="48" t="inlineStr">
+        <is>
+          <t>- 로체 (Optima, MG) 2005: 로체 국내 출시(2005.10). 국내 현대모비스(hellowcar) 스마트키 원문: 954402G000[~2008.5.28, 블랭킹 819962G020] → 954401M010[2008.8.28~2009.8.10, 819962G520] → 954402G100[2010.8.10~, 819962G030]. 2009.8.10~2010.8.10 사이 품번은 원문에 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="48" t="inlineStr">
+        <is>
+          <t>- 로체 (Optima, MG) 2008: 국내 현대모비스 확인 — 2008년 안에 폴딩키·스마트키 부품 모두 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="48" t="inlineStr">
+        <is>
+          <t>- 로체 (Optima, MG) 2009: 국내 현대모비스 확인 — 폴딩키 날짜 구간이 일부 겹쳐 표기됨(트림별 차이 가능성), 원문 그대로 병기</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="48" t="inlineStr">
+        <is>
+          <t>- 로체 (Optima, MG) 2010(단종): 로체 마지막 연식(2010) — K5로 세대교체. 국내 현대모비스(hellowcar) 스마트키 원문: 954402G000[~2008.5.28, 블랭킹 819962G020] → 954401M010[2008.8.28~2009.8.10, 819962G520] → 954402G100[2010.8.10~, 819962G030]. 2009.8.10~2010.8.10 사이 품번은 원문에 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="48" t="inlineStr">
+        <is>
+          <t>- 포르테 (Forte, TD 세단) 2008: 포르테 세단(TD) 국내 출시(2008.8.21) — 이 해엔 세단만 있었고 쿠페는 아직 출시 전. 출시 당시 디럭스 트림은 '폴딩타입 무선도어 리모컨키' 기본(다나와 2008년형 트림표). 버튼시동 스마트키가 어느 트림부터 기본인지와 폴딩키 부품번호는 국내 원문에서 확인 못함</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48" t="inlineStr">
+        <is>
+          <t>- K3 (Forte, YD/BD) 2018: K3(BD) 완전변경 출시(2018.2). 국내 현대모비스 원문: BD 스마트키 M6000[2018.1.8~8.30] → M6011[2018.8.30~2021.4.26] · M6501[2018.9.18~2021.3.24] → M6800[2021.4.5~2024.2.8] → M6801[2024.2.8~], 블레이드 81996M6020. BD 초기 스마트키(M6000/M6011/M6501, FCC CQOFD00430) 칩은 정품 기준 DST-AES ID8A(abkeys·tlkeys)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="48" t="inlineStr">
+        <is>
+          <t>- K3 (Forte, BD) 2020: 2021년형(2020년 출시)부터 버튼시동 스마트키 전 트림 기본(모터그래프·엔카)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48" t="inlineStr">
+        <is>
+          <t>- K3 (Forte, BD 페이스리프트) 2022: 스마트키 전 트림 기본화 이후 폴딩키(M6400)의 적용 대상은 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="48" t="inlineStr">
+        <is>
+          <t>- K3 (Forte, BD PE) 2024(단종): K3 국내 최종 연식 — 2024년 7월 완전 단종. 후속 K4는 국내 미출시(해외 전략형 모델), 국내 준중형 세단 수요는 셀토스·EV3·EV4로 대체됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, TF) 2010: 국내 현대모비스(hellowcar) 폴딩키 원문: TF 954302T500[~2012.7.6, 블랭킹 819962L000] → 954302T501[2012.7.6~, 819962L001] / JF 954302T570(블랭킹 81996A4000)·95430D4010 / DL3 95430L2000·L2010(블랭킹 81996L2000). 이전에 TF에 넣었던 2T570은 원문상 JF용이라 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, TF) 2011: K5 하이브리드(TFE) 출시(2011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, TF) 2013: 국내 현대모비스 확인 — 2013.6.10 기준 스마트키·비상키 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, TF/JF) 2015: K5(JF, 올 뉴 K5) 완전변경 출시(2015)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, JF) 2017: 더 뉴 K5(JF 페이스리프트) 출시(2017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, JF) 2018: 더뉴K5 하이브리드 2세대(JFE) 출시(2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, JF) 2019: JF 마지막 연식</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, JF/DL3) 2019: K5(DL3) 완전변경 출시(2019.9)로 같은 해 전환 — 하이브리드 3세대(DL3KH)도 2019년 출시</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, DL3) 2020: 국내 현대모비스(hellowcar) 원문: L3010·L2200은 연식 라벨 없는 초기 품번, L2320·L2300은 21년형, L2420·L2400은 22년형</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, DL3/DL3 페이스리프트) 2023: 더 뉴 K5(DL3 페이스리프트) 출시(2023.9)로 전환되는 해 — 95440-L2520은 하이브리드와 공용</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="48" t="inlineStr">
+        <is>
+          <t>- K5 (Optima, DL3 페이스리프트) 2026: 국내 현대모비스(hellowcar) 원문상 PE 스마트키 L2500·L2510·L2520은 종료일 없는 현행 품번</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, VG) 2009: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, VG) 2010: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, VG) 2011: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, VG) 2012: 국내 현대모비스 확인 — 2012.11.5 기준 스마트키 전환. 카드키 원문: 954403R800[2012.10.30~2013.2.28, 블레이드 819963T100] → 954403R801[2013.2.28~2015.12.31] → 95443F6000[2015.12.9~2019.6.27, 블레이드 81996F6110] → 95443F6010[2019.5.30~]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, VG) 2013: 이전에 VG 카드키 블레이드를 81996-F6110으로, 카드키에 95443-F6000을 적었으나 둘 다 YG용이라 정정(VG 카드키 블레이드는 819963T100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, VG) 2015: K7(YG) 완전변경 출시(2016.1)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, YG) 2016: 국내 현대모비스 확인 — 이모빌라이저 모듈(95420D4000)은 포터2·그랜드스타렉스와 공유</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, YG) 2019: 'K7 프리미어' 페이스리프트(2019.6)로 전환되는 해. 이전에 81996-F6110을 프리미어 스마트키 블레이드로 적었으나 원문상 카드키 블레이드라 정정(F6510 스마트키 블레이드는 원문 미확인). 스마트키 모듈(제어기) 95480-F6500</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, YG 프리미어) 2020: 스마트키 모듈(제어기): 95480-F6500</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="48" t="inlineStr">
+        <is>
+          <t>- K7 (Cadenza, YG 프리미어) 2021(단종): K7 국내 마지막 연식(2021.1 단종) — 후속 K8으로 이어짐. 스마트키 모듈: 95480-F6500(2019.6-2021.4 적용 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="48" t="inlineStr">
+        <is>
+          <t>- K8 (GL3) 2021: K8 국내 출시(2021.4). 국내 현대모비스(hellowcar) 원문: L8000(주차보조X)/L8010(주차보조O)은 ~2024.2.13, 이후 L8001/L8011로 전환. 블레이드 S9000=주차보조X, L2020=주차보조O, 폴딩키용 81996-L2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="48" t="inlineStr">
+        <is>
+          <t>- K8 (GL3/GL3 페이스리프트) 2024: 국내 현대모비스(hellowcar): 2024.2.13은 초기형 L8000·L8010 → L8001·L8011 품번 개정일이고, 페이스리프트(2024.8.9 공개, 위키백과)부터 L8500·L8510·L8520·L8530 적용 — 이전에 2.13을 페이스리프트 전환일로 적었던 것 정정. NFC 카드키 AT954AP000·GZ954AP000(K8GL3/EV6/스포티지NQ5/쏘렌토MQ4/카니발KA4 공용 리스팅)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="48" t="inlineStr">
+        <is>
+          <t>- K8 (GL3 페이스리프트) 2026: 원문상 PE 스마트키 4종은 종료일 없는 현행 품번</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="48" t="inlineStr">
+        <is>
+          <t>- K9 (K900/Quoris, KH) 2012: K9(KH) 국내 출시(2012.3.27). 국내 현대모비스(hellowcar) 원문: 스마트키 954403T200[2012.3.27~2017.12.30]→819963T000, 카드키 954433T000[~2013.7.1, 버튼X]→954433T100[2013.7.1~2014.11.15]→954433T200[2014.11.10~2017.12.30, 버튼X], 카드키 블레이드 819963T100</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="48" t="inlineStr">
+        <is>
+          <t>- K9 (K900/Quoris, KH) 2013: 국내 현대모비스(hellowcar) 원문: 3T200[2012.3.27~2017.12.30], 3T300[2013.9.1~2014.1.1]. 카드키 날짜도 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="48" t="inlineStr">
+        <is>
+          <t>- K9 (K900/Quoris, KH) 2016: 이전에 2016년 카드키 블레이드를 81996-3T200으로 적었으나 원문상 카드키 블레이드는 819963T100이라 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="48" t="inlineStr">
+        <is>
+          <t>- K9 (K900/Quoris, KH/RJ) 2018: K9(RJ, '더 K9') 완전변경 출시(2018.4)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="48" t="inlineStr">
+        <is>
+          <t>- K9 (K900, RJ) 2021: 국내 현대모비스 확인 — 2021.5.21 기준 '더뉴 K9'로 부품 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="48" t="inlineStr">
+        <is>
+          <t>- K9 (K900, RJ) 2025: 국내 현대모비스(hellowcar) 원문: 'K9RJ [2021.5.21 이후~] 95440J6610·J6600·81996J6000·J6100' — 종료일 없는 현행 품번</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="48" t="inlineStr">
+        <is>
+          <t>- 프라이드 JB 2005: 프라이드(JB) 국내 출시(2005.4.7) — 리오(BC) 후속, 국내 차명이 '프라이드'로 부활. 기본트림(LX)은 무선도어리모콘키만 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="48" t="inlineStr">
+        <is>
+          <t>- 프라이드 JB/UB 2011: 올 뉴 프라이드(UB) 완전변경 출시(2011.9.28)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="48" t="inlineStr">
+        <is>
+          <t>- 프라이드 UB 2013: 국내 현대모비스 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="48" t="inlineStr">
+        <is>
+          <t>- 프라이드 UB (더 뉴 프라이드) 2014: 더 뉴 프라이드 페이스리프트(2014.12) 출시. 국내 현대모비스(hellowcar) 재확인 — 비상키 접두사가 81996이 아니라 81999인 경우가 2개 있어서 정정함</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="48" t="inlineStr">
+        <is>
+          <t>- 프라이드 UB (더 뉴 프라이드) 2017(단종): 프라이드 국내 마지막 연식(2017.9 단종) — 4세대(리오 YB)는 국내 출시가 백지화되고 같은 플랫폼의 크로스오버 스토닉(SP2)으로 대체, 국내 후속 없음(위키백과 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="48" t="inlineStr">
+        <is>
+          <t>- 오피러스 (Opirus, GH) 2004: 국제 판매처(remotesandkeys.com, key4.com) 확인: PN 81996-3FA10, ILCO KK7-PT, 4D60 — 리모컨 없는 막대형 키(2003-2006 공용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="48" t="inlineStr">
+        <is>
+          <t>- 오피러스 (Opirus, GH) 2005: 국제 판매처 확인 — 막대형 키</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="48" t="inlineStr">
+        <is>
+          <t>- 오피러스 (Opirus, GH) 2006: 국제 판매처 확인 — 막대형 키</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="48" t="inlineStr">
+        <is>
+          <t>- 오피러스 (Opirus, GH) 2007: 국제 판매처(remotesandkeys.com) 확인: PN 81996-3F050, ILCO KK9-PT, ID46 — 리모컨 없는 막대형 키</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="48" t="inlineStr">
+        <is>
+          <t>- 오피러스 (Opirus, GH) 2008: 국제 판매처 확인 — 막대형 키</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="48" t="inlineStr">
+        <is>
+          <t>- 오피러스 (Opirus, GH 프리미엄) 2009: 오피러스 프리미엄 페이스리프트(2009.5) 출시 — 국내 현대모비스 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="48" t="inlineStr">
+        <is>
+          <t>- 오피러스 (Opirus, GH 프리미엄) 2012(단종): 오피러스 국내 마지막 연식(2012.5) — K7(Cadenza)로 세대교체, 직접적 후속 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="48" t="inlineStr">
+        <is>
+          <t>- 스팅어 (Stinger, CK) 2017: 스팅어 국내 출시(2017.5) — 제네시스 G70(IK)와 플랫폼 공유</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="48" t="inlineStr">
+        <is>
+          <t>- 스팅어 (Stinger, CK) 2018: 국내 판매처(모터스K) 확인: 2018년 7월 이후 생산된 19년형은 95440-J5200이 맞지 않을 수 있고 95440-J5210 적용. 국내 현대모비스(hellowcar): J5200·J5210은 ~2020.7.28, 이후 J5700·J5710, 블레이드 81996J5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="48" t="inlineStr">
+        <is>
+          <t>- 스팅어 (Stinger, CK) 2020: 국내 현대모비스 확인 — 2020.7.28 기준 페이스리프트 부품 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="48" t="inlineStr">
+        <is>
+          <t>- 스팅어 (Stinger, CK 페이스리프트) 2023(단종): 스팅어 국내외 단종(2023.4) — 직접적 후속 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="48" t="inlineStr">
+        <is>
+          <t>- 스토닉 2020: 페이스리프트('더 뉴 스토닉') 출시(2020)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="48" t="inlineStr">
+        <is>
+          <t>- 스토닉 2023: 생산지 이관(광명→서산 동희오토), 국내 부품번호는 초기형과 동일 계열로 확인, 페이스리프트 이후 세부 개정 여부는 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="48" t="inlineStr">
+        <is>
+          <t>- 스토닉 2024: 국내 판매처(모터스K)·헬로우카 원문: 스마트키 95440H8000·블랭킹 81999H8300 '적용시점 2017.6.21~'(종료일·개정품번 없음) → 같은 PN이므로 칩도 ID8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="48" t="inlineStr">
+        <is>
+          <t>- 셀토스 (SP2) 2020: 연식변경(2020.7.1) — 전방충돌방지보조 등 안전사양 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="48" t="inlineStr">
+        <is>
+          <t>- 셀토스 (SP2/SP2 PE) 2022: '더 뉴 셀토스'(SP2 PE) 페이스리프트 출시(2022.7)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘울 (Soul, AM) 2008: 쏘울 국내 출시(2008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘울 (Soul, AM) 2009: 칩: transpondery.com 'KIA SOUL 2008-2013: Philips PCF7952A / ID46 / Hitag 2', 2013 정품 폴딩키 '46 Chip'(vvdi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘울 부스터 (Soul, SK3) 2019: 쏘울 부스터(SK3) 완전변경 출시(2019). 국내 현대모비스(hellowcar) 확인 — 연식별 세부 날짜는 추가 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘울 부스터 (Soul, SK3) 2025(단종): 쏘울 국내외 최종 단종 연식(2025) — 후속 없음(나무위키 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="48" t="inlineStr">
+        <is>
+          <t>- 레이 (Ray, TAM) 2011: 레이 국내 출시(2011.11) — 국내 현대모비스(hellowcar) 날짜별 원문 재확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="48" t="inlineStr">
+        <is>
+          <t>- 레이 (Ray, TAM) 2015: 이전에 2015-2016 폴딩키를 A3100/A3110으로 적었으나 원문상 A3001 구간(2012.9.10~2017.12.12)이라 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="48" t="inlineStr">
+        <is>
+          <t>- 레이 (Ray, TAM) 2017: 국내 현대모비스 확인 — 2017년 하반기 스마트키 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="48" t="inlineStr">
+        <is>
+          <t>- 레이 (Ray, TAM) 2022: 국내 현대모비스 확인 — 2022.9.5 기준 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="48" t="inlineStr">
+        <is>
+          <t>- 레이 (Ray, TAM) 2025: 원문상 스마트키 A3600[2022.8.31~], 폴딩키 A3600[2022.8.31~]·A3610[2023.6.16~] 모두 종료일 없는 현행 품번</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="48" t="inlineStr">
+        <is>
+          <t>- 모닝 (Morning, SA) 2004: 모닝 국내 출시(2004)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="48" t="inlineStr">
+        <is>
+          <t>- 모닝 (Morning, SA) 2010: TA 완전변경 출시(2011)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="48" t="inlineStr">
+        <is>
+          <t>- 모닝 (Morning, TA) 2011: 올뉴 모닝(TA) 출시(2011.1). 국내 현대모비스(hellowcar) 원문: TA 스마트키 954401Y500[~2013.8.16, 블랭킹 819961Y020] → 954401Y600[2013.8.16~2016.12.29, 819961Y620] / JA 스마트키 95440G6000[2016.10.25~, ~22년식]·95440G6100[22년식~] ~2023.6.27(블랭킹 81996G6020) → 95440G6500[2023.6.27~, 81996P2800]. 이전에 TA에 G6000·G6100, JA에 1Y500·1Y600을 적었던 것은 서로 뒤바뀐 오류라 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="48" t="inlineStr">
+        <is>
+          <t>- 모닝 (Morning, TA) 2012: 국내 현대모비스 확인 — 2012.9.27 기준 폴딩키 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="48" t="inlineStr">
+        <is>
+          <t>- 모닝 (Morning, TA) 2013: 국내 현대모비스 확인 — 2013.8.1 기준 폴딩키 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="48" t="inlineStr">
+        <is>
+          <t>- EV3 (SV) 2024: EV3 국내 출시(2024.7) — K3 플랫폼 기반 E-GMP, 국내 현대모비스 확인. 부품번호는 '주차보조/디지털키' 조합별 4종</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="48" t="inlineStr">
+        <is>
+          <t>- EV3 (SV) 2026: '더 EV3' 연식변경(2026.2.2 출시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="48" t="inlineStr">
+        <is>
+          <t>- EV6 (CV) 2021: 국내 현대모비스(hellowcar) 원문: CV000(주차보조X)/CV010(주차보조O) ~2024.2.7, 이후 CV001/CV011. 블레이드 CV000=주차보조X, CV010=주차보조O</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="48" t="inlineStr">
+        <is>
+          <t>- EV6 (CV) 2024: 국내 현대모비스(hellowcar): 초기형 CV000·CV010[~2024.2.7] → CV001·CV011[2024.2.7~], 페이스리프트 전용 CV500·CV510·CV520 별도 리스팅(적용 시작일 원문 미확인). 칩: 95440-CV000 정품 HITAG AES ID4A(tlkeys)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="48" t="inlineStr">
+        <is>
+          <t>- EV6 (CV) 2025: 이전에 2025~2026년에 초기형 CV001·CV011을 적었으나 페이스리프트 전용 CV500·CV510·CV520으로 정정(hellowcar). CV510·CV520 해외 판매처 적용 2025~2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="48" t="inlineStr">
+        <is>
+          <t>- EV9 2023: EV9 국내 출시(2023.5). 국내 현대모비스(hellowcar): 스마트키 DO000·DO010·DO020·DO030(사양 표기 원문 그대로), 블랭킹 81996DO000, 케이스 81995DO000 — 종료일 없는 현행 품번. 이전에 넣었던 DO060은 국내 원문에 없어 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, JE/KM) 2004: 칩: 트랜스폰더 카탈로그 'SPORTAGE 2004~ Philips Crypto2 ID46', 247geek 'Kia Sportage 25.08.2004-01.11.2012 ID46(PCF7936)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, JE/KM) 2010: SL 완전변경 출시(2010)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, SL) 2011: 국내 현대모비스(hellowcar) 및 국제 판매처(gskeyae) 확인. transpondery.com 카탈로그 원문 확인: SL세대는 트림별로 DST80/ID6E-MA(플립) 또는 ID46/PCF7952A(스마트) 혼재 — 폴딩키 PN 국내 확인, 이전에 누락됐던 것 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, SL) 2012: transpondery.com 카탈로그 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, SL) 2015: 올 뉴 스포티지(QL) 완전변경 출시(2015)로 전환되는 해 — QL 초기부터 확정 ID47(NCF2971X) 확인됨(americankeysupply)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, QL) 2018: 국내 현대모비스 확인 — 2018년 중반 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, QL) 2019: 국내 현대모비스(hellowcar) 원문: D9000[2015.8.3~2018.8.7] → D9500[2018.6.26~] → D9600[2019.2.26~], 블랭킹 81996A4040</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, QL) 2021: 디 올 뉴 스포티지(NQ5) 완전변경 출시(2021)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, NQ5) 2022: 국내 현대모비스(hellowcar) 원문: 주차보조X P1100→P1110[2023.1.31~], 블랭킹 81999J7020 / 주차보조O P1200→P1210[2023.1.31~], 블랭킹 81996P1060. 이전 블레이드 기재(81926-J7000, 81996-K0000)는 원문과 달라 정정. 칩 ID4A(keyshop-online 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, NQ5) 2023: 국내 현대모비스 확인 — 2023.1.31 기준 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, NQ5) 2024: 더 뉴 스포티지(NQ5 PE) 출시(2024.11.5, 나무위키). 국내 현대모비스(hellowcar): PE 스마트키 P1AB0·P1AC0·P1AE0·P1AF0, 블랭킹 81996S9600(사양별 구분은 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="48" t="inlineStr">
+        <is>
+          <t>- 스포티지 (Sportage, NQ5) 2025: 이전에 2025~2026년에 초기형 PN(P1110·P1210)을 적었으나 2024.11 페이스리프트 이후 PE 부품으로 정정. 폴딩키 P1000의 PE 적용 여부는 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, BL) 2009: 쏘렌토R(XM) 완전변경 출시(2009.5)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, XM) 2010: 국내 현대모비스 확인 — 2010.7.1 기준 스마트키 전환. 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, XM) 2012: 뉴 쏘렌토R(페이스리프트) 출시(2012.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, XM) 2013: 국내 현대모비스(hellowcar) 재확인 — 954402P500용 블레이드는 819962P300(이전 819962J700은 오기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, XM/UM) 2014: 쏘렌토(UM) 완전변경 출시(2014.8)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, UM) 2015: 국내 현대모비스(hellowcar) 원문: 95440C5000[2014.8.16~2017.7.24, 블레이드 81996C5040] → 95440C5500(더뉴쏘렌토)[2017.6.29~, 블레이드 81996C5050]. 칩: C5000·C5500 모두 HITAG3 ID47(한국 시장용 정품 mk3·tlkeys), 4버튼</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, UM) 2017: 더 뉴 쏘렌토(UM 페이스리프트) 출시(2017.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, UM 페이스리프트) 2018: 국내 현대모비스 원문: 95440C5500[2017.6.29~] 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, UM/MQ4) 2020: 쏘렌토(MQ4) 완전변경 출시(2020.3)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, MQ4) 2023: 2023.8 페이스리프트('더 뉴 쏘렌토')로 전환되는 해 — 하이브리드 공용 신형 스마트키(95440-P2AD0) 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="48" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (Sorento, MQ4 페이스리프트) 2024: 국내 현대모비스(hellowcar): 더 뉴 쏘렌토(MQ4 PE) 스마트키 P2AA0·P2AB0·P2AC0·P2AD0 4종 확인(사양별 구분은 원문 미확인). 카폼: P2AD0 적용 '더 뉴 쏘렌토 2023.8 이후'(종료일 없음). 칩 ID4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM) 2008: 모하비 국내 출시(2008.1). 국내 현대모비스(hellowcar) 원문: 2J800[~2010.12.13] → 2J860[2010.12.13~2011.6.1] → 2J870[2011.6.1~2015.12.23] (블레이드 819962J700) / 1W000[2016.1.15~2019.6.13, 819962J700] / 2J200(더뉴 모하비)[2016.11.15~2019.6.13, 819962J800]</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM) 2010: 국내 현대모비스 확인 — 2010.12.13 기준 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM) 2011: 국내 현대모비스 확인 — 2011.6.1 기준 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM) 2012: 이전에 2012~2013년에 1W000·2J200을 함께 적었으나 원문상 둘 다 2016년부터라 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM) 2014: 모하비 더 마스터(1차 페이스리프트) 출시(2014.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM) 2018: 모하비 더 마스터(2차 완전변경급 페이스리프트) 출시(2019)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM 더마스터) 2019: 국제 판매처(abkeys.com) 확인 — 더마스터부터 ID46에서 ID47로 칩 세대 전환. 초기형(2008-2018)은 abkeys 확인 PCF7952A ID46</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM 더마스터) 2021: 국내 현대모비스 확인 — 2021.6.8 기준 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="48" t="inlineStr">
+        <is>
+          <t>- 모하비 (Mohave, HM 더마스터) 2025: 국내 현대모비스(hellowcar) 원문: 모하비 더마스터[2019.8.22~] 2J500[~2021.6.8] → 2J550·2JAA0[2021.6.8~, 종료일 없음], 블랭킹 819962J900</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="48" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, DE) 2016: 니로(DE) 국내 출시(2016.3.7, 95440-G5000 출시일과 일치). 칩: 같은 PN(95440-G5000) 정품 Hitag3 ID47 확인. 국내 현대모비스(hellowcar) 원문: G5000[~2019.2.28, 블랭킹 81996G5A20] → G5010[2019.2.28~] · G5025[22년형] · DB000[니로 플러스], 이후 블랭킹 81999J7020</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="48" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, DE) 2017: 국제 판매처(keyshop-online, dfwkeys4cars) 확인 — Hitag3 ID47</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="48" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, DE) 2018: 이전에 2018년에 G5010을 함께 적었으나 원문상 G5010은 2019.2.28부터라 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="48" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, DE) 2019: 니로 플러스(택시형) 출시 — 별도 스마트키 PN(95440-DB000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="48" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, DE) 2020: 니로(DE) 페이스리프트(2019.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="48" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, DE/SG2) 2022: 디 올 뉴 니로(SG2) 완전변경 출시(2022.1)로 전환되는 해 — 이때 칩이 ID47(Hitag3)에서 ID4A(Hitag AES)로 세대 전환. 디지털키2 터치 옵션 최초 도입</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="48" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, SG2) 2023: 블레이드 매칭: 원문 옵션 순서(주차보조X→81999J7020, 주차보조O→81996P1060), 셀토스·스포티지 NQ5 원문과 동일 구성</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="48" t="inlineStr">
+        <is>
+          <t>- 니로 (Niro, SG2) 2024: 국내 현대모비스 확인 — 2024.2.7 기준 부품번호 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="48" t="inlineStr">
+        <is>
+          <t>- 카렌스 (Carens, RS) 1999: 카렌스(RS) 국내 출시(1999)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="48" t="inlineStr">
+        <is>
+          <t>- 카렌스 (Carens, RS) 2002: 카렌스2/엑스트렉 페이스리프트(2002)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="48" t="inlineStr">
+        <is>
+          <t>- 카렌스 (Carens, UN) 2007: 국내 현대모비스(hellowcar) 폴딩키 원문: D101[2007.7.2~2008.5.27] → D102[2008.5.27~2010.6.16] → D103[2010.6.1~2012.7.17] → D104[2012.7.1~2012.7.17, 블랭킹 819962L001] / RP 95430A4000[2013.2.28~2016.6.30]. D100은 부품만 확인되고 날짜 옵션이 원문에 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="48" t="inlineStr">
+        <is>
+          <t>- 카렌스 (Carens, UN/RP) 2013: 올 뉴 카렌스(RP) 완전변경 출시(2013.3.29). transpondery.com 카탈로그 원문 확인: RP세대는 트림별로 DST80/ID6E-MA(플립) 또는 ID46/PCF7952A(스마트) 혼재 - 이전에 스마트키만 쓰고 플립키 트림을 빠뜨렸던 것 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="48" t="inlineStr">
+        <is>
+          <t>- 카렌스 (Carens, RP) 2016: 더 뉴 카렌스(RP 페이스리프트) 출시(2016.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="48" t="inlineStr">
+        <is>
+          <t>- 카렌스 (Carens, RP) 2017: 폴딩키 95430A4000은 원문상 2016.6.30까지 — 더 뉴 카렌스(2016.7~) 폴딩키 품번은 원문에서 확인 못해 공란</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="48" t="inlineStr">
+        <is>
+          <t>- 카렌스 (Carens, RP) 2018(단종): 카렌스 국내 최종 연식 — 2018년 10월 공식 단종. 4세대(KY, 2022+ 해외)는 인도 등 전략시장 전용, 국내 미판매, 국내 후속 없음(나무위키 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, KV-II/GQ) 2005: 그랜드카니발(VQ) 완전변경 출시(2005.7)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, VQ) 2006: 그랜드카니발(VQ). 칩·블레이드: 정품 81996-4D040 PCF7936 ID46(abkeys), 'Sedona 2006-2012 ID46 81996-4D040'(locksmithkeyless). 폴딩키: 2008.6.2 기준 001/011/021 → 002/012/022 계열 전환, 끝자리는 버튼 수(3/5/6버튼) 구분(hellowcar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, VQ) 2010: 타이거노즈 그릴 적용 페이스리프트(2010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, VQ/YP) 2014: 올 뉴 카니발(YP) 출시(2014.6). 국내 현대모비스(hellowcar) 원문: YP 스마트키 A9300(6버튼, 전동도어O)·A9100(4버튼, 전동도어X)[2014.5.26~], 블랭킹 81996A4040 — 이전 기재 95440-A9200은 국내 원문에 없는 번호라 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, YP) 2015: 국제 판매처(abkeys.com) 확인 — Hitag3 ID47</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, YP) 2018: 더 뉴 카니발(YP PE 페이스리프트) 출시(2018.3.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, YP) 2020: 카니발(KA4) 출시(2020.8). 국내 현대모비스(hellowcar) 원문: 슬라이딩도어자동X는 P2000[~2020.7.20]→R0000[2020.7.20~]→R0430(22년형), 블랭킹 81996P2700 / 자동O는 R0100→R0420(22년형), 블랭킹 81996R0710 / 주차보조버튼O는 R0510</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, KA4) 2022: 국제 판매처(Amazon/KEYECU) 확인 — '4A Chip' 명시</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, KA4) 2023: '더 뉴 카니발'(KA4 PE 페이스리프트) 출시(2023.10)로 전환되는 해</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="48" t="inlineStr">
+        <is>
+          <t>- 카니발 (Carnival, KA4 PE) 2024: 국내 현대모비스(hellowcar): 더 뉴 카니발(KA4 PE) 스마트키 R0800·R0810·R0820·R0840·R0850·R0AA0·R0AB0·R0AE0·R0AF0, 블랭킹 81996P2800(케이스 81995P2000). 사양별 구분은 원문 미확인. 이전 기재 R0870은 국내 원문에 없어 삭제, 블레이드도 P2700/R0710 → P2800으로 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 EV (전기차) 2021: 국내 현대모비스 원문: CP000[~2021.7.5, 블레이드 81996CP000] → CP500[2021.7.5~] → CP600[2023.5.18~, 블레이드 81996CP100]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 EV (전기차) 2022: 이전에 2022년에 CP600을 함께 적었으나 원문상 CP600은 2023.5.18부터라 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2003: 카키넘버원(국내 키 도매) 확인: 81996-4E000 일반키[2004.9.1~2016.8.31], 81996-4E010 이모빌라이저키(4D 칩), 81996-4E020 이모빌라이저키(46 칩), 81996-4E031 폴딩키 블레이드[2013.1.17~2016.8.31], 81996-4F700 폴딩키 블레이드[2016.8.31~]. 이모빌라이저키 4종의 연식 구간은 원문에 없어 차대번호로 확인 필요 — 이전에 연식별로 나눠 적었던 막대키 PN은 근거 없는 배분이라 삭제하고 전 구간 공통 후보로 정리. MK3 릴리즈노트: 봉고3 ID46/BOSCH 95P08</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2004: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2005: 이모빌라이저: MK3 릴리즈노트는 봉고3를 ID46·BOSCH 95P08로 분류하나, 국내 정비 자료에 봉고3 133마력 델파이 ECU(39111-4A520)와 델파이형 CRDi 인젝터가 확인됨 → 엔진/ECU 사양에 따라 4D·46 키가 나뉘는 것으로 보이나 연식·사양 매칭 원문은 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2006: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2007: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2008: 페이스리프트(2008) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2009: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2010: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2011: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2012: 이전에 2012~2015년 폴딩키를 954304E500으로 적었으나 원문상 E500(C타입)은 2016.8.31부터라 정정</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2013: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2014: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2015: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2016: 3차 페이스리프트(2016) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2017: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2018: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2019: 4차 페이스리프트(2019) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2020: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2021: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2022: 2021.12.2~2023.12 구간 폴딩키 PN은 국내 원문에서 확인하지 못해 공란</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2023: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="48" t="inlineStr">
+        <is>
+          <t>- 봉고3 (Bongo3, J) 2024: 국내 현대모비스(hellowcar): 내연 봉고3 스마트키 954404EGA0·블레이드 81996CP100 리스팅 확인. 버튼시동 스마트키는 LPG 터보 10.25인치 내비 패키지 옵션으로 확인(카눈 가격표)</t>
         </is>
       </c>
     </row>

--- a/기아_트랜스폰더_칩코드_DBnew.xlsx
+++ b/기아_트랜스폰더_칩코드_DBnew.xlsx
@@ -259,7 +259,7 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -401,6 +401,9 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1566,24 +1569,24 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G17" s="34" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952A)</t>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F17" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G17" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -1602,18 +1605,18 @@
           <t>95440-1M010</t>
         </is>
       </c>
-      <c r="L17" s="19" t="n"/>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <t>95430-1M250</t>
+        </is>
+      </c>
       <c r="M17" s="38" t="n"/>
       <c r="N17" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O17" s="35" t="inlineStr">
-        <is>
-          <t>스마트키 ID46(PCF7952A) 확인 — 하위트림 폴딩키 품번·칩 미확인</t>
-        </is>
-      </c>
+      <c r="O17" s="38" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="15">
       <c r="A18" s="19" t="inlineStr">
@@ -1631,24 +1634,24 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G18" s="34" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952A)</t>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -1667,18 +1670,18 @@
           <t>95440-1M010[~8.1], 95440-1M011[8.1~]</t>
         </is>
       </c>
-      <c r="L18" s="19" t="n"/>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <t>95430-1M250</t>
+        </is>
+      </c>
       <c r="M18" s="38" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O18" s="35" t="inlineStr">
-        <is>
-          <t>스마트키 ID46(PCF7952A) 확인 — 하위트림 폴딩키 품번·칩 미확인</t>
-        </is>
-      </c>
+      <c r="O18" s="38" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="15">
       <c r="A19" s="19" t="inlineStr">
@@ -1696,24 +1699,24 @@
           <t>2011(단종)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G19" s="34" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952A)</t>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -1732,18 +1735,18 @@
           <t>95440-1M011</t>
         </is>
       </c>
-      <c r="L19" s="19" t="n"/>
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>95430-1M250</t>
+        </is>
+      </c>
       <c r="M19" s="38" t="n"/>
       <c r="N19" s="19" t="inlineStr">
         <is>
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O19" s="35" t="inlineStr">
-        <is>
-          <t>스마트키 ID46(PCF7952A) 확인 — 하위트림 폴딩키 품번·칩 미확인</t>
-        </is>
-      </c>
+      <c r="O19" s="38" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="15">
       <c r="A20" s="24" t="inlineStr">
@@ -1761,24 +1764,24 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G20" s="34" t="inlineStr">
-        <is>
-          <t>ID8A[스마트키]</t>
+      <c r="E20" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F20" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G20" s="37" t="inlineStr">
+        <is>
+          <t>ID8A[스마트키], ID6E-MA[폴딩키]</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -1799,7 +1802,7 @@
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>95430-A7200</t>
+          <t>95430-A7100, 95430-A7200</t>
         </is>
       </c>
       <c r="M20" s="38" t="n"/>
@@ -1808,11 +1811,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O20" s="34" t="inlineStr">
-        <is>
-          <t>스마트키는 ID8A 확인 — 폴딩키(95430-A7200) 칩은 판매처마다 4D60·ID46로 다름</t>
-        </is>
-      </c>
+      <c r="O20" s="37" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="15">
       <c r="A21" s="24" t="inlineStr">
@@ -1830,24 +1829,24 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="D21" s="45" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G21" s="34" t="inlineStr">
-        <is>
-          <t>ID8A[스마트키]</t>
+      <c r="E21" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G21" s="37" t="inlineStr">
+        <is>
+          <t>ID8A[스마트키], ID6E-MA[폴딩키]</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -1868,7 +1867,7 @@
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>95430-A7200</t>
+          <t>95430-A7100, 95430-A7200</t>
         </is>
       </c>
       <c r="M21" s="38" t="n"/>
@@ -1877,11 +1876,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O21" s="35" t="inlineStr">
-        <is>
-          <t>스마트키는 ID8A 확인 — 폴딩키(95430-A7200) 칩은 판매처마다 4D60·ID46로 다름</t>
-        </is>
-      </c>
+      <c r="O21" s="38" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="15">
       <c r="A22" s="24" t="inlineStr">
@@ -1899,24 +1894,24 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="D22" s="45" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G22" s="34" t="inlineStr">
-        <is>
-          <t>ID8A[스마트키]</t>
+      <c r="E22" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F22" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G22" s="37" t="inlineStr">
+        <is>
+          <t>ID8A[스마트키], ID6E-MA[폴딩키]</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -1937,7 +1932,7 @@
       </c>
       <c r="L22" s="24" t="inlineStr">
         <is>
-          <t>95430-A7200</t>
+          <t>95430-A7100, 95430-A7200</t>
         </is>
       </c>
       <c r="M22" s="38" t="n"/>
@@ -1946,11 +1941,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O22" s="35" t="inlineStr">
-        <is>
-          <t>스마트키는 ID8A 확인 — 폴딩키(95430-A7200) 칩은 판매처마다 4D60·ID46로 다름</t>
-        </is>
-      </c>
+      <c r="O22" s="38" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="15">
       <c r="A23" s="24" t="inlineStr">
@@ -1968,24 +1959,24 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="D23" s="45" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G23" s="34" t="inlineStr">
-        <is>
-          <t>ID8A[스마트키]</t>
+      <c r="E23" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G23" s="37" t="inlineStr">
+        <is>
+          <t>ID8A[스마트키], ID6E-MA[폴딩키]</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -2006,7 +1997,7 @@
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>95430-A7200</t>
+          <t>95430-A7100, 95430-A7200</t>
         </is>
       </c>
       <c r="M23" s="38" t="n"/>
@@ -2015,11 +2006,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O23" s="35" t="inlineStr">
-        <is>
-          <t>스마트키는 ID8A 확인 — 폴딩키(95430-A7200) 칩은 판매처마다 4D60·ID46로 다름</t>
-        </is>
-      </c>
+      <c r="O23" s="38" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="15">
       <c r="A24" s="24" t="inlineStr">
@@ -2247,9 +2234,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
-        <is>
-          <t>ID8A[자료 상충], ID47[자료 상충]</t>
+      <c r="G27" s="37" t="inlineStr">
+        <is>
+          <t>ID8A</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -2279,11 +2266,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O27" s="35" t="inlineStr">
-        <is>
-          <t>칩 자료 상충 — remotesandkeys는 2020 Forte TEXAS ID8A, dfwkeys4cars 종합표는 Forte 2019-2023 Hitag3 ID47</t>
-        </is>
-      </c>
+      <c r="O27" s="38" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="15">
       <c r="A28" s="24" t="inlineStr">
@@ -6127,12 +6110,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G91" s="34" t="inlineStr">
+      <c r="G91" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H91" s="19" t="n"/>
+      <c r="H91" s="19" t="inlineStr">
+        <is>
+          <t>81996-1G100[이모빌라이저키, 2005.2.15~2009.12.10], 81996-1G000[칩 없음]</t>
+        </is>
+      </c>
       <c r="I91" s="19" t="n"/>
       <c r="J91" s="19" t="n"/>
       <c r="K91" s="19" t="n"/>
@@ -6143,11 +6130,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O91" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O91" s="38" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1" s="15">
       <c r="A92" s="19" t="inlineStr">
@@ -6180,12 +6163,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G92" s="34" t="inlineStr">
+      <c r="G92" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H92" s="19" t="n"/>
+      <c r="H92" s="19" t="inlineStr">
+        <is>
+          <t>81996-1G100[이모빌라이저키, 2005.2.15~2009.12.10], 81996-1G000[칩 없음]</t>
+        </is>
+      </c>
       <c r="I92" s="19" t="n"/>
       <c r="J92" s="19" t="n"/>
       <c r="K92" s="19" t="n"/>
@@ -6196,11 +6183,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O92" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O92" s="38" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1" s="15">
       <c r="A93" s="19" t="inlineStr">
@@ -6233,12 +6216,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G93" s="34" t="inlineStr">
+      <c r="G93" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H93" s="19" t="n"/>
+      <c r="H93" s="19" t="inlineStr">
+        <is>
+          <t>81996-1G100[이모빌라이저키, 2005.2.15~2009.12.10], 81996-1G000[칩 없음]</t>
+        </is>
+      </c>
       <c r="I93" s="19" t="n"/>
       <c r="J93" s="19" t="n"/>
       <c r="K93" s="19" t="n"/>
@@ -6249,11 +6236,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O93" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O93" s="38" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1" s="15">
       <c r="A94" s="19" t="inlineStr">
@@ -6286,12 +6269,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G94" s="34" t="inlineStr">
+      <c r="G94" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H94" s="19" t="n"/>
+      <c r="H94" s="19" t="inlineStr">
+        <is>
+          <t>81996-1G100[이모빌라이저키, 2005.2.15~2009.12.10], 81996-1G000[칩 없음]</t>
+        </is>
+      </c>
       <c r="I94" s="19" t="n"/>
       <c r="J94" s="19" t="n"/>
       <c r="K94" s="19" t="n"/>
@@ -6302,11 +6289,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O94" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O94" s="38" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1" s="15">
       <c r="A95" s="19" t="inlineStr">
@@ -6339,12 +6322,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G95" s="34" t="inlineStr">
+      <c r="G95" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H95" s="19" t="n"/>
+      <c r="H95" s="19" t="inlineStr">
+        <is>
+          <t>81996-1G000[칩 없음]</t>
+        </is>
+      </c>
       <c r="I95" s="19" t="n"/>
       <c r="J95" s="19" t="n"/>
       <c r="K95" s="19" t="n"/>
@@ -6355,11 +6342,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O95" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O95" s="38" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="15">
       <c r="A96" s="19" t="inlineStr">
@@ -6441,7 +6424,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G97" s="34" t="inlineStr">
+      <c r="G97" s="37" t="inlineStr">
         <is>
           <t>ID6E-MA, ID46(PCF7952)</t>
         </is>
@@ -6457,11 +6440,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O97" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O97" s="38" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1" s="15">
       <c r="A98" s="19" t="inlineStr">
@@ -10936,12 +10915,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G176" s="34" t="inlineStr">
+      <c r="G176" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H176" s="19" t="n"/>
+      <c r="H176" s="19" t="inlineStr">
+        <is>
+          <t>81996-07020, 81996-07100</t>
+        </is>
+      </c>
       <c r="I176" s="19" t="n"/>
       <c r="J176" s="19" t="n"/>
       <c r="K176" s="19" t="n"/>
@@ -10952,11 +10935,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O176" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O176" s="38" t="n"/>
     </row>
     <row r="177" ht="15" customHeight="1" s="15">
       <c r="A177" s="19" t="inlineStr">
@@ -10989,12 +10968,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G177" s="34" t="inlineStr">
+      <c r="G177" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H177" s="19" t="n"/>
+      <c r="H177" s="19" t="inlineStr">
+        <is>
+          <t>81996-07020, 81996-07100</t>
+        </is>
+      </c>
       <c r="I177" s="19" t="n"/>
       <c r="J177" s="19" t="n"/>
       <c r="K177" s="19" t="n"/>
@@ -11005,11 +10988,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O177" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O177" s="38" t="n"/>
     </row>
     <row r="178" ht="15" customHeight="1" s="15">
       <c r="A178" s="19" t="inlineStr">
@@ -11042,12 +11021,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G178" s="34" t="inlineStr">
+      <c r="G178" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H178" s="19" t="n"/>
+      <c r="H178" s="19" t="inlineStr">
+        <is>
+          <t>81996-07020, 81996-07100</t>
+        </is>
+      </c>
       <c r="I178" s="19" t="n"/>
       <c r="J178" s="19" t="n"/>
       <c r="K178" s="19" t="n"/>
@@ -11058,11 +11041,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O178" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O178" s="38" t="n"/>
     </row>
     <row r="179" ht="15" customHeight="1" s="15">
       <c r="A179" s="19" t="inlineStr">
@@ -11095,12 +11074,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G179" s="34" t="inlineStr">
+      <c r="G179" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H179" s="19" t="n"/>
+      <c r="H179" s="19" t="inlineStr">
+        <is>
+          <t>81996-07020, 81996-07100</t>
+        </is>
+      </c>
       <c r="I179" s="19" t="n"/>
       <c r="J179" s="19" t="n"/>
       <c r="K179" s="19" t="n"/>
@@ -11111,11 +11094,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O179" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O179" s="38" t="n"/>
     </row>
     <row r="180" ht="15" customHeight="1" s="15">
       <c r="A180" s="19" t="inlineStr">
@@ -11148,12 +11127,16 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G180" s="34" t="inlineStr">
+      <c r="G180" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936AS)</t>
         </is>
       </c>
-      <c r="H180" s="19" t="n"/>
+      <c r="H180" s="19" t="inlineStr">
+        <is>
+          <t>81996-07020, 81996-07100</t>
+        </is>
+      </c>
       <c r="I180" s="19" t="n"/>
       <c r="J180" s="19" t="n"/>
       <c r="K180" s="19" t="n"/>
@@ -11164,11 +11147,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O180" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O180" s="38" t="n"/>
     </row>
     <row r="181" ht="15" customHeight="1" s="15">
       <c r="A181" s="19" t="inlineStr">
@@ -11609,24 +11588,24 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="D188" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E188" s="21" t="inlineStr">
+      <c r="D188" s="45" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="F188" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G188" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[TA], ID46[TA], ID6E-MA[JA, 자료 상충], ID75[JA, 자료 상충]</t>
+      <c r="E188" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F188" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G188" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[TA], ID46[TA], ID6E-MA[JA, 폴딩키], ID8A[JA, 스마트키]</t>
         </is>
       </c>
       <c r="H188" s="24" t="inlineStr">
@@ -11652,11 +11631,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O188" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O188" s="38" t="n"/>
     </row>
     <row r="189" ht="15" customHeight="1" s="15">
       <c r="A189" s="19" t="inlineStr">
@@ -11674,24 +11649,24 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="D189" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E189" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F189" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G189" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
+      <c r="D189" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E189" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F189" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G189" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[폴딩키], ID8A[스마트키]</t>
         </is>
       </c>
       <c r="H189" s="24" t="inlineStr">
@@ -11717,11 +11692,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O189" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O189" s="38" t="n"/>
     </row>
     <row r="190" ht="15" customHeight="1" s="15">
       <c r="A190" s="19" t="inlineStr">
@@ -11739,24 +11710,24 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D190" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E190" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F190" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G190" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
+      <c r="D190" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E190" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F190" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G190" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[폴딩키], ID8A[스마트키]</t>
         </is>
       </c>
       <c r="H190" s="24" t="inlineStr">
@@ -11782,11 +11753,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O190" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O190" s="38" t="n"/>
     </row>
     <row r="191" ht="15" customHeight="1" s="15">
       <c r="A191" s="19" t="inlineStr">
@@ -11804,24 +11771,24 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="D191" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E191" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F191" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G191" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
+      <c r="D191" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E191" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F191" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G191" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[폴딩키], ID8A[스마트키]</t>
         </is>
       </c>
       <c r="H191" s="24" t="inlineStr">
@@ -11847,11 +11814,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O191" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O191" s="38" t="n"/>
     </row>
     <row r="192" ht="15" customHeight="1" s="15">
       <c r="A192" s="19" t="inlineStr">
@@ -11869,24 +11832,24 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="D192" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E192" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F192" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G192" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
+      <c r="D192" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E192" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F192" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G192" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[폴딩키], ID8A[스마트키]</t>
         </is>
       </c>
       <c r="H192" s="24" t="inlineStr">
@@ -11912,11 +11875,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O192" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O192" s="38" t="n"/>
     </row>
     <row r="193" ht="15" customHeight="1" s="15">
       <c r="A193" s="19" t="inlineStr">
@@ -11934,24 +11893,24 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D193" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E193" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F193" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G193" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
+      <c r="D193" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E193" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F193" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G193" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[폴딩키], ID8A[스마트키]</t>
         </is>
       </c>
       <c r="H193" s="24" t="inlineStr">
@@ -11977,11 +11936,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O193" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O193" s="38" t="n"/>
     </row>
     <row r="194" ht="15" customHeight="1" s="15">
       <c r="A194" s="19" t="inlineStr">
@@ -11999,24 +11954,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D194" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E194" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F194" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G194" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
+      <c r="D194" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E194" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F194" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G194" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[폴딩키], ID8A[스마트키]</t>
         </is>
       </c>
       <c r="H194" s="24" t="inlineStr">
@@ -12042,11 +11997,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O194" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O194" s="38" t="n"/>
     </row>
     <row r="195" ht="15" customHeight="1" s="15">
       <c r="A195" s="19" t="inlineStr">
@@ -12064,24 +12015,24 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D195" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E195" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F195" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G195" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
+      <c r="D195" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E195" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F195" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G195" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[폴딩키], ID8A[스마트키]</t>
         </is>
       </c>
       <c r="H195" s="24" t="inlineStr">
@@ -12107,11 +12058,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O195" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O195" s="38" t="n"/>
     </row>
     <row r="196" ht="15" customHeight="1" s="15">
       <c r="A196" s="19" t="inlineStr">
@@ -12129,24 +12076,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D196" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E196" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F196" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G196" s="34" t="inlineStr">
-        <is>
-          <t>ID6E-MA[자료 상충], ID75[자료 상충]</t>
+      <c r="D196" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E196" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F196" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G196" s="37" t="inlineStr">
+        <is>
+          <t>ID6E-MA[폴딩키], ID8A[스마트키]</t>
         </is>
       </c>
       <c r="H196" s="24" t="inlineStr">
@@ -12172,11 +12119,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O196" s="35" t="inlineStr">
-        <is>
-          <t>JA 칩 자료 상충 — ID6E-MA(DST80) 표기와 ID75(Texas AES) 표기가 갈림</t>
-        </is>
-      </c>
+      <c r="O196" s="38" t="n"/>
     </row>
     <row r="197" ht="15" customHeight="1" s="15">
       <c r="A197" s="24" t="inlineStr">
@@ -12353,24 +12296,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D200" s="25" t="inlineStr">
+      <c r="D200" s="44" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E200" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F200" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G200" s="34" t="inlineStr">
-        <is>
-          <t>ID4A[추정]</t>
+      <c r="E200" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F200" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G200" s="37" t="inlineStr">
+        <is>
+          <t>ID4A</t>
         </is>
       </c>
       <c r="H200" s="19" t="n"/>
@@ -12388,11 +12331,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O200" s="34" t="inlineStr">
-        <is>
-          <t>95440-EZ000 칩 표기 원문 없음 — 같은 시기 K4(95440-GG000) HITAG AES 4A 기준 추정</t>
-        </is>
-      </c>
+      <c r="O200" s="37" t="n"/>
     </row>
     <row r="201" ht="15" customHeight="1" s="15">
       <c r="A201" s="24" t="inlineStr">
@@ -12410,24 +12349,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D201" s="25" t="inlineStr">
+      <c r="D201" s="44" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E201" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F201" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G201" s="34" t="inlineStr">
-        <is>
-          <t>ID4A[추정]</t>
+      <c r="E201" s="45" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F201" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G201" s="37" t="inlineStr">
+        <is>
+          <t>ID4A</t>
         </is>
       </c>
       <c r="H201" s="19" t="n"/>
@@ -12445,11 +12384,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O201" s="34" t="inlineStr">
-        <is>
-          <t>95440-EZ000 칩 표기 원문 없음 — 같은 시기 K4(95440-GG000) HITAG AES 4A 기준 추정</t>
-        </is>
-      </c>
+      <c r="O201" s="37" t="n"/>
     </row>
     <row r="202" ht="15" customHeight="1" s="15">
       <c r="A202" s="24" t="inlineStr">
@@ -13579,23 +13514,23 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G223" s="34" t="inlineStr">
+      <c r="G223" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H223" s="19" t="n"/>
+      <c r="H223" s="19" t="inlineStr">
+        <is>
+          <t>81996-2F010[2004.6~]</t>
+        </is>
+      </c>
       <c r="I223" s="19" t="n"/>
       <c r="J223" s="19" t="n"/>
       <c r="K223" s="19" t="n"/>
       <c r="L223" s="19" t="n"/>
       <c r="M223" s="38" t="n"/>
       <c r="N223" s="19" t="n"/>
-      <c r="O223" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O223" s="38" t="n"/>
     </row>
     <row r="224" ht="15" customHeight="1" s="15">
       <c r="A224" s="19" t="inlineStr">
@@ -13628,23 +13563,23 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G224" s="34" t="inlineStr">
+      <c r="G224" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H224" s="19" t="n"/>
+      <c r="H224" s="19" t="inlineStr">
+        <is>
+          <t>81996-2F010[2004.6~]</t>
+        </is>
+      </c>
       <c r="I224" s="19" t="n"/>
       <c r="J224" s="19" t="n"/>
       <c r="K224" s="19" t="n"/>
       <c r="L224" s="19" t="n"/>
       <c r="M224" s="38" t="n"/>
       <c r="N224" s="19" t="n"/>
-      <c r="O224" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O224" s="38" t="n"/>
     </row>
     <row r="225" ht="15" customHeight="1" s="15">
       <c r="A225" s="19" t="inlineStr">
@@ -13677,23 +13612,23 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G225" s="34" t="inlineStr">
+      <c r="G225" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H225" s="19" t="n"/>
+      <c r="H225" s="19" t="inlineStr">
+        <is>
+          <t>81996-2F010[2004.6~]</t>
+        </is>
+      </c>
       <c r="I225" s="19" t="n"/>
       <c r="J225" s="19" t="n"/>
       <c r="K225" s="19" t="n"/>
       <c r="L225" s="19" t="n"/>
       <c r="M225" s="38" t="n"/>
       <c r="N225" s="19" t="n"/>
-      <c r="O225" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O225" s="38" t="n"/>
     </row>
     <row r="226" ht="15" customHeight="1" s="15">
       <c r="A226" s="19" t="inlineStr">
@@ -13726,23 +13661,23 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G226" s="34" t="inlineStr">
+      <c r="G226" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H226" s="19" t="n"/>
+      <c r="H226" s="19" t="inlineStr">
+        <is>
+          <t>81996-2F010[2004.6~]</t>
+        </is>
+      </c>
       <c r="I226" s="19" t="n"/>
       <c r="J226" s="19" t="n"/>
       <c r="K226" s="19" t="n"/>
       <c r="L226" s="19" t="n"/>
       <c r="M226" s="38" t="n"/>
       <c r="N226" s="19" t="n"/>
-      <c r="O226" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O226" s="38" t="n"/>
     </row>
     <row r="227" ht="15" customHeight="1" s="15">
       <c r="A227" s="19" t="inlineStr">
@@ -13775,23 +13710,23 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G227" s="34" t="inlineStr">
+      <c r="G227" s="37" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
       </c>
-      <c r="H227" s="19" t="n"/>
+      <c r="H227" s="19" t="inlineStr">
+        <is>
+          <t>81996-2F010[2004.6~]</t>
+        </is>
+      </c>
       <c r="I227" s="19" t="n"/>
       <c r="J227" s="19" t="n"/>
       <c r="K227" s="19" t="n"/>
       <c r="L227" s="19" t="n"/>
       <c r="M227" s="38" t="n"/>
       <c r="N227" s="19" t="n"/>
-      <c r="O227" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O227" s="38" t="n"/>
     </row>
     <row r="228" ht="15" customHeight="1" s="15">
       <c r="A228" s="19" t="inlineStr">
@@ -13976,24 +13911,24 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="D231" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E231" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F231" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G231" s="34" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[플립키], ID6E-MA[일부 자료]</t>
+      <c r="D231" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E231" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F231" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G231" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[플립키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H231" s="24" t="inlineStr">
@@ -14019,11 +13954,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O231" s="35" t="inlineStr">
-        <is>
-          <t>플립키 ID6E-MA는 일부 자료에만 나옴(국제 판매처는 플립키 95430-3W200 ID46 PCF7936)</t>
-        </is>
-      </c>
+      <c r="O231" s="38" t="n"/>
     </row>
     <row r="232" ht="15" customHeight="1" s="15">
       <c r="A232" s="19" t="inlineStr">
@@ -14041,24 +13972,24 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="D232" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E232" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F232" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G232" s="34" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[플립키], ID6E-MA[일부 자료]</t>
+      <c r="D232" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E232" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F232" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G232" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[플립키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H232" s="24" t="inlineStr">
@@ -14084,11 +14015,7 @@
           <t>현대모비스 부품몰(파츠로/헬로우카 등) 실제 국내 정품 판매 페이지</t>
         </is>
       </c>
-      <c r="O232" s="35" t="inlineStr">
-        <is>
-          <t>플립키 ID6E-MA는 일부 자료에만 나옴(국제 판매처는 플립키 95430-3W200 ID46 PCF7936)</t>
-        </is>
-      </c>
+      <c r="O232" s="38" t="n"/>
     </row>
     <row r="233" ht="15" customHeight="1" s="15">
       <c r="A233" s="19" t="inlineStr">
@@ -14858,38 +14785,38 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="D245" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E245" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F245" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G245" s="24" t="inlineStr">
-        <is>
-          <t>ID46</t>
-        </is>
-      </c>
-      <c r="H245" s="19" t="n"/>
+      <c r="D245" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E245" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F245" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G245" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
+        </is>
+      </c>
+      <c r="H245" s="19" t="inlineStr">
+        <is>
+          <t>81996-3EG00, 81996-3EC00[뉴 쏘렌토]</t>
+        </is>
+      </c>
       <c r="I245" s="19" t="n"/>
       <c r="J245" s="19" t="n"/>
       <c r="K245" s="19" t="n"/>
       <c r="L245" s="19" t="n"/>
-      <c r="M245" s="19" t="n"/>
+      <c r="M245" s="38" t="n"/>
       <c r="N245" s="19" t="n"/>
-      <c r="O245" s="23" t="inlineStr">
-        <is>
-          <t>쏘렌토(BL) 국내 출시(2002.2). 칩: transpondery.com 카탈로그 'KIA SORENTO 2002-2009: PHILIPS Crypto 2 / ID46 / Hitag 2' — 이전 2002~2005 ID60·2006~ ID46 구분은 근거 없는 추정이라 정정(북미형 BL은 트랜스폰더 없는 기계식 키인 경우 있음)</t>
-        </is>
-      </c>
+      <c r="O245" s="38" t="n"/>
     </row>
     <row r="246" ht="15" customHeight="1" s="15">
       <c r="A246" s="19" t="inlineStr">
@@ -14907,38 +14834,38 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="D246" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E246" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F246" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G246" s="34" t="inlineStr">
-        <is>
-          <t>ID46</t>
-        </is>
-      </c>
-      <c r="H246" s="19" t="n"/>
+      <c r="D246" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E246" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F246" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G246" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
+        </is>
+      </c>
+      <c r="H246" s="19" t="inlineStr">
+        <is>
+          <t>81996-3EG00, 81996-3EC00[뉴 쏘렌토]</t>
+        </is>
+      </c>
       <c r="I246" s="19" t="n"/>
       <c r="J246" s="19" t="n"/>
       <c r="K246" s="19" t="n"/>
       <c r="L246" s="19" t="n"/>
       <c r="M246" s="38" t="n"/>
       <c r="N246" s="19" t="n"/>
-      <c r="O246" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O246" s="38" t="n"/>
     </row>
     <row r="247" ht="15" customHeight="1" s="15">
       <c r="A247" s="19" t="inlineStr">
@@ -14956,38 +14883,38 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="D247" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E247" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F247" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G247" s="34" t="inlineStr">
-        <is>
-          <t>ID46</t>
-        </is>
-      </c>
-      <c r="H247" s="19" t="n"/>
+      <c r="D247" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E247" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F247" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G247" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
+        </is>
+      </c>
+      <c r="H247" s="19" t="inlineStr">
+        <is>
+          <t>81996-3EG00, 81996-3EC00[뉴 쏘렌토]</t>
+        </is>
+      </c>
       <c r="I247" s="19" t="n"/>
       <c r="J247" s="19" t="n"/>
       <c r="K247" s="19" t="n"/>
       <c r="L247" s="19" t="n"/>
       <c r="M247" s="38" t="n"/>
       <c r="N247" s="19" t="n"/>
-      <c r="O247" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O247" s="38" t="n"/>
     </row>
     <row r="248" ht="15" customHeight="1" s="15">
       <c r="A248" s="19" t="inlineStr">
@@ -15005,38 +14932,38 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="D248" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E248" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F248" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G248" s="34" t="inlineStr">
-        <is>
-          <t>ID46</t>
-        </is>
-      </c>
-      <c r="H248" s="19" t="n"/>
+      <c r="D248" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E248" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F248" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G248" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
+        </is>
+      </c>
+      <c r="H248" s="19" t="inlineStr">
+        <is>
+          <t>81996-3EG00, 81996-3EC00[뉴 쏘렌토]</t>
+        </is>
+      </c>
       <c r="I248" s="19" t="n"/>
       <c r="J248" s="19" t="n"/>
       <c r="K248" s="19" t="n"/>
       <c r="L248" s="19" t="n"/>
       <c r="M248" s="38" t="n"/>
       <c r="N248" s="19" t="n"/>
-      <c r="O248" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O248" s="38" t="n"/>
     </row>
     <row r="249" ht="15" customHeight="1" s="15">
       <c r="A249" s="19" t="inlineStr">
@@ -15054,38 +14981,38 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="D249" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E249" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F249" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G249" s="34" t="inlineStr">
-        <is>
-          <t>ID46</t>
-        </is>
-      </c>
-      <c r="H249" s="19" t="n"/>
+      <c r="D249" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E249" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F249" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G249" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
+        </is>
+      </c>
+      <c r="H249" s="19" t="inlineStr">
+        <is>
+          <t>81996-3EG00, 81996-3EC00[뉴 쏘렌토]</t>
+        </is>
+      </c>
       <c r="I249" s="19" t="n"/>
       <c r="J249" s="19" t="n"/>
       <c r="K249" s="19" t="n"/>
       <c r="L249" s="19" t="n"/>
       <c r="M249" s="38" t="n"/>
       <c r="N249" s="19" t="n"/>
-      <c r="O249" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O249" s="38" t="n"/>
     </row>
     <row r="250" ht="15" customHeight="1" s="15">
       <c r="A250" s="19" t="inlineStr">
@@ -15103,38 +15030,38 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="D250" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E250" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F250" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G250" s="34" t="inlineStr">
-        <is>
-          <t>ID46</t>
-        </is>
-      </c>
-      <c r="H250" s="19" t="n"/>
+      <c r="D250" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E250" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F250" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G250" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
+        </is>
+      </c>
+      <c r="H250" s="19" t="inlineStr">
+        <is>
+          <t>81996-3EG00, 81996-3EC00[뉴 쏘렌토]</t>
+        </is>
+      </c>
       <c r="I250" s="19" t="n"/>
       <c r="J250" s="19" t="n"/>
       <c r="K250" s="19" t="n"/>
       <c r="L250" s="19" t="n"/>
       <c r="M250" s="38" t="n"/>
       <c r="N250" s="19" t="n"/>
-      <c r="O250" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O250" s="38" t="n"/>
     </row>
     <row r="251" ht="15" customHeight="1" s="15">
       <c r="A251" s="19" t="inlineStr">
@@ -15152,38 +15079,38 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="D251" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E251" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F251" s="22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G251" s="34" t="inlineStr">
-        <is>
-          <t>ID46</t>
-        </is>
-      </c>
-      <c r="H251" s="19" t="n"/>
+      <c r="D251" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E251" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F251" s="43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G251" s="37" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
+        </is>
+      </c>
+      <c r="H251" s="19" t="inlineStr">
+        <is>
+          <t>81996-3EG00, 81996-3EC00[뉴 쏘렌토]</t>
+        </is>
+      </c>
       <c r="I251" s="19" t="n"/>
       <c r="J251" s="19" t="n"/>
       <c r="K251" s="19" t="n"/>
       <c r="L251" s="19" t="n"/>
       <c r="M251" s="38" t="n"/>
       <c r="N251" s="19" t="n"/>
-      <c r="O251" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O251" s="38" t="n"/>
     </row>
     <row r="252" ht="15" customHeight="1" s="15">
       <c r="A252" s="19" t="inlineStr">
@@ -18396,7 +18323,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G308" s="34" t="inlineStr">
+      <c r="G308" s="37" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18412,11 +18339,7 @@
       </c>
       <c r="M308" s="38" t="n"/>
       <c r="N308" s="19" t="n"/>
-      <c r="O308" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O308" s="38" t="n"/>
     </row>
     <row r="309" ht="15" customHeight="1" s="15">
       <c r="A309" s="19" t="inlineStr">
@@ -18449,7 +18372,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G309" s="34" t="inlineStr">
+      <c r="G309" s="37" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18465,11 +18388,7 @@
       </c>
       <c r="M309" s="38" t="n"/>
       <c r="N309" s="19" t="n"/>
-      <c r="O309" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O309" s="38" t="n"/>
     </row>
     <row r="310" ht="15" customHeight="1" s="15">
       <c r="A310" s="19" t="inlineStr">
@@ -18502,7 +18421,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G310" s="34" t="inlineStr">
+      <c r="G310" s="37" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18522,11 +18441,7 @@
       </c>
       <c r="M310" s="38" t="n"/>
       <c r="N310" s="19" t="n"/>
-      <c r="O310" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O310" s="38" t="n"/>
     </row>
     <row r="311" ht="15" customHeight="1" s="15">
       <c r="A311" s="19" t="inlineStr">
@@ -18559,7 +18474,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G311" s="34" t="inlineStr">
+      <c r="G311" s="37" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -18579,11 +18494,7 @@
       </c>
       <c r="M311" s="38" t="n"/>
       <c r="N311" s="19" t="n"/>
-      <c r="O311" s="35" t="inlineStr">
-        <is>
-          <t>국내 부품번호·칩 원문 없음 — 해외 트랜스폰더 카탈로그의 칩 기준</t>
-        </is>
-      </c>
+      <c r="O311" s="38" t="n"/>
     </row>
     <row r="312" ht="15" customHeight="1" s="15">
       <c r="A312" s="19" t="inlineStr">
@@ -22615,7 +22526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A207"/>
+  <dimension ref="A1:A221"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.2"/>
   <cols>
     <col width="118" customWidth="1" style="15" min="1" max="1"/>
@@ -22716,1337 +22627,1431 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="n"/>
+      <c r="A16" s="49" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="48" t="inlineStr">
+      <c r="A18" s="49" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="A19" s="49" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="49" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="49" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="48" t="n"/>
+      <c r="A24" s="49" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="48" t="inlineStr">
+      <c r="A25" s="49" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="49" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="48" t="inlineStr">
+      <c r="A27" s="49" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="48" t="inlineStr">
+      <c r="A28" s="49" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="48" t="inlineStr">
+      <c r="A29" s="49" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="48" t="inlineStr">
+      <c r="A30" s="49" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="inlineStr">
+      <c r="A31" s="49" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="49" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="n"/>
+      <c r="A33" s="49" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="48" t="inlineStr">
+      <c r="A34" s="49" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="48" t="inlineStr">
+      <c r="A35" s="49" t="inlineStr">
         <is>
           <t>- K3 (Forte, YD 페이스리프트) 2016: A7600 칩은 Lonsdor 8A 스마트키 PCB 지원 차종(K3 2016-2018)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="48" t="inlineStr">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t>- K3 (Forte, YD 페이스리프트) 2017: 국내 현대모비스 원문 확인</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="48" t="inlineStr">
+      <c r="A37" s="49" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD) 2021: 더 뉴 K3(BD PE) 출시(2021.4). 95440-M6800은 한국 시장용 정품 HITAG AES ID4A(NCF29A1M)로 다수 판매처(mk3·abkeys·americankeysupply) 일치 확인 → 기존 'ID8A/ID47 미확정' 해소(PE 이전은 ID8A, PE 이후는 ID4A)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="48" t="inlineStr">
+      <c r="A38" s="49" t="inlineStr">
         <is>
           <t>- 스토닉 2017: 스토닉 국내 출시(2017.6.21) — 프라이드(UB)와 같은 플랫폼 공유 크로스오버. 국제 판매처(gskeyae.com) 확인: '2017-2018 KIA Stonic ... 8A Texas Crypto 128-bits AES' — 이전에 'ID47 추정'이라고 했던 건 정정함</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="48" t="inlineStr">
+      <c r="A39" s="49" t="inlineStr">
         <is>
           <t>- 쏘울 (Soul, PS) 2014: 칩: 95440-B2000·B2AA0 한국 시장용 정품 8A Texas Crypto 128bit AES, 4버튼(mk3·abkeys·remotesandkeys) — 이전 'ID47 추정'은 정정</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="48" t="inlineStr">
+      <c r="A40" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2016: 국제 판매처(go-parts.com, americankeysupply) 확인: Hitag3 ID47 - 이전에 ID6E-MA(DST80) 추정이라고 했던 건 정정함</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="48" t="inlineStr">
+      <c r="A41" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, MQ4) 2021: 칩: 95440-P2000(5버튼)·P2200(7버튼)·P2AD0(7버튼) 모두 정품 HITAG AES ID4A(mk3·abkeys·royalkeysupply) — 이전 '추정' 해소</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="48" t="inlineStr">
+      <c r="A42" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2021: 이전 '적용 시점 추정' 해소: G5025는 원문상 22년형</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="49" t="inlineStr">
         <is>
           <t>- 레이 2023: 95440-A3600(2022.8.31~)은 DST-AES ID6A 4버튼, 2023-2024 레이 적용(mk3·abkeys·vvdi)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="48" t="n"/>
+      <c r="A44" s="49" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="48" t="inlineStr">
+      <c r="A45" s="49" t="inlineStr">
         <is>
           <t>※ 연식별 참고 메모 (예전 비고 칸 내용 — 색 없는 행이라 비고에서 옮김)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="48" t="inlineStr">
+      <c r="A46" s="49" t="inlineStr">
         <is>
           <t>- 옵티마 (Optima, MS) 2005(단종): 옵티마 국내 마지막 연식(2005.10 단종, 로체로 세대교체). 국제 판매처(abkeys.com) 확인: PN 81996-3C010, 4D-60/HYN7R, 'KIA OPTIMA 2000-2005' 명시 — 나무위키 확인: EF쏘나타와 완전히 동일한 모델(플랫폼·전자장비 100% 공유)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="48" t="inlineStr">
+      <c r="A47" s="49" t="inlineStr">
         <is>
           <t>- 로체 (Optima, MG) 2005: 로체 국내 출시(2005.10). 국내 현대모비스(hellowcar) 스마트키 원문: 954402G000[~2008.5.28, 블랭킹 819962G020] → 954401M010[2008.8.28~2009.8.10, 819962G520] → 954402G100[2010.8.10~, 819962G030]. 2009.8.10~2010.8.10 사이 품번은 원문에 없음</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="48" t="inlineStr">
+      <c r="A48" s="49" t="inlineStr">
         <is>
           <t>- 로체 (Optima, MG) 2008: 국내 현대모비스 확인 — 2008년 안에 폴딩키·스마트키 부품 모두 전환</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="48" t="inlineStr">
+      <c r="A49" s="49" t="inlineStr">
         <is>
           <t>- 로체 (Optima, MG) 2009: 국내 현대모비스 확인 — 폴딩키 날짜 구간이 일부 겹쳐 표기됨(트림별 차이 가능성), 원문 그대로 병기</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="48" t="inlineStr">
+      <c r="A50" s="49" t="inlineStr">
         <is>
           <t>- 로체 (Optima, MG) 2010(단종): 로체 마지막 연식(2010) — K5로 세대교체. 국내 현대모비스(hellowcar) 스마트키 원문: 954402G000[~2008.5.28, 블랭킹 819962G020] → 954401M010[2008.8.28~2009.8.10, 819962G520] → 954402G100[2010.8.10~, 819962G030]. 2009.8.10~2010.8.10 사이 품번은 원문에 없음</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="48" t="inlineStr">
+      <c r="A51" s="49" t="inlineStr">
         <is>
           <t>- 포르테 (Forte, TD 세단) 2008: 포르테 세단(TD) 국내 출시(2008.8.21) — 이 해엔 세단만 있었고 쿠페는 아직 출시 전. 출시 당시 디럭스 트림은 '폴딩타입 무선도어 리모컨키' 기본(다나와 2008년형 트림표). 버튼시동 스마트키가 어느 트림부터 기본인지와 폴딩키 부품번호는 국내 원문에서 확인 못함</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="48" t="inlineStr">
+      <c r="A52" s="49" t="inlineStr">
         <is>
           <t>- K3 (Forte, YD/BD) 2018: K3(BD) 완전변경 출시(2018.2). 국내 현대모비스 원문: BD 스마트키 M6000[2018.1.8~8.30] → M6011[2018.8.30~2021.4.26] · M6501[2018.9.18~2021.3.24] → M6800[2021.4.5~2024.2.8] → M6801[2024.2.8~], 블레이드 81996M6020. BD 초기 스마트키(M6000/M6011/M6501, FCC CQOFD00430) 칩은 정품 기준 DST-AES ID8A(abkeys·tlkeys)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="48" t="inlineStr">
+      <c r="A53" s="49" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD) 2020: 2021년형(2020년 출시)부터 버튼시동 스마트키 전 트림 기본(모터그래프·엔카)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="48" t="inlineStr">
+      <c r="A54" s="49" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD 페이스리프트) 2022: 스마트키 전 트림 기본화 이후 폴딩키(M6400)의 적용 대상은 원문 미확인</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="48" t="inlineStr">
+      <c r="A55" s="49" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD PE) 2024(단종): K3 국내 최종 연식 — 2024년 7월 완전 단종. 후속 K4는 국내 미출시(해외 전략형 모델), 국내 준중형 세단 수요는 셀토스·EV3·EV4로 대체됨</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="48" t="inlineStr">
+      <c r="A56" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, TF) 2010: 국내 현대모비스(hellowcar) 폴딩키 원문: TF 954302T500[~2012.7.6, 블랭킹 819962L000] → 954302T501[2012.7.6~, 819962L001] / JF 954302T570(블랭킹 81996A4000)·95430D4010 / DL3 95430L2000·L2010(블랭킹 81996L2000). 이전에 TF에 넣었던 2T570은 원문상 JF용이라 이동</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="48" t="inlineStr">
+      <c r="A57" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, TF) 2011: K5 하이브리드(TFE) 출시(2011)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="48" t="inlineStr">
+      <c r="A58" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, TF) 2013: 국내 현대모비스 확인 — 2013.6.10 기준 스마트키·비상키 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="48" t="inlineStr">
+      <c r="A59" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, TF/JF) 2015: K5(JF, 올 뉴 K5) 완전변경 출시(2015)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="48" t="inlineStr">
+      <c r="A60" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, JF) 2017: 더 뉴 K5(JF 페이스리프트) 출시(2017)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="48" t="inlineStr">
+      <c r="A61" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, JF) 2018: 더뉴K5 하이브리드 2세대(JFE) 출시(2018)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="48" t="inlineStr">
+      <c r="A62" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, JF) 2019: JF 마지막 연식</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="48" t="inlineStr">
+      <c r="A63" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, JF/DL3) 2019: K5(DL3) 완전변경 출시(2019.9)로 같은 해 전환 — 하이브리드 3세대(DL3KH)도 2019년 출시</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="48" t="inlineStr">
+      <c r="A64" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, DL3) 2020: 국내 현대모비스(hellowcar) 원문: L3010·L2200은 연식 라벨 없는 초기 품번, L2320·L2300은 21년형, L2420·L2400은 22년형</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="48" t="inlineStr">
+      <c r="A65" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, DL3/DL3 페이스리프트) 2023: 더 뉴 K5(DL3 페이스리프트) 출시(2023.9)로 전환되는 해 — 95440-L2520은 하이브리드와 공용</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="48" t="inlineStr">
+      <c r="A66" s="49" t="inlineStr">
         <is>
           <t>- K5 (Optima, DL3 페이스리프트) 2026: 국내 현대모비스(hellowcar) 원문상 PE 스마트키 L2500·L2510·L2520은 종료일 없는 현행 품번</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="48" t="inlineStr">
+      <c r="A67" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2009: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="48" t="inlineStr">
+      <c r="A68" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2010: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="48" t="inlineStr">
+      <c r="A69" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2011: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="48" t="inlineStr">
+      <c r="A70" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2012: 국내 현대모비스 확인 — 2012.11.5 기준 스마트키 전환. 카드키 원문: 954403R800[2012.10.30~2013.2.28, 블레이드 819963T100] → 954403R801[2013.2.28~2015.12.31] → 95443F6000[2015.12.9~2019.6.27, 블레이드 81996F6110] → 95443F6010[2019.5.30~]</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="48" t="inlineStr">
+      <c r="A71" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2013: 이전에 VG 카드키 블레이드를 81996-F6110으로, 카드키에 95443-F6000을 적었으나 둘 다 YG용이라 정정(VG 카드키 블레이드는 819963T100)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="48" t="inlineStr">
+      <c r="A72" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2015: K7(YG) 완전변경 출시(2016.1)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="48" t="inlineStr">
+      <c r="A73" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, YG) 2016: 국내 현대모비스 확인 — 이모빌라이저 모듈(95420D4000)은 포터2·그랜드스타렉스와 공유</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="48" t="inlineStr">
+      <c r="A74" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, YG) 2019: 'K7 프리미어' 페이스리프트(2019.6)로 전환되는 해. 이전에 81996-F6110을 프리미어 스마트키 블레이드로 적었으나 원문상 카드키 블레이드라 정정(F6510 스마트키 블레이드는 원문 미확인). 스마트키 모듈(제어기) 95480-F6500</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="48" t="inlineStr">
+      <c r="A75" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, YG 프리미어) 2020: 스마트키 모듈(제어기): 95480-F6500</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="48" t="inlineStr">
+      <c r="A76" s="49" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, YG 프리미어) 2021(단종): K7 국내 마지막 연식(2021.1 단종) — 후속 K8으로 이어짐. 스마트키 모듈: 95480-F6500(2019.6-2021.4 적용 확인)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="48" t="inlineStr">
+      <c r="A77" s="49" t="inlineStr">
         <is>
           <t>- K8 (GL3) 2021: K8 국내 출시(2021.4). 국내 현대모비스(hellowcar) 원문: L8000(주차보조X)/L8010(주차보조O)은 ~2024.2.13, 이후 L8001/L8011로 전환. 블레이드 S9000=주차보조X, L2020=주차보조O, 폴딩키용 81996-L2000</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="48" t="inlineStr">
+      <c r="A78" s="49" t="inlineStr">
         <is>
           <t>- K8 (GL3/GL3 페이스리프트) 2024: 국내 현대모비스(hellowcar): 2024.2.13은 초기형 L8000·L8010 → L8001·L8011 품번 개정일이고, 페이스리프트(2024.8.9 공개, 위키백과)부터 L8500·L8510·L8520·L8530 적용 — 이전에 2.13을 페이스리프트 전환일로 적었던 것 정정. NFC 카드키 AT954AP000·GZ954AP000(K8GL3/EV6/스포티지NQ5/쏘렌토MQ4/카니발KA4 공용 리스팅)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="48" t="inlineStr">
+      <c r="A79" s="49" t="inlineStr">
         <is>
           <t>- K8 (GL3 페이스리프트) 2026: 원문상 PE 스마트키 4종은 종료일 없는 현행 품번</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="48" t="inlineStr">
+      <c r="A80" s="49" t="inlineStr">
         <is>
           <t>- K9 (K900/Quoris, KH) 2012: K9(KH) 국내 출시(2012.3.27). 국내 현대모비스(hellowcar) 원문: 스마트키 954403T200[2012.3.27~2017.12.30]→819963T000, 카드키 954433T000[~2013.7.1, 버튼X]→954433T100[2013.7.1~2014.11.15]→954433T200[2014.11.10~2017.12.30, 버튼X], 카드키 블레이드 819963T100</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="48" t="inlineStr">
+      <c r="A81" s="49" t="inlineStr">
         <is>
           <t>- K9 (K900/Quoris, KH) 2013: 국내 현대모비스(hellowcar) 원문: 3T200[2012.3.27~2017.12.30], 3T300[2013.9.1~2014.1.1]. 카드키 날짜도 원문 확인</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="48" t="inlineStr">
+      <c r="A82" s="49" t="inlineStr">
         <is>
           <t>- K9 (K900/Quoris, KH) 2016: 이전에 2016년 카드키 블레이드를 81996-3T200으로 적었으나 원문상 카드키 블레이드는 819963T100이라 정정</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="48" t="inlineStr">
+      <c r="A83" s="49" t="inlineStr">
         <is>
           <t>- K9 (K900/Quoris, KH/RJ) 2018: K9(RJ, '더 K9') 완전변경 출시(2018.4)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="48" t="inlineStr">
+      <c r="A84" s="49" t="inlineStr">
         <is>
           <t>- K9 (K900, RJ) 2021: 국내 현대모비스 확인 — 2021.5.21 기준 '더뉴 K9'로 부품 전환</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="48" t="inlineStr">
+      <c r="A85" s="49" t="inlineStr">
         <is>
           <t>- K9 (K900, RJ) 2025: 국내 현대모비스(hellowcar) 원문: 'K9RJ [2021.5.21 이후~] 95440J6610·J6600·81996J6000·J6100' — 종료일 없는 현행 품번</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="48" t="inlineStr">
+      <c r="A86" s="49" t="inlineStr">
         <is>
           <t>- 프라이드 JB 2005: 프라이드(JB) 국내 출시(2005.4.7) — 리오(BC) 후속, 국내 차명이 '프라이드'로 부활. 기본트림(LX)은 무선도어리모콘키만 제공</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="48" t="inlineStr">
+      <c r="A87" s="49" t="inlineStr">
         <is>
           <t>- 프라이드 JB/UB 2011: 올 뉴 프라이드(UB) 완전변경 출시(2011.9.28)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="48" t="inlineStr">
+      <c r="A88" s="49" t="inlineStr">
         <is>
           <t>- 프라이드 UB 2013: 국내 현대모비스 확인</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="48" t="inlineStr">
+      <c r="A89" s="49" t="inlineStr">
         <is>
           <t>- 프라이드 UB (더 뉴 프라이드) 2014: 더 뉴 프라이드 페이스리프트(2014.12) 출시. 국내 현대모비스(hellowcar) 재확인 — 비상키 접두사가 81996이 아니라 81999인 경우가 2개 있어서 정정함</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="48" t="inlineStr">
+      <c r="A90" s="49" t="inlineStr">
         <is>
           <t>- 프라이드 UB (더 뉴 프라이드) 2017(단종): 프라이드 국내 마지막 연식(2017.9 단종) — 4세대(리오 YB)는 국내 출시가 백지화되고 같은 플랫폼의 크로스오버 스토닉(SP2)으로 대체, 국내 후속 없음(위키백과 확인)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="48" t="inlineStr">
+      <c r="A91" s="49" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2004: 국제 판매처(remotesandkeys.com, key4.com) 확인: PN 81996-3FA10, ILCO KK7-PT, 4D60 — 리모컨 없는 막대형 키(2003-2006 공용)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="48" t="inlineStr">
+      <c r="A92" s="49" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2005: 국제 판매처 확인 — 막대형 키</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="48" t="inlineStr">
+      <c r="A93" s="49" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2006: 국제 판매처 확인 — 막대형 키</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="48" t="inlineStr">
+      <c r="A94" s="49" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2007: 국제 판매처(remotesandkeys.com) 확인: PN 81996-3F050, ILCO KK9-PT, ID46 — 리모컨 없는 막대형 키</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="48" t="inlineStr">
+      <c r="A95" s="49" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2008: 국제 판매처 확인 — 막대형 키</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="48" t="inlineStr">
+      <c r="A96" s="49" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH 프리미엄) 2009: 오피러스 프리미엄 페이스리프트(2009.5) 출시 — 국내 현대모비스 확인</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="48" t="inlineStr">
+      <c r="A97" s="49" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH 프리미엄) 2012(단종): 오피러스 국내 마지막 연식(2012.5) — K7(Cadenza)로 세대교체, 직접적 후속 없음</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="48" t="inlineStr">
+      <c r="A98" s="49" t="inlineStr">
         <is>
           <t>- 스팅어 (Stinger, CK) 2017: 스팅어 국내 출시(2017.5) — 제네시스 G70(IK)와 플랫폼 공유</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="48" t="inlineStr">
+      <c r="A99" s="49" t="inlineStr">
         <is>
           <t>- 스팅어 (Stinger, CK) 2018: 국내 판매처(모터스K) 확인: 2018년 7월 이후 생산된 19년형은 95440-J5200이 맞지 않을 수 있고 95440-J5210 적용. 국내 현대모비스(hellowcar): J5200·J5210은 ~2020.7.28, 이후 J5700·J5710, 블레이드 81996J5000</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="48" t="inlineStr">
+      <c r="A100" s="49" t="inlineStr">
         <is>
           <t>- 스팅어 (Stinger, CK) 2020: 국내 현대모비스 확인 — 2020.7.28 기준 페이스리프트 부품 전환</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="48" t="inlineStr">
+      <c r="A101" s="49" t="inlineStr">
         <is>
           <t>- 스팅어 (Stinger, CK 페이스리프트) 2023(단종): 스팅어 국내외 단종(2023.4) — 직접적 후속 없음</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="48" t="inlineStr">
+      <c r="A102" s="49" t="inlineStr">
         <is>
           <t>- 스토닉 2020: 페이스리프트('더 뉴 스토닉') 출시(2020)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="48" t="inlineStr">
+      <c r="A103" s="49" t="inlineStr">
         <is>
           <t>- 스토닉 2023: 생산지 이관(광명→서산 동희오토), 국내 부품번호는 초기형과 동일 계열로 확인, 페이스리프트 이후 세부 개정 여부는 미확인</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="48" t="inlineStr">
+      <c r="A104" s="49" t="inlineStr">
         <is>
           <t>- 스토닉 2024: 국내 판매처(모터스K)·헬로우카 원문: 스마트키 95440H8000·블랭킹 81999H8300 '적용시점 2017.6.21~'(종료일·개정품번 없음) → 같은 PN이므로 칩도 ID8A</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="48" t="inlineStr">
+      <c r="A105" s="49" t="inlineStr">
         <is>
           <t>- 셀토스 (SP2) 2020: 연식변경(2020.7.1) — 전방충돌방지보조 등 안전사양 추가</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="48" t="inlineStr">
+      <c r="A106" s="49" t="inlineStr">
         <is>
           <t>- 셀토스 (SP2/SP2 PE) 2022: '더 뉴 셀토스'(SP2 PE) 페이스리프트 출시(2022.7)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="48" t="inlineStr">
+      <c r="A107" s="49" t="inlineStr">
         <is>
           <t>- 쏘울 (Soul, AM) 2008: 쏘울 국내 출시(2008)</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="48" t="inlineStr">
+      <c r="A108" s="49" t="inlineStr">
         <is>
           <t>- 쏘울 (Soul, AM) 2009: 칩: transpondery.com 'KIA SOUL 2008-2013: Philips PCF7952A / ID46 / Hitag 2', 2013 정품 폴딩키 '46 Chip'(vvdi)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="48" t="inlineStr">
+      <c r="A109" s="49" t="inlineStr">
         <is>
           <t>- 쏘울 부스터 (Soul, SK3) 2019: 쏘울 부스터(SK3) 완전변경 출시(2019). 국내 현대모비스(hellowcar) 확인 — 연식별 세부 날짜는 추가 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="48" t="inlineStr">
+      <c r="A110" s="49" t="inlineStr">
         <is>
           <t>- 쏘울 부스터 (Soul, SK3) 2025(단종): 쏘울 국내외 최종 단종 연식(2025) — 후속 없음(나무위키 확인)</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="48" t="inlineStr">
+      <c r="A111" s="49" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2011: 레이 국내 출시(2011.11) — 국내 현대모비스(hellowcar) 날짜별 원문 재확인</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="48" t="inlineStr">
+      <c r="A112" s="49" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2015: 이전에 2015-2016 폴딩키를 A3100/A3110으로 적었으나 원문상 A3001 구간(2012.9.10~2017.12.12)이라 정정</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="48" t="inlineStr">
+      <c r="A113" s="49" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2017: 국내 현대모비스 확인 — 2017년 하반기 스마트키 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="48" t="inlineStr">
+      <c r="A114" s="49" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2022: 국내 현대모비스 확인 — 2022.9.5 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="48" t="inlineStr">
+      <c r="A115" s="49" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2025: 원문상 스마트키 A3600[2022.8.31~], 폴딩키 A3600[2022.8.31~]·A3610[2023.6.16~] 모두 종료일 없는 현행 품번</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="48" t="inlineStr">
+      <c r="A116" s="49" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, SA) 2004: 모닝 국내 출시(2004)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="48" t="inlineStr">
+      <c r="A117" s="49" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, SA) 2010: TA 완전변경 출시(2011)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="48" t="inlineStr">
+      <c r="A118" s="49" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, TA) 2011: 올뉴 모닝(TA) 출시(2011.1). 국내 현대모비스(hellowcar) 원문: TA 스마트키 954401Y500[~2013.8.16, 블랭킹 819961Y020] → 954401Y600[2013.8.16~2016.12.29, 819961Y620] / JA 스마트키 95440G6000[2016.10.25~, ~22년식]·95440G6100[22년식~] ~2023.6.27(블랭킹 81996G6020) → 95440G6500[2023.6.27~, 81996P2800]. 이전에 TA에 G6000·G6100, JA에 1Y500·1Y600을 적었던 것은 서로 뒤바뀐 오류라 정정</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="48" t="inlineStr">
+      <c r="A119" s="49" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, TA) 2012: 국내 현대모비스 확인 — 2012.9.27 기준 폴딩키 전환</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="48" t="inlineStr">
+      <c r="A120" s="49" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, TA) 2013: 국내 현대모비스 확인 — 2013.8.1 기준 폴딩키 전환</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="48" t="inlineStr">
+      <c r="A121" s="49" t="inlineStr">
         <is>
           <t>- EV3 (SV) 2024: EV3 국내 출시(2024.7) — K3 플랫폼 기반 E-GMP, 국내 현대모비스 확인. 부품번호는 '주차보조/디지털키' 조합별 4종</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="48" t="inlineStr">
+      <c r="A122" s="49" t="inlineStr">
         <is>
           <t>- EV3 (SV) 2026: '더 EV3' 연식변경(2026.2.2 출시)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="48" t="inlineStr">
+      <c r="A123" s="49" t="inlineStr">
         <is>
           <t>- EV6 (CV) 2021: 국내 현대모비스(hellowcar) 원문: CV000(주차보조X)/CV010(주차보조O) ~2024.2.7, 이후 CV001/CV011. 블레이드 CV000=주차보조X, CV010=주차보조O</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="48" t="inlineStr">
+      <c r="A124" s="49" t="inlineStr">
         <is>
           <t>- EV6 (CV) 2024: 국내 현대모비스(hellowcar): 초기형 CV000·CV010[~2024.2.7] → CV001·CV011[2024.2.7~], 페이스리프트 전용 CV500·CV510·CV520 별도 리스팅(적용 시작일 원문 미확인). 칩: 95440-CV000 정품 HITAG AES ID4A(tlkeys)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="48" t="inlineStr">
+      <c r="A125" s="49" t="inlineStr">
         <is>
           <t>- EV6 (CV) 2025: 이전에 2025~2026년에 초기형 CV001·CV011을 적었으나 페이스리프트 전용 CV500·CV510·CV520으로 정정(hellowcar). CV510·CV520 해외 판매처 적용 2025~2026</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="48" t="inlineStr">
+      <c r="A126" s="49" t="inlineStr">
         <is>
           <t>- EV9 2023: EV9 국내 출시(2023.5). 국내 현대모비스(hellowcar): 스마트키 DO000·DO010·DO020·DO030(사양 표기 원문 그대로), 블랭킹 81996DO000, 케이스 81995DO000 — 종료일 없는 현행 품번. 이전에 넣었던 DO060은 국내 원문에 없어 삭제</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="48" t="inlineStr">
+      <c r="A127" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, JE/KM) 2004: 칩: 트랜스폰더 카탈로그 'SPORTAGE 2004~ Philips Crypto2 ID46', 247geek 'Kia Sportage 25.08.2004-01.11.2012 ID46(PCF7936)'</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="48" t="inlineStr">
+      <c r="A128" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, JE/KM) 2010: SL 완전변경 출시(2010)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="48" t="inlineStr">
+      <c r="A129" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, SL) 2011: 국내 현대모비스(hellowcar) 및 국제 판매처(gskeyae) 확인. transpondery.com 카탈로그 원문 확인: SL세대는 트림별로 DST80/ID6E-MA(플립) 또는 ID46/PCF7952A(스마트) 혼재 — 폴딩키 PN 국내 확인, 이전에 누락됐던 것 추가</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="48" t="inlineStr">
+      <c r="A130" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, SL) 2012: transpondery.com 카탈로그 확인</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="48" t="inlineStr">
+      <c r="A131" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, SL) 2015: 올 뉴 스포티지(QL) 완전변경 출시(2015)로 전환되는 해 — QL 초기부터 확정 ID47(NCF2971X) 확인됨(americankeysupply)</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="48" t="inlineStr">
+      <c r="A132" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2018: 국내 현대모비스 확인 — 2018년 중반 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="48" t="inlineStr">
+      <c r="A133" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2019: 국내 현대모비스(hellowcar) 원문: D9000[2015.8.3~2018.8.7] → D9500[2018.6.26~] → D9600[2019.2.26~], 블랭킹 81996A4040</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="48" t="inlineStr">
+      <c r="A134" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2021: 디 올 뉴 스포티지(NQ5) 완전변경 출시(2021)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="48" t="inlineStr">
+      <c r="A135" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, NQ5) 2022: 국내 현대모비스(hellowcar) 원문: 주차보조X P1100→P1110[2023.1.31~], 블랭킹 81999J7020 / 주차보조O P1200→P1210[2023.1.31~], 블랭킹 81996P1060. 이전 블레이드 기재(81926-J7000, 81996-K0000)는 원문과 달라 정정. 칩 ID4A(keyshop-online 등)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="48" t="inlineStr">
+      <c r="A136" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, NQ5) 2023: 국내 현대모비스 확인 — 2023.1.31 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="48" t="inlineStr">
+      <c r="A137" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, NQ5) 2024: 더 뉴 스포티지(NQ5 PE) 출시(2024.11.5, 나무위키). 국내 현대모비스(hellowcar): PE 스마트키 P1AB0·P1AC0·P1AE0·P1AF0, 블랭킹 81996S9600(사양별 구분은 원문 미확인)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="48" t="inlineStr">
+      <c r="A138" s="49" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, NQ5) 2025: 이전에 2025~2026년에 초기형 PN(P1110·P1210)을 적었으나 2024.11 페이스리프트 이후 PE 부품으로 정정. 폴딩키 P1000의 PE 적용 여부는 원문 미확인</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="48" t="inlineStr">
+      <c r="A139" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, BL) 2009: 쏘렌토R(XM) 완전변경 출시(2009.5)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="48" t="inlineStr">
+      <c r="A140" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, XM) 2010: 국내 현대모비스 확인 — 2010.7.1 기준 스마트키 전환. 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="48" t="inlineStr">
+      <c r="A141" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, XM) 2012: 뉴 쏘렌토R(페이스리프트) 출시(2012.7)</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="48" t="inlineStr">
+      <c r="A142" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, XM) 2013: 국내 현대모비스(hellowcar) 재확인 — 954402P500용 블레이드는 819962P300(이전 819962J700은 오기)</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="48" t="inlineStr">
+      <c r="A143" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, XM/UM) 2014: 쏘렌토(UM) 완전변경 출시(2014.8)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="48" t="inlineStr">
+      <c r="A144" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, UM) 2015: 국내 현대모비스(hellowcar) 원문: 95440C5000[2014.8.16~2017.7.24, 블레이드 81996C5040] → 95440C5500(더뉴쏘렌토)[2017.6.29~, 블레이드 81996C5050]. 칩: C5000·C5500 모두 HITAG3 ID47(한국 시장용 정품 mk3·tlkeys), 4버튼</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="48" t="inlineStr">
+      <c r="A145" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, UM) 2017: 더 뉴 쏘렌토(UM 페이스리프트) 출시(2017.7)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="48" t="inlineStr">
+      <c r="A146" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, UM 페이스리프트) 2018: 국내 현대모비스 원문: 95440C5500[2017.6.29~] 적용</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="48" t="inlineStr">
+      <c r="A147" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, UM/MQ4) 2020: 쏘렌토(MQ4) 완전변경 출시(2020.3)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="48" t="inlineStr">
+      <c r="A148" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, MQ4) 2023: 2023.8 페이스리프트('더 뉴 쏘렌토')로 전환되는 해 — 하이브리드 공용 신형 스마트키(95440-P2AD0) 등장</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="48" t="inlineStr">
+      <c r="A149" s="49" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, MQ4 페이스리프트) 2024: 국내 현대모비스(hellowcar): 더 뉴 쏘렌토(MQ4 PE) 스마트키 P2AA0·P2AB0·P2AC0·P2AD0 4종 확인(사양별 구분은 원문 미확인). 카폼: P2AD0 적용 '더 뉴 쏘렌토 2023.8 이후'(종료일 없음). 칩 ID4A</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="48" t="inlineStr">
+      <c r="A150" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2008: 모하비 국내 출시(2008.1). 국내 현대모비스(hellowcar) 원문: 2J800[~2010.12.13] → 2J860[2010.12.13~2011.6.1] → 2J870[2011.6.1~2015.12.23] (블레이드 819962J700) / 1W000[2016.1.15~2019.6.13, 819962J700] / 2J200(더뉴 모하비)[2016.11.15~2019.6.13, 819962J800]</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="48" t="inlineStr">
+      <c r="A151" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2010: 국내 현대모비스 확인 — 2010.12.13 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="48" t="inlineStr">
+      <c r="A152" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2011: 국내 현대모비스 확인 — 2011.6.1 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="48" t="inlineStr">
+      <c r="A153" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2012: 이전에 2012~2013년에 1W000·2J200을 함께 적었으나 원문상 둘 다 2016년부터라 정정</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="48" t="inlineStr">
+      <c r="A154" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2014: 모하비 더 마스터(1차 페이스리프트) 출시(2014.5)</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="48" t="inlineStr">
+      <c r="A155" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2018: 모하비 더 마스터(2차 완전변경급 페이스리프트) 출시(2019)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="48" t="inlineStr">
+      <c r="A156" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM 더마스터) 2019: 국제 판매처(abkeys.com) 확인 — 더마스터부터 ID46에서 ID47로 칩 세대 전환. 초기형(2008-2018)은 abkeys 확인 PCF7952A ID46</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="48" t="inlineStr">
+      <c r="A157" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM 더마스터) 2021: 국내 현대모비스 확인 — 2021.6.8 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="48" t="inlineStr">
+      <c r="A158" s="49" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM 더마스터) 2025: 국내 현대모비스(hellowcar) 원문: 모하비 더마스터[2019.8.22~] 2J500[~2021.6.8] → 2J550·2JAA0[2021.6.8~, 종료일 없음], 블랭킹 819962J900</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="48" t="inlineStr">
+      <c r="A159" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2016: 니로(DE) 국내 출시(2016.3.7, 95440-G5000 출시일과 일치). 칩: 같은 PN(95440-G5000) 정품 Hitag3 ID47 확인. 국내 현대모비스(hellowcar) 원문: G5000[~2019.2.28, 블랭킹 81996G5A20] → G5010[2019.2.28~] · G5025[22년형] · DB000[니로 플러스], 이후 블랭킹 81999J7020</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="48" t="inlineStr">
+      <c r="A160" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2017: 국제 판매처(keyshop-online, dfwkeys4cars) 확인 — Hitag3 ID47</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="48" t="inlineStr">
+      <c r="A161" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2018: 이전에 2018년에 G5010을 함께 적었으나 원문상 G5010은 2019.2.28부터라 정정</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="48" t="inlineStr">
+      <c r="A162" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2019: 니로 플러스(택시형) 출시 — 별도 스마트키 PN(95440-DB000)</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="48" t="inlineStr">
+      <c r="A163" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2020: 니로(DE) 페이스리프트(2019.7)</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="48" t="inlineStr">
+      <c r="A164" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE/SG2) 2022: 디 올 뉴 니로(SG2) 완전변경 출시(2022.1)로 전환되는 해 — 이때 칩이 ID47(Hitag3)에서 ID4A(Hitag AES)로 세대 전환. 디지털키2 터치 옵션 최초 도입</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="48" t="inlineStr">
+      <c r="A165" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, SG2) 2023: 블레이드 매칭: 원문 옵션 순서(주차보조X→81999J7020, 주차보조O→81996P1060), 셀토스·스포티지 NQ5 원문과 동일 구성</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="48" t="inlineStr">
+      <c r="A166" s="49" t="inlineStr">
         <is>
           <t>- 니로 (Niro, SG2) 2024: 국내 현대모비스 확인 — 2024.2.7 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="48" t="inlineStr">
+      <c r="A167" s="49" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RS) 1999: 카렌스(RS) 국내 출시(1999)</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="48" t="inlineStr">
+      <c r="A168" s="49" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RS) 2002: 카렌스2/엑스트렉 페이스리프트(2002)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="48" t="inlineStr">
+      <c r="A169" s="49" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, UN) 2007: 국내 현대모비스(hellowcar) 폴딩키 원문: D101[2007.7.2~2008.5.27] → D102[2008.5.27~2010.6.16] → D103[2010.6.1~2012.7.17] → D104[2012.7.1~2012.7.17, 블랭킹 819962L001] / RP 95430A4000[2013.2.28~2016.6.30]. D100은 부품만 확인되고 날짜 옵션이 원문에 없음</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="48" t="inlineStr">
+      <c r="A170" s="49" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, UN/RP) 2013: 올 뉴 카렌스(RP) 완전변경 출시(2013.3.29). transpondery.com 카탈로그 원문 확인: RP세대는 트림별로 DST80/ID6E-MA(플립) 또는 ID46/PCF7952A(스마트) 혼재 - 이전에 스마트키만 쓰고 플립키 트림을 빠뜨렸던 것 정정</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="48" t="inlineStr">
+      <c r="A171" s="49" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RP) 2016: 더 뉴 카렌스(RP 페이스리프트) 출시(2016.7)</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="48" t="inlineStr">
+      <c r="A172" s="49" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RP) 2017: 폴딩키 95430A4000은 원문상 2016.6.30까지 — 더 뉴 카렌스(2016.7~) 폴딩키 품번은 원문에서 확인 못해 공란</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="48" t="inlineStr">
+      <c r="A173" s="49" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RP) 2018(단종): 카렌스 국내 최종 연식 — 2018년 10월 공식 단종. 4세대(KY, 2022+ 해외)는 인도 등 전략시장 전용, 국내 미판매, 국내 후속 없음(나무위키 확인)</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="48" t="inlineStr">
+      <c r="A174" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, KV-II/GQ) 2005: 그랜드카니발(VQ) 완전변경 출시(2005.7)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="48" t="inlineStr">
+      <c r="A175" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, VQ) 2006: 그랜드카니발(VQ). 칩·블레이드: 정품 81996-4D040 PCF7936 ID46(abkeys), 'Sedona 2006-2012 ID46 81996-4D040'(locksmithkeyless). 폴딩키: 2008.6.2 기준 001/011/021 → 002/012/022 계열 전환, 끝자리는 버튼 수(3/5/6버튼) 구분(hellowcar)</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="48" t="inlineStr">
+      <c r="A176" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, VQ) 2010: 타이거노즈 그릴 적용 페이스리프트(2010)</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="48" t="inlineStr">
+      <c r="A177" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, VQ/YP) 2014: 올 뉴 카니발(YP) 출시(2014.6). 국내 현대모비스(hellowcar) 원문: YP 스마트키 A9300(6버튼, 전동도어O)·A9100(4버튼, 전동도어X)[2014.5.26~], 블랭킹 81996A4040 — 이전 기재 95440-A9200은 국내 원문에 없는 번호라 삭제</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="48" t="inlineStr">
+      <c r="A178" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, YP) 2015: 국제 판매처(abkeys.com) 확인 — Hitag3 ID47</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="48" t="inlineStr">
+      <c r="A179" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, YP) 2018: 더 뉴 카니발(YP PE 페이스리프트) 출시(2018.3.13)</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="48" t="inlineStr">
+      <c r="A180" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, YP) 2020: 카니발(KA4) 출시(2020.8). 국내 현대모비스(hellowcar) 원문: 슬라이딩도어자동X는 P2000[~2020.7.20]→R0000[2020.7.20~]→R0430(22년형), 블랭킹 81996P2700 / 자동O는 R0100→R0420(22년형), 블랭킹 81996R0710 / 주차보조버튼O는 R0510</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="48" t="inlineStr">
+      <c r="A181" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, KA4) 2022: 국제 판매처(Amazon/KEYECU) 확인 — '4A Chip' 명시</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="48" t="inlineStr">
+      <c r="A182" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, KA4) 2023: '더 뉴 카니발'(KA4 PE 페이스리프트) 출시(2023.10)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="48" t="inlineStr">
+      <c r="A183" s="49" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, KA4 PE) 2024: 국내 현대모비스(hellowcar): 더 뉴 카니발(KA4 PE) 스마트키 R0800·R0810·R0820·R0840·R0850·R0AA0·R0AB0·R0AE0·R0AF0, 블랭킹 81996P2800(케이스 81995P2000). 사양별 구분은 원문 미확인. 이전 기재 R0870은 국내 원문에 없어 삭제, 블레이드도 P2700/R0710 → P2800으로 정정</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="48" t="inlineStr">
+      <c r="A184" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 EV (전기차) 2021: 국내 현대모비스 원문: CP000[~2021.7.5, 블레이드 81996CP000] → CP500[2021.7.5~] → CP600[2023.5.18~, 블레이드 81996CP100]</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="48" t="inlineStr">
+      <c r="A185" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 EV (전기차) 2022: 이전에 2022년에 CP600을 함께 적었으나 원문상 CP600은 2023.5.18부터라 정정</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="48" t="inlineStr">
+      <c r="A186" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2003: 카키넘버원(국내 키 도매) 확인: 81996-4E000 일반키[2004.9.1~2016.8.31], 81996-4E010 이모빌라이저키(4D 칩), 81996-4E020 이모빌라이저키(46 칩), 81996-4E031 폴딩키 블레이드[2013.1.17~2016.8.31], 81996-4F700 폴딩키 블레이드[2016.8.31~]. 이모빌라이저키 4종의 연식 구간은 원문에 없어 차대번호로 확인 필요 — 이전에 연식별로 나눠 적었던 막대키 PN은 근거 없는 배분이라 삭제하고 전 구간 공통 후보로 정리. MK3 릴리즈노트: 봉고3 ID46/BOSCH 95P08</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="48" t="inlineStr">
+      <c r="A187" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2004: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="48" t="inlineStr">
+      <c r="A188" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2005: 이모빌라이저: MK3 릴리즈노트는 봉고3를 ID46·BOSCH 95P08로 분류하나, 국내 정비 자료에 봉고3 133마력 델파이 ECU(39111-4A520)와 델파이형 CRDi 인젝터가 확인됨 → 엔진/ECU 사양에 따라 4D·46 키가 나뉘는 것으로 보이나 연식·사양 매칭 원문은 없음</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="48" t="inlineStr">
+      <c r="A189" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2006: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="48" t="inlineStr">
+      <c r="A190" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2007: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="48" t="inlineStr">
+      <c r="A191" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2008: 페이스리프트(2008) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="48" t="inlineStr">
+      <c r="A192" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2009: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="48" t="inlineStr">
+      <c r="A193" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2010: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="48" t="inlineStr">
+      <c r="A194" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2011: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="48" t="inlineStr">
+      <c r="A195" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2012: 이전에 2012~2015년 폴딩키를 954304E500으로 적었으나 원문상 E500(C타입)은 2016.8.31부터라 정정</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="48" t="inlineStr">
+      <c r="A196" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2013: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="48" t="inlineStr">
+      <c r="A197" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2014: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="48" t="inlineStr">
+      <c r="A198" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2015: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="48" t="inlineStr">
+      <c r="A199" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2016: 3차 페이스리프트(2016) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="48" t="inlineStr">
+      <c r="A200" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2017: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="48" t="inlineStr">
+      <c r="A201" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2018: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="48" t="inlineStr">
+      <c r="A202" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2019: 4차 페이스리프트(2019) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="48" t="inlineStr">
+      <c r="A203" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2020: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="48" t="inlineStr">
+      <c r="A204" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2021: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="48" t="inlineStr">
+      <c r="A205" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2022: 2021.12.2~2023.12 구간 폴딩키 PN은 국내 원문에서 확인하지 못해 공란</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="48" t="inlineStr">
+      <c r="A206" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2023: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="48" t="inlineStr">
+      <c r="A207" s="49" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2024: 국내 현대모비스(hellowcar): 내연 봉고3 스마트키 954404EGA0·블레이드 81996CP100 리스팅 확인. 버튼시동 스마트키는 LPG 터보 10.25인치 내비 패키지 옵션으로 확인(카눈 가격표)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="49" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="49" t="inlineStr">
+        <is>
+          <t>※ 2차 재조사로 확인한 근거 (2026.9, 색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="49" t="inlineStr">
+        <is>
+          <t>- 포르테 (TD) 2009-2011: 폴딩키 95430-1M250(Cerato 2010-2013 433MHz) PCF7936 ID46(abkeys·tlkeys), 블랭킹 81996-1M020(카다몰 포르테 키-블랭킹 피아이씨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="49" t="inlineStr">
+        <is>
+          <t>- K3 (YD) 2012-2015: 폴딩키 95430-A7100(Cerato 2013-2017 OKA-870T) 4D60 Carbon 80bit = DST80(ID6E-MA)(abkeys), 95430-A7200도 4D60 칩 키(keyless2go) — 이전 "4D60·ID46 상충"은 80bit DST80로 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="49" t="inlineStr">
+        <is>
+          <t>- K3 (BD) 2019: 95440-M6011·M6501(FCC CQOFD00430) 8A Texas Crypto 128bit AES(검색요약 key4·keydirect·abkeys M6010) — dfwkeys4cars 종합표의 ID47은 품번 근거 없어 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="49" t="inlineStr">
+        <is>
+          <t>- 프라이드 JB: 국내 이모빌라이저키 81996-1G100(뉴프라이드 2005.2.15~2009.12.10, 드림열쇠), 칩 없는 키 81996-1G000(Rio 2005-2011) — 같은 플랫폼 베르나 MC 81996-1E010도 ID46</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="49" t="inlineStr">
+        <is>
+          <t>- 프라이드 UB 2012: 2011.9 출시 스마트키 95440-1W000 계열(헬로우카 프라이드UB 954401W000/1W040/1W001) — 2013년과 같은 키</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="49" t="inlineStr">
+        <is>
+          <t>- 모닝 (SA) 2005-2009: 현대모비스 모닝SA 키 81996-07020·07100(헬로우카), 같은 계열 Picanto 81996-07010 PCF7936 ID46 HYN6(abkeys 2005+)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="49" t="inlineStr">
+        <is>
+          <t>- 모닝 (JA): 폴딩키 95430-G6600 4D-60 Carbon 80bit(DST80, abkeys·tlkeys), 스마트키 95440-G6000·G6100 DST-AES ID8A(mk3·keyshop-online·tlkeys) — 이전 "DST80 vs ID75 상충"은 폴딩키·스마트키 칩이 다른 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="49" t="inlineStr">
+        <is>
+          <t>- EV4 (CT1): 95440-EZ300(EV4 2025 7버튼) NCF29A HITAG AES(auto-keys.eu) → ID4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="49" t="inlineStr">
+        <is>
+          <t>- 스포티지 (JE/KM): 드림열쇠 "뉴스포티지 81996-2F010(04년6월~), 쎄라토(05년~)", 81996-2F010 PCF7936 ID46 HYN6(abkeys)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="49" t="inlineStr">
+        <is>
+          <t>- 스포티지 (SL) 2013-2014: 플립키 95430-3W200 PCF7936 HITAG2 ID46 HY22(auto-keys.eu OEM) — ID6E-MA 표기는 2011-2012 플립키 해당</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="49" t="inlineStr">
+        <is>
+          <t>- 쏘렌토 (BL): 국내 이모빌라이저 키 81996-3EG00(드림열쇠), 뉴 쏘렌토 이모빌라이저 키블레이드 81996-3EC00(카키넘버원·대남열쇠) PCF7936 ID46 HYN7R(abkeys)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="49" t="inlineStr">
+        <is>
+          <t>- 카렌스 (UN) 2008-2011: Carens 2006(후기)-2011 ID46 PCF7936 키(autoecupart), 국내 폴딩키 954301D101~D104(헬로우카) 적용 기간 확인</t>
         </is>
       </c>
     </row>

--- a/기아_트랜스폰더_칩코드_DBnew.xlsx
+++ b/기아_트랜스폰더_칩코드_DBnew.xlsx
@@ -24823,7 +24823,7 @@
     <row r="22">
       <c r="A22" s="56" t="inlineStr">
         <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>

--- a/기아_트랜스폰더_칩코드_DBnew.xlsx
+++ b/기아_트랜스폰더_칩코드_DBnew.xlsx
@@ -888,7 +888,7 @@
       <c r="I3" s="19" t="n"/>
       <c r="J3" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY12, Lishi HYN7R-HY7R-HY16</t>
+          <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
         </is>
       </c>
       <c r="K3" s="19" t="n"/>
@@ -942,7 +942,7 @@
       <c r="I4" s="19" t="n"/>
       <c r="J4" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY12, Lishi HYN7R-HY7R-HY16</t>
+          <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
         </is>
       </c>
       <c r="K4" s="19" t="n"/>
@@ -996,7 +996,7 @@
       <c r="I5" s="19" t="n"/>
       <c r="J5" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY12, Lishi HYN7R-HY7R-HY16</t>
+          <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
         </is>
       </c>
       <c r="K5" s="19" t="n"/>
@@ -1050,7 +1050,7 @@
       <c r="I6" s="19" t="n"/>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY12, Lishi HYN7R-HY7R-HY16</t>
+          <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
         </is>
       </c>
       <c r="K6" s="19" t="n"/>
@@ -1104,7 +1104,7 @@
       <c r="I7" s="19" t="n"/>
       <c r="J7" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY12, Lishi HYN7R-HY7R-HY16</t>
+          <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
         </is>
       </c>
       <c r="K7" s="19" t="n"/>
@@ -1490,7 +1490,11 @@
           <t>819962G030[2G100용], 819962L000</t>
         </is>
       </c>
-      <c r="J13" s="19" t="n"/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K13" s="19" t="n"/>
       <c r="L13" s="24" t="inlineStr">
         <is>
@@ -1558,7 +1562,7 @@
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY15, X280, Lishi HYN14R-HY15</t>
+          <t>HY15[ILCO], X280, HYN14R-HY15[Lishi], HYN14R[Silca]</t>
         </is>
       </c>
       <c r="K14" s="19" t="n"/>
@@ -1624,7 +1628,7 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY15, X280, Lishi HYN14R-HY15</t>
+          <t>HY15[ILCO], X280, HYN14R-HY15[Lishi], HYN14R[Silca]</t>
         </is>
       </c>
       <c r="K15" s="19" t="n"/>
@@ -1694,7 +1698,7 @@
       </c>
       <c r="J16" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY15, X280, Lishi HYN14R-HY15</t>
+          <t>HY15[ILCO], X280, HYN14R-HY15[Lishi], HYN14R[Silca]</t>
         </is>
       </c>
       <c r="K16" s="19" t="n"/>
@@ -1764,7 +1768,7 @@
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
-          <t>ILCO HY15, X280, Lishi HYN14R-HY15</t>
+          <t>HY15[ILCO], X280, HYN14R-HY15[Lishi], HYN14R[Silca]</t>
         </is>
       </c>
       <c r="K17" s="19" t="n"/>
@@ -2254,7 +2258,7 @@
       </c>
       <c r="J24" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, Lishi K5</t>
+          <t>KK12[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K24" s="19" t="n"/>
@@ -2324,7 +2328,7 @@
       </c>
       <c r="J25" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, Lishi K5</t>
+          <t>KK12[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K25" s="19" t="n"/>
@@ -2394,7 +2398,7 @@
       </c>
       <c r="J26" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, ILCO KK12-P, Lishi K5</t>
+          <t>KK12[ILCO], KK12-P[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K26" s="19" t="n"/>
@@ -2464,7 +2468,7 @@
       </c>
       <c r="J27" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, ILCO KK12-P, Lishi K5</t>
+          <t>KK12[ILCO], KK12-P[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K27" s="19" t="n"/>
@@ -2534,7 +2538,7 @@
       </c>
       <c r="J28" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, ILCO KK12-P, Lishi K5</t>
+          <t>KK12[ILCO], KK12-P[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K28" s="19" t="n"/>
@@ -2604,7 +2608,7 @@
       </c>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, ILCO KK12-P, Lishi K5</t>
+          <t>KK12[ILCO], KK12-P[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K29" s="19" t="n"/>
@@ -2674,7 +2678,7 @@
       </c>
       <c r="J30" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, ILCO KK12-P, Lishi K5</t>
+          <t>KK12[ILCO], KK12-P[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K30" s="19" t="n"/>
@@ -2744,7 +2748,7 @@
       </c>
       <c r="J31" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, ILCO KK12-P, Lishi K5</t>
+          <t>KK12[ILCO], KK12-P[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K31" s="19" t="n"/>
@@ -2814,7 +2818,7 @@
       </c>
       <c r="J32" s="24" t="inlineStr">
         <is>
-          <t>ILCO KK12, ILCO KK12-P, Lishi K5</t>
+          <t>KK12[ILCO], KK12-P[ILCO], K5[Lishi]</t>
         </is>
       </c>
       <c r="K32" s="19" t="n"/>
@@ -2882,7 +2886,11 @@
           <t>819962G030[스마트키용], 819962L000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J33" s="19" t="n"/>
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K33" s="19" t="n"/>
       <c r="L33" s="24" t="inlineStr">
         <is>
@@ -2948,7 +2956,11 @@
           <t>819962G030[스마트키용], 819962L000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J34" s="19" t="n"/>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K34" s="19" t="n"/>
       <c r="L34" s="24" t="inlineStr">
         <is>
@@ -3014,7 +3026,11 @@
           <t>819962G030[스마트키용], 819962L000[2T500용], 819962L001[2T501용]</t>
         </is>
       </c>
-      <c r="J35" s="19" t="n"/>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K35" s="19" t="n"/>
       <c r="L35" s="24" t="inlineStr">
         <is>
@@ -3080,7 +3096,11 @@
           <t>819962G030[2T000용], 81999-A4040[2T500용], 819962L001[폴딩키용]</t>
         </is>
       </c>
-      <c r="J36" s="19" t="n"/>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K36" s="19" t="n"/>
       <c r="L36" s="24" t="inlineStr">
         <is>
@@ -3608,7 +3628,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J44" s="19" t="n"/>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K44" s="19" t="n"/>
       <c r="L44" s="24" t="inlineStr">
         <is>
@@ -3674,7 +3698,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J45" s="19" t="n"/>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K45" s="19" t="n"/>
       <c r="L45" s="24" t="inlineStr">
         <is>
@@ -3740,7 +3768,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J46" s="19" t="n"/>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K46" s="19" t="n"/>
       <c r="L46" s="24" t="inlineStr">
         <is>
@@ -3806,7 +3838,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J47" s="19" t="n"/>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K47" s="19" t="n"/>
       <c r="L47" s="24" t="inlineStr">
         <is>
@@ -3872,7 +3908,11 @@
           <t>81996-S9000[초기형], 81996-L2020[초기형], 81996-S9600[페이스리프트]</t>
         </is>
       </c>
-      <c r="J48" s="19" t="n"/>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K48" s="19" t="n"/>
       <c r="L48" s="24" t="inlineStr">
         <is>
@@ -3938,7 +3978,11 @@
           <t>81996-S9600, 81996-L2000</t>
         </is>
       </c>
-      <c r="J49" s="19" t="n"/>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K49" s="19" t="n"/>
       <c r="L49" s="24" t="inlineStr">
         <is>
@@ -4004,7 +4048,11 @@
           <t>81996-S9600, 81996-L2000</t>
         </is>
       </c>
-      <c r="J50" s="19" t="n"/>
+      <c r="J50" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K50" s="19" t="n"/>
       <c r="L50" s="24" t="inlineStr">
         <is>
@@ -4070,7 +4118,11 @@
           <t>81996-S9600, 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J51" s="19" t="n"/>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K51" s="19" t="n"/>
       <c r="L51" s="24" t="inlineStr">
         <is>
@@ -4136,7 +4188,11 @@
           <t>819962J700[스마트키용], 819963J000[폴딩키용], 819963R500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J52" s="19" t="n"/>
+      <c r="J52" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K52" s="19" t="n"/>
       <c r="L52" s="24" t="inlineStr">
         <is>
@@ -4202,7 +4258,11 @@
           <t>819962J700[스마트키용], 819963J000[폴딩키용], 819963R500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J53" s="19" t="n"/>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K53" s="19" t="n"/>
       <c r="L53" s="24" t="inlineStr">
         <is>
@@ -4268,7 +4328,11 @@
           <t>819962J700[스마트키용], 819963J000[폴딩키용], 819963R500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J54" s="19" t="n"/>
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K54" s="19" t="n"/>
       <c r="L54" s="24" t="inlineStr">
         <is>
@@ -4334,7 +4398,11 @@
           <t>819962J700[3R000용], 819963T000[3R500용], 819963T100[카드키용], 819963J000[폴딩키용], 819963R500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J55" s="19" t="n"/>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO], LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
           <t>95440-3R800[2012.10.30~]</t>
@@ -4404,7 +4472,11 @@
           <t>819963T000[스마트키용], 819963T100[카드키용], 819963J000[폴딩키용], 819963R500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J56" s="19" t="n"/>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K56" s="24" t="inlineStr">
         <is>
           <t>95440-3R800[~2.28], 95440-3R801[2.28~]</t>
@@ -4474,7 +4546,11 @@
           <t>819963T000[스마트키용], 819963T100[카드키용], 819963J000[폴딩키용], 819963R500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J57" s="19" t="n"/>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
           <t>95440-3R801</t>
@@ -4544,7 +4620,11 @@
           <t>819963T000, 819963T100</t>
         </is>
       </c>
-      <c r="J58" s="19" t="n"/>
+      <c r="J58" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K58" s="24" t="inlineStr">
         <is>
           <t>95440-3R801[~12.31]</t>
@@ -4614,7 +4694,11 @@
           <t>81996-F6100, 81996-F6600[스마트키용], 81996-F6110[카드키용], 81996-F6500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J59" s="19" t="n"/>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
           <t>95443-F6000[12.9~]</t>
@@ -4688,7 +4772,11 @@
           <t>81996-F6100[스마트키용], 81996-F6600[스마트키용], 81996-F6110[카드키용], 81996-F6500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J60" s="19" t="n"/>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K60" s="24" t="inlineStr">
         <is>
           <t>95443-F6000</t>
@@ -4762,7 +4850,11 @@
           <t>81996-F6100[스마트키용], 81996-F6600[스마트키용], 81996-F6110[카드키용], 81996-F6500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J61" s="19" t="n"/>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K61" s="24" t="inlineStr">
         <is>
           <t>95443-F6000</t>
@@ -4836,7 +4928,11 @@
           <t>81996-F6100[스마트키용], 81996-F6600[스마트키용], 81996-F6110[카드키용], 81996-F6500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J62" s="19" t="n"/>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K62" s="24" t="inlineStr">
         <is>
           <t>95443-F6000</t>
@@ -4910,7 +5006,11 @@
           <t>81996-F6100[스마트키용, ~6.27], 81996-F6600[스마트키용, ~6.27], 81996-F6110[카드키용], 81996-F6500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J63" s="19" t="n"/>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K63" s="24" t="inlineStr">
         <is>
           <t>95443-F6000[~6.27], 95443-F6010[5.30~]</t>
@@ -5132,7 +5232,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J66" s="19" t="n"/>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K66" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -5202,7 +5306,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J67" s="19" t="n"/>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K67" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -5272,7 +5380,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J68" s="19" t="n"/>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K68" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -5342,7 +5454,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J69" s="19" t="n"/>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K69" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -5412,7 +5528,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용, 초기형 기준]</t>
         </is>
       </c>
-      <c r="J70" s="19" t="n"/>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K70" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -5482,7 +5602,11 @@
           <t>81996-S9000[주차보조X용], 81996-L2020[주차보조O용], 81996-L2000[폴딩키용, 초기형 기준]</t>
         </is>
       </c>
-      <c r="J71" s="19" t="n"/>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K71" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -5552,7 +5676,11 @@
           <t>819963T000[스마트키용], 819963T100[카드키용]</t>
         </is>
       </c>
-      <c r="J72" s="19" t="n"/>
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K72" s="24" t="inlineStr">
         <is>
           <t>95443-3T000[버튼 없음]</t>
@@ -5618,7 +5746,11 @@
           <t>819963T000[스마트키용], 819963T100[카드키용]</t>
         </is>
       </c>
-      <c r="J73" s="19" t="n"/>
+      <c r="J73" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K73" s="24" t="inlineStr">
         <is>
           <t>95443-3T000[버튼 없음, ~7.1], 95443-3T100[7.1~]</t>
@@ -5684,7 +5816,11 @@
           <t>819963T000[스마트키용], 819963T100[카드키용]</t>
         </is>
       </c>
-      <c r="J74" s="19" t="n"/>
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K74" s="24" t="inlineStr">
         <is>
           <t>95443-3T100[~11.15], 95443-3T200[버튼 없음, 11.10~]</t>
@@ -5750,7 +5886,11 @@
           <t>819963T000[스마트키용], 819963T100[카드키용]</t>
         </is>
       </c>
-      <c r="J75" s="19" t="n"/>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K75" s="24" t="inlineStr">
         <is>
           <t>95443-3T200[버튼 없음]</t>
@@ -5816,7 +5956,11 @@
           <t>819963T000[스마트키용], 819963T100[카드키용]</t>
         </is>
       </c>
-      <c r="J76" s="19" t="n"/>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K76" s="24" t="inlineStr">
         <is>
           <t>95443-3T200[버튼 없음]</t>
@@ -5882,7 +6026,11 @@
           <t>819963T000[스마트키용], 819963T100[카드키용]</t>
         </is>
       </c>
-      <c r="J77" s="19" t="n"/>
+      <c r="J77" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K77" s="24" t="inlineStr">
         <is>
           <t>95443-3T200[버튼 없음, ~2017.12.30]</t>
@@ -5948,7 +6096,11 @@
           <t>819963T000, 819963T100</t>
         </is>
       </c>
-      <c r="J78" s="19" t="n"/>
+      <c r="J78" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO], TOYO-18[JMA]</t>
+        </is>
+      </c>
       <c r="K78" s="24" t="n"/>
       <c r="L78" s="24" t="inlineStr">
         <is>
@@ -6010,7 +6162,11 @@
           <t>81996-J6000[스마트키용], 81996-J6010[카드키용]</t>
         </is>
       </c>
-      <c r="J79" s="19" t="n"/>
+      <c r="J79" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K79" s="24" t="inlineStr">
         <is>
           <t>95443-J6000[버튼 있음, 2018.3.5~]</t>
@@ -6076,7 +6232,11 @@
           <t>81996-J6000[스마트키용], 81996-J6010[카드키용]</t>
         </is>
       </c>
-      <c r="J80" s="19" t="n"/>
+      <c r="J80" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K80" s="24" t="inlineStr">
         <is>
           <t>95443-J6000[버튼 있음]</t>
@@ -6142,7 +6302,11 @@
           <t>81996-J6000[스마트키용], 81996-J6010[카드키용]</t>
         </is>
       </c>
-      <c r="J81" s="19" t="n"/>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K81" s="24" t="inlineStr">
         <is>
           <t>95443-J6000[버튼 있음]</t>
@@ -6208,7 +6372,11 @@
           <t>81996-J6000[스마트키용], 81996-J6100[스마트키용], 81996-J6010[카드키용]</t>
         </is>
       </c>
-      <c r="J82" s="19" t="n"/>
+      <c r="J82" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K82" s="24" t="inlineStr">
         <is>
           <t>95443-J6000[버튼 있음]</t>
@@ -6274,7 +6442,11 @@
           <t>81996-J6000, 81996-J6100</t>
         </is>
       </c>
-      <c r="J83" s="19" t="n"/>
+      <c r="J83" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K83" s="19" t="n"/>
       <c r="L83" s="24" t="inlineStr">
         <is>
@@ -6336,7 +6508,11 @@
           <t>81996-J6000, 81996-J6100</t>
         </is>
       </c>
-      <c r="J84" s="19" t="n"/>
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K84" s="19" t="n"/>
       <c r="L84" s="24" t="inlineStr">
         <is>
@@ -6398,7 +6574,11 @@
           <t>81996-J6000, 81996-J6100</t>
         </is>
       </c>
-      <c r="J85" s="19" t="n"/>
+      <c r="J85" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K85" s="19" t="n"/>
       <c r="L85" s="24" t="inlineStr">
         <is>
@@ -6460,7 +6640,11 @@
           <t>81996-J6000, 81996-J6100</t>
         </is>
       </c>
-      <c r="J86" s="19" t="n"/>
+      <c r="J86" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K86" s="24" t="inlineStr">
         <is>
           <t>95443-J6000[버튼 있음]</t>
@@ -6526,7 +6710,11 @@
           <t>81996-J6000, 81996-J6100</t>
         </is>
       </c>
-      <c r="J87" s="19" t="n"/>
+      <c r="J87" s="19" t="inlineStr">
+        <is>
+          <t>LXP90[ILCO]</t>
+        </is>
+      </c>
       <c r="K87" s="24" t="inlineStr">
         <is>
           <t>95443-J6000[버튼 있음]</t>
@@ -7156,7 +7344,11 @@
           <t>81996-2G030[954401W000용], 81999-2G030[954401W040용], 81999-A4040[954401W001용, 2013.3.25~2017.3.31]</t>
         </is>
       </c>
-      <c r="J98" s="19" t="n"/>
+      <c r="J98" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K98" s="19" t="n"/>
       <c r="L98" s="24" t="inlineStr">
         <is>
@@ -7222,7 +7414,11 @@
           <t>81996-2G030[954401W000용], 81999-2G030[954401W040용], 81999-A4040[954401W001용, 2013.3.25~2017.3.31]</t>
         </is>
       </c>
-      <c r="J99" s="19" t="n"/>
+      <c r="J99" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K99" s="19" t="n"/>
       <c r="L99" s="24" t="inlineStr">
         <is>
@@ -7288,7 +7484,11 @@
           <t>81996-2G030[954401W000용], 81999-2G030[954401W040용], 81999-A4040[954401W001용, 2013.3.25~2017.3.31]</t>
         </is>
       </c>
-      <c r="J100" s="19" t="n"/>
+      <c r="J100" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K100" s="19" t="n"/>
       <c r="L100" s="24" t="inlineStr">
         <is>
@@ -7354,7 +7554,11 @@
           <t>81996-2G030[954401W000용], 81999-2G030[954401W040용], 81999-A4040[954401W001용, 2013.3.25~2017.3.31]</t>
         </is>
       </c>
-      <c r="J101" s="19" t="n"/>
+      <c r="J101" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K101" s="19" t="n"/>
       <c r="L101" s="24" t="inlineStr">
         <is>
@@ -9058,7 +9262,11 @@
           <t>81999-J7020[스마트키용], 81996-K0000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J129" s="19" t="n"/>
+      <c r="J129" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K129" s="19" t="n"/>
       <c r="L129" s="24" t="inlineStr">
         <is>
@@ -9128,7 +9336,11 @@
           <t>81999-J7020[스마트키용], 81996-K0000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J130" s="19" t="n"/>
+      <c r="J130" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K130" s="19" t="n"/>
       <c r="L130" s="24" t="inlineStr">
         <is>
@@ -9194,7 +9406,11 @@
           <t>81999-J7020[스마트키용], 81996-K0000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J131" s="19" t="n"/>
+      <c r="J131" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K131" s="19" t="n"/>
       <c r="L131" s="24" t="inlineStr">
         <is>
@@ -9260,7 +9476,11 @@
           <t>81999-J7020[초기형 스마트키용], 81996-P1060[페이스리프트 스마트키용], 81996-K0000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J132" s="19" t="n"/>
+      <c r="J132" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K132" s="19" t="n"/>
       <c r="L132" s="24" t="inlineStr">
         <is>
@@ -9326,7 +9546,11 @@
           <t>81996-P1060[스마트키용], 81996-K0000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J133" s="19" t="n"/>
+      <c r="J133" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K133" s="19" t="n"/>
       <c r="L133" s="24" t="inlineStr">
         <is>
@@ -9392,7 +9616,11 @@
           <t>81996-P1060[스마트키용], 81996-K0000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J134" s="19" t="n"/>
+      <c r="J134" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K134" s="19" t="n"/>
       <c r="L134" s="24" t="inlineStr">
         <is>
@@ -9458,7 +9686,11 @@
           <t>81996-P1060[스마트키용], 81996-K0000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J135" s="19" t="n"/>
+      <c r="J135" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K135" s="19" t="n"/>
       <c r="L135" s="24" t="inlineStr">
         <is>
@@ -9524,7 +9756,11 @@
           <t>81996-P1060[스마트키용], 81996-K0000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J136" s="19" t="n"/>
+      <c r="J136" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K136" s="19" t="n"/>
       <c r="L136" s="24" t="inlineStr">
         <is>
@@ -9570,7 +9806,11 @@
       </c>
       <c r="H137" s="24" t="n"/>
       <c r="I137" s="24" t="n"/>
-      <c r="J137" s="19" t="n"/>
+      <c r="J137" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K137" s="19" t="n"/>
       <c r="L137" s="24" t="n"/>
       <c r="M137" s="24" t="n"/>
@@ -10798,7 +11038,11 @@
           <t>819962J700[스마트키용], 819963J000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J157" s="19" t="n"/>
+      <c r="J157" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K157" s="19" t="n"/>
       <c r="L157" s="24" t="inlineStr">
         <is>
@@ -10864,7 +11108,11 @@
           <t>819962J700[스마트키용], 819963J000[폴딩키용], 819963R001[폴딩키용]</t>
         </is>
       </c>
-      <c r="J158" s="19" t="n"/>
+      <c r="J158" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K158" s="19" t="n"/>
       <c r="L158" s="24" t="inlineStr">
         <is>
@@ -10930,7 +11178,11 @@
           <t>819962J700[스마트키용], 819963R001[폴딩키용]</t>
         </is>
       </c>
-      <c r="J159" s="19" t="n"/>
+      <c r="J159" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K159" s="19" t="n"/>
       <c r="L159" s="24" t="inlineStr">
         <is>
@@ -10996,7 +11248,11 @@
           <t>819962J700[스마트키용], 819963R001[폴딩키용]</t>
         </is>
       </c>
-      <c r="J160" s="19" t="n"/>
+      <c r="J160" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K160" s="19" t="n"/>
       <c r="L160" s="24" t="inlineStr">
         <is>
@@ -11062,7 +11318,11 @@
           <t>819962J700[스마트키용], 819963R001[폴딩키용]</t>
         </is>
       </c>
-      <c r="J161" s="19" t="n"/>
+      <c r="J161" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K161" s="19" t="n"/>
       <c r="L161" s="24" t="inlineStr">
         <is>
@@ -11128,7 +11388,11 @@
           <t>819962J700[스마트키용], 819963R001[폴딩키용]</t>
         </is>
       </c>
-      <c r="J162" s="19" t="n"/>
+      <c r="J162" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K162" s="19" t="n"/>
       <c r="L162" s="24" t="inlineStr">
         <is>
@@ -11194,7 +11458,11 @@
           <t>819962J700[스마트키용], 819962P300[스마트키용], 819963R001[폴딩키용], 819961U000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J163" s="19" t="n"/>
+      <c r="J163" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO], KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K163" s="19" t="n"/>
       <c r="L163" s="24" t="inlineStr">
         <is>
@@ -11260,7 +11528,11 @@
           <t>819962P300[스마트키용], 819961U000[폴딩키용]</t>
         </is>
       </c>
-      <c r="J164" s="19" t="n"/>
+      <c r="J164" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K164" s="19" t="n"/>
       <c r="L164" s="24" t="inlineStr">
         <is>
@@ -11326,7 +11598,11 @@
           <t>819962P300[스마트키용], 819961U000[폴딩키용], 81996-A3500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J165" s="19" t="n"/>
+      <c r="J165" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K165" s="19" t="n"/>
       <c r="L165" s="24" t="inlineStr">
         <is>
@@ -11392,7 +11668,11 @@
           <t>819962P300[스마트키용], 819961U000[폴딩키용], 81996-A3500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J166" s="19" t="n"/>
+      <c r="J166" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K166" s="19" t="n"/>
       <c r="L166" s="24" t="inlineStr">
         <is>
@@ -11458,7 +11738,11 @@
           <t>819962P300[스마트키용], 819961U000[폴딩키용], 81996-A3500[폴딩키용]</t>
         </is>
       </c>
-      <c r="J167" s="19" t="n"/>
+      <c r="J167" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K167" s="19" t="n"/>
       <c r="L167" s="24" t="inlineStr">
         <is>
@@ -11524,7 +11808,11 @@
           <t>819962P300[스마트키용], 81996-A3800[스마트키용], 819961U000[폴딩키용], 81996-A3500[폴딩키용], 81996-A3600[폴딩키용]</t>
         </is>
       </c>
-      <c r="J168" s="19" t="n"/>
+      <c r="J168" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K168" s="19" t="n"/>
       <c r="L168" s="24" t="inlineStr">
         <is>
@@ -14716,7 +15004,11 @@
           <t>819962M020</t>
         </is>
       </c>
-      <c r="J220" s="19" t="n"/>
+      <c r="J220" s="19" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO]</t>
+        </is>
+      </c>
       <c r="K220" s="19" t="n"/>
       <c r="L220" s="24" t="inlineStr">
         <is>
@@ -14782,7 +15074,11 @@
           <t>819962M020</t>
         </is>
       </c>
-      <c r="J221" s="19" t="n"/>
+      <c r="J221" s="19" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO]</t>
+        </is>
+      </c>
       <c r="K221" s="19" t="n"/>
       <c r="L221" s="24" t="inlineStr">
         <is>
@@ -14848,7 +15144,11 @@
           <t>819962M020[~7.2 이전], 81996A4040[6.29 이후]</t>
         </is>
       </c>
-      <c r="J222" s="19" t="n"/>
+      <c r="J222" s="19" t="inlineStr">
+        <is>
+          <t>HY15R[ILCO], HY17[ILCO], KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K222" s="19" t="n"/>
       <c r="L222" s="24" t="inlineStr">
         <is>
@@ -14914,7 +15214,11 @@
           <t>81996A4040</t>
         </is>
       </c>
-      <c r="J223" s="19" t="n"/>
+      <c r="J223" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K223" s="19" t="n"/>
       <c r="L223" s="24" t="inlineStr">
         <is>
@@ -14980,7 +15284,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J224" s="19" t="n"/>
+      <c r="J224" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K224" s="19" t="n"/>
       <c r="L224" s="24" t="inlineStr">
         <is>
@@ -15046,7 +15354,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J225" s="19" t="n"/>
+      <c r="J225" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K225" s="19" t="n"/>
       <c r="L225" s="24" t="inlineStr">
         <is>
@@ -15112,7 +15424,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J226" s="19" t="n"/>
+      <c r="J226" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K226" s="19" t="n"/>
       <c r="L226" s="24" t="inlineStr">
         <is>
@@ -15178,7 +15494,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J227" s="19" t="n"/>
+      <c r="J227" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K227" s="19" t="n"/>
       <c r="L227" s="24" t="inlineStr">
         <is>
@@ -15244,7 +15564,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J228" s="19" t="n"/>
+      <c r="J228" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K228" s="19" t="n"/>
       <c r="L228" s="24" t="inlineStr">
         <is>
@@ -15310,7 +15634,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J229" s="19" t="n"/>
+      <c r="J229" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K229" s="19" t="n"/>
       <c r="L229" s="24" t="inlineStr">
         <is>
@@ -15376,7 +15704,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J230" s="19" t="n"/>
+      <c r="J230" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K230" s="19" t="n"/>
       <c r="L230" s="24" t="inlineStr">
         <is>
@@ -15442,7 +15774,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J231" s="19" t="n"/>
+      <c r="J231" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K231" s="19" t="n"/>
       <c r="L231" s="24" t="inlineStr">
         <is>
@@ -15508,7 +15844,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용]</t>
         </is>
       </c>
-      <c r="J232" s="19" t="n"/>
+      <c r="J232" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K232" s="19" t="n"/>
       <c r="L232" s="24" t="inlineStr">
         <is>
@@ -15574,7 +15914,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용]</t>
         </is>
       </c>
-      <c r="J233" s="19" t="n"/>
+      <c r="J233" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K233" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -15644,7 +15988,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용]</t>
         </is>
       </c>
-      <c r="J234" s="19" t="n"/>
+      <c r="J234" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K234" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -15714,7 +16062,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용], 81996-S9600[PE용]</t>
         </is>
       </c>
-      <c r="J235" s="19" t="n"/>
+      <c r="J235" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K235" s="24" t="inlineStr">
         <is>
           <t>AT954AP000, GZ954AP000[디지털키2 NFC 카드키]</t>
@@ -16414,7 +16766,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J247" s="19" t="n"/>
+      <c r="J247" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K247" s="19" t="n"/>
       <c r="L247" s="24" t="inlineStr">
         <is>
@@ -16480,7 +16836,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J248" s="19" t="n"/>
+      <c r="J248" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K248" s="19" t="n"/>
       <c r="L248" s="24" t="inlineStr">
         <is>
@@ -16546,7 +16906,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J249" s="19" t="n"/>
+      <c r="J249" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K249" s="19" t="n"/>
       <c r="L249" s="24" t="inlineStr">
         <is>
@@ -16612,7 +16976,11 @@
           <t>819962P300</t>
         </is>
       </c>
-      <c r="J250" s="19" t="n"/>
+      <c r="J250" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K250" s="19" t="n"/>
       <c r="L250" s="24" t="inlineStr">
         <is>
@@ -16678,7 +17046,11 @@
           <t>819962P300</t>
         </is>
       </c>
-      <c r="J251" s="19" t="n"/>
+      <c r="J251" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K251" s="19" t="n"/>
       <c r="L251" s="24" t="inlineStr">
         <is>
@@ -16744,7 +17116,11 @@
           <t>81996-C5040, 81996-C5050</t>
         </is>
       </c>
-      <c r="J252" s="19" t="n"/>
+      <c r="J252" s="19" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO]</t>
+        </is>
+      </c>
       <c r="K252" s="19" t="n"/>
       <c r="L252" s="24" t="inlineStr">
         <is>
@@ -16806,7 +17182,11 @@
           <t>81996-C5040</t>
         </is>
       </c>
-      <c r="J253" s="19" t="n"/>
+      <c r="J253" s="19" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO]</t>
+        </is>
+      </c>
       <c r="K253" s="19" t="n"/>
       <c r="L253" s="24" t="inlineStr">
         <is>
@@ -16868,7 +17248,11 @@
           <t>81996-C5040</t>
         </is>
       </c>
-      <c r="J254" s="19" t="n"/>
+      <c r="J254" s="19" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO]</t>
+        </is>
+      </c>
       <c r="K254" s="19" t="n"/>
       <c r="L254" s="24" t="inlineStr">
         <is>
@@ -16930,7 +17314,11 @@
           <t>81996-C5040[C5000용], 81996-C5050[C5500용]</t>
         </is>
       </c>
-      <c r="J255" s="19" t="n"/>
+      <c r="J255" s="19" t="inlineStr">
+        <is>
+          <t>HY18R[ILCO]</t>
+        </is>
+      </c>
       <c r="K255" s="19" t="n"/>
       <c r="L255" s="24" t="inlineStr">
         <is>
@@ -17636,7 +18024,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J266" s="19" t="n"/>
+      <c r="J266" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K266" s="19" t="n"/>
       <c r="L266" s="24" t="inlineStr">
         <is>
@@ -17698,7 +18090,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J267" s="19" t="n"/>
+      <c r="J267" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K267" s="19" t="n"/>
       <c r="L267" s="24" t="inlineStr">
         <is>
@@ -17760,7 +18156,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J268" s="19" t="n"/>
+      <c r="J268" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K268" s="19" t="n"/>
       <c r="L268" s="24" t="inlineStr">
         <is>
@@ -17822,7 +18222,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J269" s="19" t="n"/>
+      <c r="J269" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K269" s="19" t="n"/>
       <c r="L269" s="24" t="inlineStr">
         <is>
@@ -17884,7 +18288,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J270" s="19" t="n"/>
+      <c r="J270" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K270" s="19" t="n"/>
       <c r="L270" s="24" t="inlineStr">
         <is>
@@ -17946,7 +18354,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J271" s="19" t="n"/>
+      <c r="J271" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K271" s="19" t="n"/>
       <c r="L271" s="24" t="inlineStr">
         <is>
@@ -18008,7 +18420,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J272" s="19" t="n"/>
+      <c r="J272" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K272" s="19" t="n"/>
       <c r="L272" s="24" t="inlineStr">
         <is>
@@ -18070,7 +18486,11 @@
           <t>819962J700</t>
         </is>
       </c>
-      <c r="J273" s="19" t="n"/>
+      <c r="J273" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K273" s="19" t="n"/>
       <c r="L273" s="24" t="inlineStr">
         <is>
@@ -18132,7 +18552,11 @@
           <t>819962J700[1W000용], 819962J800[2J200용]</t>
         </is>
       </c>
-      <c r="J274" s="19" t="n"/>
+      <c r="J274" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K274" s="19" t="n"/>
       <c r="L274" s="24" t="inlineStr">
         <is>
@@ -18194,7 +18618,11 @@
           <t>819962J700[1W000용], 819962J800[2J200용]</t>
         </is>
       </c>
-      <c r="J275" s="19" t="n"/>
+      <c r="J275" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K275" s="19" t="n"/>
       <c r="L275" s="24" t="inlineStr">
         <is>
@@ -18256,7 +18684,11 @@
           <t>819962J700[1W000용], 819962J800[2J200용]</t>
         </is>
       </c>
-      <c r="J276" s="19" t="n"/>
+      <c r="J276" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K276" s="19" t="n"/>
       <c r="L276" s="24" t="inlineStr">
         <is>
@@ -18318,7 +18750,11 @@
           <t>819962J700[더뉴 모하비, ~6.13], 819962J800[더뉴 모하비, ~6.13], 81996-2J900[더마스터]</t>
         </is>
       </c>
-      <c r="J277" s="19" t="n"/>
+      <c r="J277" s="19" t="inlineStr">
+        <is>
+          <t>HY22[ILCO]</t>
+        </is>
+      </c>
       <c r="K277" s="19" t="n"/>
       <c r="L277" s="24" t="inlineStr">
         <is>
@@ -18946,7 +19382,11 @@
           <t>81996-G5A20[G5000용], 81999-J7020[G5010, DB000용]</t>
         </is>
       </c>
-      <c r="J287" s="19" t="n"/>
+      <c r="J287" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K287" s="19" t="n"/>
       <c r="L287" s="24" t="inlineStr">
         <is>
@@ -19012,7 +19452,11 @@
           <t>81999-J7020</t>
         </is>
       </c>
-      <c r="J288" s="19" t="n"/>
+      <c r="J288" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K288" s="19" t="n"/>
       <c r="L288" s="24" t="inlineStr">
         <is>
@@ -19078,7 +19522,11 @@
           <t>81999-J7020</t>
         </is>
       </c>
-      <c r="J289" s="19" t="n"/>
+      <c r="J289" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K289" s="19" t="n"/>
       <c r="L289" s="24" t="inlineStr">
         <is>
@@ -19144,7 +19592,11 @@
           <t>81999-J7020</t>
         </is>
       </c>
-      <c r="J290" s="19" t="n"/>
+      <c r="J290" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K290" s="19" t="n"/>
       <c r="L290" s="24" t="inlineStr">
         <is>
@@ -19206,7 +19658,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용]</t>
         </is>
       </c>
-      <c r="J291" s="19" t="n"/>
+      <c r="J291" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K291" s="19" t="n"/>
       <c r="L291" s="24" t="inlineStr">
         <is>
@@ -19268,7 +19724,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용]</t>
         </is>
       </c>
-      <c r="J292" s="19" t="n"/>
+      <c r="J292" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K292" s="19" t="n"/>
       <c r="L292" s="24" t="inlineStr">
         <is>
@@ -19330,7 +19790,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용]</t>
         </is>
       </c>
-      <c r="J293" s="19" t="n"/>
+      <c r="J293" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K293" s="19" t="n"/>
       <c r="L293" s="24" t="inlineStr">
         <is>
@@ -19392,7 +19856,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용]</t>
         </is>
       </c>
-      <c r="J294" s="19" t="n"/>
+      <c r="J294" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K294" s="19" t="n"/>
       <c r="L294" s="24" t="inlineStr">
         <is>
@@ -19454,7 +19922,11 @@
           <t>81999-J7020[주차보조X용], 81996-P1060[주차보조O용, 초기형]</t>
         </is>
       </c>
-      <c r="J295" s="19" t="n"/>
+      <c r="J295" s="19" t="inlineStr">
+        <is>
+          <t>KK12[ILCO]</t>
+        </is>
+      </c>
       <c r="K295" s="19" t="n"/>
       <c r="L295" s="24" t="inlineStr">
         <is>
@@ -20346,7 +20818,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J311" s="19" t="n"/>
+      <c r="J311" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K311" s="19" t="n"/>
       <c r="L311" s="24" t="inlineStr">
         <is>
@@ -20412,7 +20888,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J312" s="19" t="n"/>
+      <c r="J312" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K312" s="19" t="n"/>
       <c r="L312" s="24" t="inlineStr">
         <is>
@@ -20478,7 +20958,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J313" s="19" t="n"/>
+      <c r="J313" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K313" s="19" t="n"/>
       <c r="L313" s="24" t="inlineStr">
         <is>
@@ -20544,7 +21028,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J314" s="19" t="n"/>
+      <c r="J314" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K314" s="19" t="n"/>
       <c r="L314" s="24" t="inlineStr">
         <is>
@@ -20610,7 +21098,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J315" s="19" t="n"/>
+      <c r="J315" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K315" s="19" t="n"/>
       <c r="L315" s="24" t="inlineStr">
         <is>
@@ -20672,7 +21164,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J316" s="19" t="n"/>
+      <c r="J316" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K316" s="19" t="n"/>
       <c r="L316" s="24" t="inlineStr">
         <is>
@@ -21666,7 +22162,11 @@
           <t>81996-A4040[스마트키용]</t>
         </is>
       </c>
-      <c r="J333" s="19" t="n"/>
+      <c r="J333" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K333" s="19" t="n"/>
       <c r="L333" s="24" t="inlineStr">
         <is>
@@ -21728,7 +22228,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J334" s="19" t="n"/>
+      <c r="J334" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K334" s="19" t="n"/>
       <c r="L334" s="24" t="inlineStr">
         <is>
@@ -21794,7 +22298,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J335" s="19" t="n"/>
+      <c r="J335" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K335" s="19" t="n"/>
       <c r="L335" s="24" t="inlineStr">
         <is>
@@ -21860,7 +22368,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J336" s="19" t="n"/>
+      <c r="J336" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K336" s="19" t="n"/>
       <c r="L336" s="24" t="inlineStr">
         <is>
@@ -21926,7 +22438,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J337" s="19" t="n"/>
+      <c r="J337" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K337" s="19" t="n"/>
       <c r="L337" s="24" t="inlineStr">
         <is>
@@ -21992,7 +22508,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J338" s="19" t="n"/>
+      <c r="J338" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K338" s="19" t="n"/>
       <c r="L338" s="24" t="inlineStr">
         <is>
@@ -22058,7 +22578,11 @@
           <t>81996-A4040</t>
         </is>
       </c>
-      <c r="J339" s="19" t="n"/>
+      <c r="J339" s="19" t="inlineStr">
+        <is>
+          <t>KK10[ILCO], KIA7[Silca]</t>
+        </is>
+      </c>
       <c r="K339" s="19" t="n"/>
       <c r="L339" s="24" t="inlineStr">
         <is>

--- a/기아_트랜스폰더_칩코드_DBnew.xlsx
+++ b/기아_트랜스폰더_칩코드_DBnew.xlsx
@@ -264,7 +264,7 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -430,6 +430,9 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -6775,7 +6778,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I88" s="19" t="n"/>
+      <c r="I88" s="19" t="inlineStr">
+        <is>
+          <t>81996-1G100[이모빌라이저키, 2005.2.15~2009.12.10], 81996-1G000[칩 없음]</t>
+        </is>
+      </c>
       <c r="J88" s="19" t="n"/>
       <c r="K88" s="19" t="n"/>
       <c r="L88" s="19" t="n"/>
@@ -7119,7 +7126,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I94" s="19" t="n"/>
+      <c r="I94" s="19" t="inlineStr">
+        <is>
+          <t>81996-1G000[칩 없음]</t>
+        </is>
+      </c>
       <c r="J94" s="19" t="n"/>
       <c r="K94" s="19" t="n"/>
       <c r="L94" s="19" t="n"/>
@@ -7177,7 +7188,11 @@
       <c r="J95" s="19" t="n"/>
       <c r="K95" s="19" t="n"/>
       <c r="L95" s="19" t="n"/>
-      <c r="M95" s="19" t="n"/>
+      <c r="M95" s="19" t="inlineStr">
+        <is>
+          <t>95430-1W002</t>
+        </is>
+      </c>
       <c r="N95" s="19" t="n"/>
       <c r="O95" s="19" t="inlineStr">
         <is>
@@ -7231,7 +7246,11 @@
       <c r="J96" s="19" t="n"/>
       <c r="K96" s="19" t="n"/>
       <c r="L96" s="19" t="n"/>
-      <c r="M96" s="19" t="n"/>
+      <c r="M96" s="19" t="inlineStr">
+        <is>
+          <t>95430-1W002</t>
+        </is>
+      </c>
       <c r="N96" s="38" t="n"/>
       <c r="O96" s="19" t="inlineStr">
         <is>
@@ -9870,8 +9889,16 @@
       <c r="I138" s="19" t="n"/>
       <c r="J138" s="19" t="n"/>
       <c r="K138" s="19" t="n"/>
-      <c r="L138" s="19" t="n"/>
-      <c r="M138" s="19" t="n"/>
+      <c r="L138" s="19" t="inlineStr">
+        <is>
+          <t>95440-2K200</t>
+        </is>
+      </c>
+      <c r="M138" s="19" t="inlineStr">
+        <is>
+          <t>95430-2K211</t>
+        </is>
+      </c>
       <c r="N138" s="19" t="n"/>
       <c r="O138" s="19" t="n"/>
       <c r="P138" s="19" t="n"/>
@@ -12071,7 +12098,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I172" s="19" t="n"/>
+      <c r="I172" s="19" t="inlineStr">
+        <is>
+          <t>81996-07020, 81996-07100</t>
+        </is>
+      </c>
       <c r="J172" s="19" t="n"/>
       <c r="K172" s="19" t="n"/>
       <c r="L172" s="19" t="n"/>
@@ -14463,7 +14494,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I210" s="19" t="n"/>
+      <c r="I210" s="19" t="inlineStr">
+        <is>
+          <t>0K2AC-76201A[ID48 키]</t>
+        </is>
+      </c>
       <c r="J210" s="19" t="n"/>
       <c r="K210" s="19" t="n"/>
       <c r="L210" s="19" t="n"/>
@@ -14517,7 +14552,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I211" s="19" t="n"/>
+      <c r="I211" s="19" t="inlineStr">
+        <is>
+          <t>0K2AC-76201A[ID48 키]</t>
+        </is>
+      </c>
       <c r="J211" s="19" t="n"/>
       <c r="K211" s="19" t="n"/>
       <c r="L211" s="19" t="n"/>
@@ -14629,7 +14668,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I213" s="19" t="n"/>
+      <c r="I213" s="19" t="inlineStr">
+        <is>
+          <t>81996-2F010[2004.6~]</t>
+        </is>
+      </c>
       <c r="J213" s="19" t="n"/>
       <c r="K213" s="19" t="n"/>
       <c r="L213" s="19" t="n"/>
@@ -14949,7 +14992,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I219" s="19" t="n"/>
+      <c r="I219" s="19" t="inlineStr">
+        <is>
+          <t>81996-2F010[2004.6~]</t>
+        </is>
+      </c>
       <c r="J219" s="19" t="n"/>
       <c r="K219" s="19" t="n"/>
       <c r="L219" s="19" t="n"/>
@@ -16649,7 +16696,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I245" s="19" t="n"/>
+      <c r="I245" s="19" t="inlineStr">
+        <is>
+          <t>81996-3EG00, 81996-3EC00[뉴 쏘렌토]</t>
+        </is>
+      </c>
       <c r="J245" s="19" t="n"/>
       <c r="K245" s="19" t="n"/>
       <c r="L245" s="24" t="n"/>
@@ -20759,11 +20810,19 @@
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I310" s="24" t="n"/>
+      <c r="I310" s="24" t="inlineStr">
+        <is>
+          <t>819962L001</t>
+        </is>
+      </c>
       <c r="J310" s="19" t="n"/>
       <c r="K310" s="19" t="n"/>
       <c r="L310" s="24" t="n"/>
-      <c r="M310" s="24" t="n"/>
+      <c r="M310" s="24" t="inlineStr">
+        <is>
+          <t>954301D104</t>
+        </is>
+      </c>
       <c r="N310" s="19" t="n"/>
       <c r="O310" s="19" t="inlineStr">
         <is>
@@ -25199,7 +25258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A229"/>
+  <dimension ref="A1:A230"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.2"/>
   <cols>
     <col width="118" customWidth="1" style="15" min="1" max="1"/>
@@ -25300,1483 +25359,1490 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="57" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="56" t="n"/>
+      <c r="A16" s="57" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="56" t="inlineStr">
+      <c r="A17" s="57" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="56" t="inlineStr">
+      <c r="A18" s="57" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="56" t="inlineStr">
+      <c r="A19" s="57" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="56" t="inlineStr">
+      <c r="A20" s="57" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="56" t="inlineStr">
+      <c r="A21" s="57" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="56" t="inlineStr">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="56" t="inlineStr">
+      <c r="A23" s="57" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="56" t="n"/>
+      <c r="A24" s="57" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="56" t="inlineStr">
+      <c r="A25" s="57" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="56" t="inlineStr">
+      <c r="A26" s="57" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="56" t="inlineStr">
+      <c r="A27" s="57" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="56" t="inlineStr">
+      <c r="A28" s="57" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="56" t="inlineStr">
+      <c r="A29" s="57" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="56" t="inlineStr">
+      <c r="A30" s="57" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="56" t="inlineStr">
+      <c r="A31" s="57" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="56" t="inlineStr">
+      <c r="A32" s="57" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="56" t="n"/>
+      <c r="A33" s="57" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="56" t="inlineStr">
+      <c r="A34" s="57" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="56" t="inlineStr">
+      <c r="A35" s="57" t="inlineStr">
         <is>
           <t>- K3 (Forte, YD 페이스리프트) 2016: A7600 칩은 Lonsdor 8A 스마트키 PCB 지원 차종(K3 2016-2018)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="56" t="inlineStr">
+      <c r="A36" s="57" t="inlineStr">
         <is>
           <t>- K3 (Forte, YD 페이스리프트) 2017: 국내 현대모비스 원문 확인</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="56" t="inlineStr">
+      <c r="A37" s="57" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD) 2021: 더 뉴 K3(BD PE) 출시(2021.4). 95440-M6800은 한국 시장용 정품 HITAG AES ID4A(NCF29A1M)로 다수 판매처(mk3·abkeys·americankeysupply) 일치 확인 → 기존 'ID8A/ID47 미확정' 해소(PE 이전은 ID8A, PE 이후는 ID4A)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="56" t="inlineStr">
+      <c r="A38" s="57" t="inlineStr">
         <is>
           <t>- 스토닉 2017: 스토닉 국내 출시(2017.6.21) — 프라이드(UB)와 같은 플랫폼 공유 크로스오버. 국제 판매처(gskeyae.com) 확인: '2017-2018 KIA Stonic ... 8A Texas Crypto 128-bits AES' — 이전에 'ID47 추정'이라고 했던 건 정정함</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="56" t="inlineStr">
+      <c r="A39" s="57" t="inlineStr">
         <is>
           <t>- 쏘울 (Soul, PS) 2014: 칩: 95440-B2000·B2AA0 한국 시장용 정품 8A Texas Crypto 128bit AES, 4버튼(mk3·abkeys·remotesandkeys) — 이전 'ID47 추정'은 정정</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="56" t="inlineStr">
+      <c r="A40" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2016: 국제 판매처(go-parts.com, americankeysupply) 확인: Hitag3 ID47 - 이전에 ID6E-MA(DST80) 추정이라고 했던 건 정정함</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="56" t="inlineStr">
+      <c r="A41" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, MQ4) 2021: 칩: 95440-P2000(5버튼)·P2200(7버튼)·P2AD0(7버튼) 모두 정품 HITAG AES ID4A(mk3·abkeys·royalkeysupply) — 이전 '추정' 해소</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="56" t="inlineStr">
+      <c r="A42" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2021: 이전 '적용 시점 추정' 해소: G5025는 원문상 22년형</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="56" t="inlineStr">
+      <c r="A43" s="57" t="inlineStr">
         <is>
           <t>- 레이 2023: 95440-A3600(2022.8.31~)은 DST-AES ID6A 4버튼, 2023-2024 레이 적용(mk3·abkeys·vvdi)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="56" t="n"/>
+      <c r="A44" s="57" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="56" t="inlineStr">
+      <c r="A45" s="57" t="inlineStr">
         <is>
           <t>※ 연식별 참고 메모 (예전 비고 칸 내용 — 색 없는 행이라 비고에서 옮김)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="56" t="inlineStr">
+      <c r="A46" s="57" t="inlineStr">
         <is>
           <t>- 옵티마 (Optima, MS) 2005(단종): 옵티마 국내 마지막 연식(2005.10 단종, 로체로 세대교체). 국제 판매처(abkeys.com) 확인: PN 81996-3C010, 4D-60/HYN7R, 'KIA OPTIMA 2000-2005' 명시 — 나무위키 확인: EF쏘나타와 완전히 동일한 모델(플랫폼·전자장비 100% 공유)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="56" t="inlineStr">
+      <c r="A47" s="57" t="inlineStr">
         <is>
           <t>- 로체 (Optima, MG) 2005: 로체 국내 출시(2005.10). 국내 현대모비스(hellowcar) 스마트키 원문: 954402G000[~2008.5.28, 블랭킹 819962G020] → 954401M010[2008.8.28~2009.8.10, 819962G520] → 954402G100[2010.8.10~, 819962G030]. 2009.8.10~2010.8.10 사이 품번은 원문에 없음</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="56" t="inlineStr">
+      <c r="A48" s="57" t="inlineStr">
         <is>
           <t>- 로체 (Optima, MG) 2008: 국내 현대모비스 확인 — 2008년 안에 폴딩키·스마트키 부품 모두 전환</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="56" t="inlineStr">
+      <c r="A49" s="57" t="inlineStr">
         <is>
           <t>- 로체 (Optima, MG) 2009: 국내 현대모비스 확인 — 폴딩키 날짜 구간이 일부 겹쳐 표기됨(트림별 차이 가능성), 원문 그대로 병기</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="56" t="inlineStr">
+      <c r="A50" s="57" t="inlineStr">
         <is>
           <t>- 로체 (Optima, MG) 2010(단종): 로체 마지막 연식(2010) — K5로 세대교체. 국내 현대모비스(hellowcar) 스마트키 원문: 954402G000[~2008.5.28, 블랭킹 819962G020] → 954401M010[2008.8.28~2009.8.10, 819962G520] → 954402G100[2010.8.10~, 819962G030]. 2009.8.10~2010.8.10 사이 품번은 원문에 없음</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="56" t="inlineStr">
+      <c r="A51" s="57" t="inlineStr">
         <is>
           <t>- 포르테 (Forte, TD 세단) 2008: 포르테 세단(TD) 국내 출시(2008.8.21) — 이 해엔 세단만 있었고 쿠페는 아직 출시 전. 출시 당시 디럭스 트림은 '폴딩타입 무선도어 리모컨키' 기본(다나와 2008년형 트림표). 버튼시동 스마트키가 어느 트림부터 기본인지와 폴딩키 부품번호는 국내 원문에서 확인 못함</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="56" t="inlineStr">
+      <c r="A52" s="57" t="inlineStr">
         <is>
           <t>- K3 (Forte, YD/BD) 2018: K3(BD) 완전변경 출시(2018.2). 국내 현대모비스 원문: BD 스마트키 M6000[2018.1.8~8.30] → M6011[2018.8.30~2021.4.26] · M6501[2018.9.18~2021.3.24] → M6800[2021.4.5~2024.2.8] → M6801[2024.2.8~], 블레이드 81996M6020. BD 초기 스마트키(M6000/M6011/M6501, FCC CQOFD00430) 칩은 정품 기준 DST-AES ID8A(abkeys·tlkeys)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="56" t="inlineStr">
+      <c r="A53" s="57" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD) 2020: 2021년형(2020년 출시)부터 버튼시동 스마트키 전 트림 기본(모터그래프·엔카)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="56" t="inlineStr">
+      <c r="A54" s="57" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD 페이스리프트) 2022: 스마트키 전 트림 기본화 이후 폴딩키(M6400)의 적용 대상은 원문 미확인</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="56" t="inlineStr">
+      <c r="A55" s="57" t="inlineStr">
         <is>
           <t>- K3 (Forte, BD PE) 2024(단종): K3 국내 최종 연식 — 2024년 7월 완전 단종. 후속 K4는 국내 미출시(해외 전략형 모델), 국내 준중형 세단 수요는 셀토스·EV3·EV4로 대체됨</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="56" t="inlineStr">
+      <c r="A56" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, TF) 2010: 국내 현대모비스(hellowcar) 폴딩키 원문: TF 954302T500[~2012.7.6, 블랭킹 819962L000] → 954302T501[2012.7.6~, 819962L001] / JF 954302T570(블랭킹 81996A4000)·95430D4010 / DL3 95430L2000·L2010(블랭킹 81996L2000). 이전에 TF에 넣었던 2T570은 원문상 JF용이라 이동</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="56" t="inlineStr">
+      <c r="A57" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, TF) 2011: K5 하이브리드(TFE) 출시(2011)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="56" t="inlineStr">
+      <c r="A58" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, TF) 2013: 국내 현대모비스 확인 — 2013.6.10 기준 스마트키·비상키 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="56" t="inlineStr">
+      <c r="A59" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, TF/JF) 2015: K5(JF, 올 뉴 K5) 완전변경 출시(2015)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="56" t="inlineStr">
+      <c r="A60" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, JF) 2017: 더 뉴 K5(JF 페이스리프트) 출시(2017)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="56" t="inlineStr">
+      <c r="A61" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, JF) 2018: 더뉴K5 하이브리드 2세대(JFE) 출시(2018)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="56" t="inlineStr">
+      <c r="A62" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, JF) 2019: JF 마지막 연식</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="56" t="inlineStr">
+      <c r="A63" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, JF/DL3) 2019: K5(DL3) 완전변경 출시(2019.9)로 같은 해 전환 — 하이브리드 3세대(DL3KH)도 2019년 출시</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="56" t="inlineStr">
+      <c r="A64" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, DL3) 2020: 국내 현대모비스(hellowcar) 원문: L3010·L2200은 연식 라벨 없는 초기 품번, L2320·L2300은 21년형, L2420·L2400은 22년형</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="56" t="inlineStr">
+      <c r="A65" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, DL3/DL3 페이스리프트) 2023: 더 뉴 K5(DL3 페이스리프트) 출시(2023.9)로 전환되는 해 — 95440-L2520은 하이브리드와 공용</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="56" t="inlineStr">
+      <c r="A66" s="57" t="inlineStr">
         <is>
           <t>- K5 (Optima, DL3 페이스리프트) 2026: 국내 현대모비스(hellowcar) 원문상 PE 스마트키 L2500·L2510·L2520은 종료일 없는 현행 품번</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="56" t="inlineStr">
+      <c r="A67" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2009: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="56" t="inlineStr">
+      <c r="A68" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2010: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="56" t="inlineStr">
+      <c r="A69" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2011: 국내 현대모비스(hellowcar) 재확인 — 초기 스마트키(954403R000)용 블레이드는 819962J700(이전 기재 819963T000은 3R500용이라 정정). 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="56" t="inlineStr">
+      <c r="A70" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2012: 국내 현대모비스 확인 — 2012.11.5 기준 스마트키 전환. 카드키 원문: 954403R800[2012.10.30~2013.2.28, 블레이드 819963T100] → 954403R801[2013.2.28~2015.12.31] → 95443F6000[2015.12.9~2019.6.27, 블레이드 81996F6110] → 95443F6010[2019.5.30~]</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="56" t="inlineStr">
+      <c r="A71" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2013: 이전에 VG 카드키 블레이드를 81996-F6110으로, 카드키에 95443-F6000을 적었으나 둘 다 YG용이라 정정(VG 카드키 블레이드는 819963T100)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="56" t="inlineStr">
+      <c r="A72" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, VG) 2015: K7(YG) 완전변경 출시(2016.1)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="56" t="inlineStr">
+      <c r="A73" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, YG) 2016: 국내 현대모비스 확인 — 이모빌라이저 모듈(95420D4000)은 포터2·그랜드스타렉스와 공유</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="56" t="inlineStr">
+      <c r="A74" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, YG) 2019: 'K7 프리미어' 페이스리프트(2019.6)로 전환되는 해. 이전에 81996-F6110을 프리미어 스마트키 블레이드로 적었으나 원문상 카드키 블레이드라 정정(F6510 스마트키 블레이드는 원문 미확인). 스마트키 모듈(제어기) 95480-F6500</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="56" t="inlineStr">
+      <c r="A75" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, YG 프리미어) 2020: 스마트키 모듈(제어기): 95480-F6500</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="56" t="inlineStr">
+      <c r="A76" s="57" t="inlineStr">
         <is>
           <t>- K7 (Cadenza, YG 프리미어) 2021(단종): K7 국내 마지막 연식(2021.1 단종) — 후속 K8으로 이어짐. 스마트키 모듈: 95480-F6500(2019.6-2021.4 적용 확인)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="56" t="inlineStr">
+      <c r="A77" s="57" t="inlineStr">
         <is>
           <t>- K8 (GL3) 2021: K8 국내 출시(2021.4). 국내 현대모비스(hellowcar) 원문: L8000(주차보조X)/L8010(주차보조O)은 ~2024.2.13, 이후 L8001/L8011로 전환. 블레이드 S9000=주차보조X, L2020=주차보조O, 폴딩키용 81996-L2000</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="56" t="inlineStr">
+      <c r="A78" s="57" t="inlineStr">
         <is>
           <t>- K8 (GL3/GL3 페이스리프트) 2024: 국내 현대모비스(hellowcar): 2024.2.13은 초기형 L8000·L8010 → L8001·L8011 품번 개정일이고, 페이스리프트(2024.8.9 공개, 위키백과)부터 L8500·L8510·L8520·L8530 적용 — 이전에 2.13을 페이스리프트 전환일로 적었던 것 정정. NFC 카드키 AT954AP000·GZ954AP000(K8GL3/EV6/스포티지NQ5/쏘렌토MQ4/카니발KA4 공용 리스팅)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="56" t="inlineStr">
+      <c r="A79" s="57" t="inlineStr">
         <is>
           <t>- K8 (GL3 페이스리프트) 2026: 원문상 PE 스마트키 4종은 종료일 없는 현행 품번</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="56" t="inlineStr">
+      <c r="A80" s="57" t="inlineStr">
         <is>
           <t>- K9 (K900/Quoris, KH) 2012: K9(KH) 국내 출시(2012.3.27). 국내 현대모비스(hellowcar) 원문: 스마트키 954403T200[2012.3.27~2017.12.30]→819963T000, 카드키 954433T000[~2013.7.1, 버튼X]→954433T100[2013.7.1~2014.11.15]→954433T200[2014.11.10~2017.12.30, 버튼X], 카드키 블레이드 819963T100</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="56" t="inlineStr">
+      <c r="A81" s="57" t="inlineStr">
         <is>
           <t>- K9 (K900/Quoris, KH) 2013: 국내 현대모비스(hellowcar) 원문: 3T200[2012.3.27~2017.12.30], 3T300[2013.9.1~2014.1.1]. 카드키 날짜도 원문 확인</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="56" t="inlineStr">
+      <c r="A82" s="57" t="inlineStr">
         <is>
           <t>- K9 (K900/Quoris, KH) 2016: 이전에 2016년 카드키 블레이드를 81996-3T200으로 적었으나 원문상 카드키 블레이드는 819963T100이라 정정</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="56" t="inlineStr">
+      <c r="A83" s="57" t="inlineStr">
         <is>
           <t>- K9 (K900/Quoris, KH/RJ) 2018: K9(RJ, '더 K9') 완전변경 출시(2018.4)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="56" t="inlineStr">
+      <c r="A84" s="57" t="inlineStr">
         <is>
           <t>- K9 (K900, RJ) 2021: 국내 현대모비스 확인 — 2021.5.21 기준 '더뉴 K9'로 부품 전환</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="56" t="inlineStr">
+      <c r="A85" s="57" t="inlineStr">
         <is>
           <t>- K9 (K900, RJ) 2025: 국내 현대모비스(hellowcar) 원문: 'K9RJ [2021.5.21 이후~] 95440J6610·J6600·81996J6000·J6100' — 종료일 없는 현행 품번</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="56" t="inlineStr">
+      <c r="A86" s="57" t="inlineStr">
         <is>
           <t>- 프라이드 JB 2005: 프라이드(JB) 국내 출시(2005.4.7) — 리오(BC) 후속, 국내 차명이 '프라이드'로 부활. 기본트림(LX)은 무선도어리모콘키만 제공</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="56" t="inlineStr">
+      <c r="A87" s="57" t="inlineStr">
         <is>
           <t>- 프라이드 JB/UB 2011: 올 뉴 프라이드(UB) 완전변경 출시(2011.9.28)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="56" t="inlineStr">
+      <c r="A88" s="57" t="inlineStr">
         <is>
           <t>- 프라이드 UB 2013: 국내 현대모비스 확인</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="56" t="inlineStr">
+      <c r="A89" s="57" t="inlineStr">
         <is>
           <t>- 프라이드 UB (더 뉴 프라이드) 2014: 더 뉴 프라이드 페이스리프트(2014.12) 출시. 국내 현대모비스(hellowcar) 재확인 — 비상키 접두사가 81996이 아니라 81999인 경우가 2개 있어서 정정함</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="56" t="inlineStr">
+      <c r="A90" s="57" t="inlineStr">
         <is>
           <t>- 프라이드 UB (더 뉴 프라이드) 2017(단종): 프라이드 국내 마지막 연식(2017.9 단종) — 4세대(리오 YB)는 국내 출시가 백지화되고 같은 플랫폼의 크로스오버 스토닉(SP2)으로 대체, 국내 후속 없음(위키백과 확인)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="56" t="inlineStr">
+      <c r="A91" s="57" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2004: 국제 판매처(remotesandkeys.com, key4.com) 확인: PN 81996-3FA10, ILCO KK7-PT, 4D60 — 리모컨 없는 막대형 키(2003-2006 공용)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="56" t="inlineStr">
+      <c r="A92" s="57" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2005: 국제 판매처 확인 — 막대형 키</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="56" t="inlineStr">
+      <c r="A93" s="57" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2006: 국제 판매처 확인 — 막대형 키</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="56" t="inlineStr">
+      <c r="A94" s="57" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2007: 국제 판매처(remotesandkeys.com) 확인: PN 81996-3F050, ILCO KK9-PT, ID46 — 리모컨 없는 막대형 키</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="56" t="inlineStr">
+      <c r="A95" s="57" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH) 2008: 국제 판매처 확인 — 막대형 키</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="56" t="inlineStr">
+      <c r="A96" s="57" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH 프리미엄) 2009: 오피러스 프리미엄 페이스리프트(2009.5) 출시 — 국내 현대모비스 확인</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="56" t="inlineStr">
+      <c r="A97" s="57" t="inlineStr">
         <is>
           <t>- 오피러스 (Opirus, GH 프리미엄) 2012(단종): 오피러스 국내 마지막 연식(2012.5) — K7(Cadenza)로 세대교체, 직접적 후속 없음</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="56" t="inlineStr">
+      <c r="A98" s="57" t="inlineStr">
         <is>
           <t>- 스팅어 (Stinger, CK) 2017: 스팅어 국내 출시(2017.5) — 제네시스 G70(IK)와 플랫폼 공유</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="56" t="inlineStr">
+      <c r="A99" s="57" t="inlineStr">
         <is>
           <t>- 스팅어 (Stinger, CK) 2018: 국내 판매처(모터스K) 확인: 2018년 7월 이후 생산된 19년형은 95440-J5200이 맞지 않을 수 있고 95440-J5210 적용. 국내 현대모비스(hellowcar): J5200·J5210은 ~2020.7.28, 이후 J5700·J5710, 블레이드 81996J5000</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="56" t="inlineStr">
+      <c r="A100" s="57" t="inlineStr">
         <is>
           <t>- 스팅어 (Stinger, CK) 2020: 국내 현대모비스 확인 — 2020.7.28 기준 페이스리프트 부품 전환</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="56" t="inlineStr">
+      <c r="A101" s="57" t="inlineStr">
         <is>
           <t>- 스팅어 (Stinger, CK 페이스리프트) 2023(단종): 스팅어 국내외 단종(2023.4) — 직접적 후속 없음</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="56" t="inlineStr">
+      <c r="A102" s="57" t="inlineStr">
         <is>
           <t>- 스토닉 2020: 페이스리프트('더 뉴 스토닉') 출시(2020)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="56" t="inlineStr">
+      <c r="A103" s="57" t="inlineStr">
         <is>
           <t>- 스토닉 2023: 생산지 이관(광명→서산 동희오토), 국내 부품번호는 초기형과 동일 계열로 확인, 페이스리프트 이후 세부 개정 여부는 미확인</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="56" t="inlineStr">
+      <c r="A104" s="57" t="inlineStr">
         <is>
           <t>- 스토닉 2024: 국내 판매처(모터스K)·헬로우카 원문: 스마트키 95440H8000·블랭킹 81999H8300 '적용시점 2017.6.21~'(종료일·개정품번 없음) → 같은 PN이므로 칩도 ID8A</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="56" t="inlineStr">
+      <c r="A105" s="57" t="inlineStr">
         <is>
           <t>- 셀토스 (SP2) 2020: 연식변경(2020.7.1) — 전방충돌방지보조 등 안전사양 추가</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="56" t="inlineStr">
+      <c r="A106" s="57" t="inlineStr">
         <is>
           <t>- 셀토스 (SP2/SP2 PE) 2022: '더 뉴 셀토스'(SP2 PE) 페이스리프트 출시(2022.7)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="56" t="inlineStr">
+      <c r="A107" s="57" t="inlineStr">
         <is>
           <t>- 쏘울 (Soul, AM) 2008: 쏘울 국내 출시(2008)</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="56" t="inlineStr">
+      <c r="A108" s="57" t="inlineStr">
         <is>
           <t>- 쏘울 (Soul, AM) 2009: 칩: transpondery.com 'KIA SOUL 2008-2013: Philips PCF7952A / ID46 / Hitag 2', 2013 정품 폴딩키 '46 Chip'(vvdi)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="56" t="inlineStr">
+      <c r="A109" s="57" t="inlineStr">
         <is>
           <t>- 쏘울 부스터 (Soul, SK3) 2019: 쏘울 부스터(SK3) 완전변경 출시(2019). 국내 현대모비스(hellowcar) 확인 — 연식별 세부 날짜는 추가 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="56" t="inlineStr">
+      <c r="A110" s="57" t="inlineStr">
         <is>
           <t>- 쏘울 부스터 (Soul, SK3) 2025(단종): 쏘울 국내외 최종 단종 연식(2025) — 후속 없음(나무위키 확인)</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="56" t="inlineStr">
+      <c r="A111" s="57" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2011: 레이 국내 출시(2011.11) — 국내 현대모비스(hellowcar) 날짜별 원문 재확인</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="56" t="inlineStr">
+      <c r="A112" s="57" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2015: 이전에 2015-2016 폴딩키를 A3100/A3110으로 적었으나 원문상 A3001 구간(2012.9.10~2017.12.12)이라 정정</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="56" t="inlineStr">
+      <c r="A113" s="57" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2017: 국내 현대모비스 확인 — 2017년 하반기 스마트키 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="56" t="inlineStr">
+      <c r="A114" s="57" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2022: 국내 현대모비스 확인 — 2022.9.5 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="56" t="inlineStr">
+      <c r="A115" s="57" t="inlineStr">
         <is>
           <t>- 레이 (Ray, TAM) 2025: 원문상 스마트키 A3600[2022.8.31~], 폴딩키 A3600[2022.8.31~]·A3610[2023.6.16~] 모두 종료일 없는 현행 품번</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="56" t="inlineStr">
+      <c r="A116" s="57" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, SA) 2004: 모닝 국내 출시(2004)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="56" t="inlineStr">
+      <c r="A117" s="57" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, SA) 2010: TA 완전변경 출시(2011)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="56" t="inlineStr">
+      <c r="A118" s="57" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, TA) 2011: 올뉴 모닝(TA) 출시(2011.1). 국내 현대모비스(hellowcar) 원문: TA 스마트키 954401Y500[~2013.8.16, 블랭킹 819961Y020] → 954401Y600[2013.8.16~2016.12.29, 819961Y620] / JA 스마트키 95440G6000[2016.10.25~, ~22년식]·95440G6100[22년식~] ~2023.6.27(블랭킹 81996G6020) → 95440G6500[2023.6.27~, 81996P2800]. 이전에 TA에 G6000·G6100, JA에 1Y500·1Y600을 적었던 것은 서로 뒤바뀐 오류라 정정</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="56" t="inlineStr">
+      <c r="A119" s="57" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, TA) 2012: 국내 현대모비스 확인 — 2012.9.27 기준 폴딩키 전환</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="56" t="inlineStr">
+      <c r="A120" s="57" t="inlineStr">
         <is>
           <t>- 모닝 (Morning, TA) 2013: 국내 현대모비스 확인 — 2013.8.1 기준 폴딩키 전환</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="56" t="inlineStr">
+      <c r="A121" s="57" t="inlineStr">
         <is>
           <t>- EV3 (SV) 2024: EV3 국내 출시(2024.7) — K3 플랫폼 기반 E-GMP, 국내 현대모비스 확인. 부품번호는 '주차보조/디지털키' 조합별 4종</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="56" t="inlineStr">
+      <c r="A122" s="57" t="inlineStr">
         <is>
           <t>- EV3 (SV) 2026: '더 EV3' 연식변경(2026.2.2 출시)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="56" t="inlineStr">
+      <c r="A123" s="57" t="inlineStr">
         <is>
           <t>- EV6 (CV) 2021: 국내 현대모비스(hellowcar) 원문: CV000(주차보조X)/CV010(주차보조O) ~2024.2.7, 이후 CV001/CV011. 블레이드 CV000=주차보조X, CV010=주차보조O</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="56" t="inlineStr">
+      <c r="A124" s="57" t="inlineStr">
         <is>
           <t>- EV6 (CV) 2024: 국내 현대모비스(hellowcar): 초기형 CV000·CV010[~2024.2.7] → CV001·CV011[2024.2.7~], 페이스리프트 전용 CV500·CV510·CV520 별도 리스팅(적용 시작일 원문 미확인). 칩: 95440-CV000 정품 HITAG AES ID4A(tlkeys)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="56" t="inlineStr">
+      <c r="A125" s="57" t="inlineStr">
         <is>
           <t>- EV6 (CV) 2025: 이전에 2025~2026년에 초기형 CV001·CV011을 적었으나 페이스리프트 전용 CV500·CV510·CV520으로 정정(hellowcar). CV510·CV520 해외 판매처 적용 2025~2026</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="56" t="inlineStr">
+      <c r="A126" s="57" t="inlineStr">
         <is>
           <t>- EV9 2023: EV9 국내 출시(2023.5). 국내 현대모비스(hellowcar): 스마트키 DO000·DO010·DO020·DO030(사양 표기 원문 그대로), 블랭킹 81996DO000, 케이스 81995DO000 — 종료일 없는 현행 품번. 이전에 넣었던 DO060은 국내 원문에 없어 삭제</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="56" t="inlineStr">
+      <c r="A127" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, JE/KM) 2004: 칩: 트랜스폰더 카탈로그 'SPORTAGE 2004~ Philips Crypto2 ID46', 247geek 'Kia Sportage 25.08.2004-01.11.2012 ID46(PCF7936)'</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="56" t="inlineStr">
+      <c r="A128" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, JE/KM) 2010: SL 완전변경 출시(2010)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="56" t="inlineStr">
+      <c r="A129" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, SL) 2011: 국내 현대모비스(hellowcar) 및 국제 판매처(gskeyae) 확인. transpondery.com 카탈로그 원문 확인: SL세대는 트림별로 DST80/ID6E-MA(플립) 또는 ID46/PCF7952A(스마트) 혼재 — 폴딩키 PN 국내 확인, 이전에 누락됐던 것 추가</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="56" t="inlineStr">
+      <c r="A130" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, SL) 2012: transpondery.com 카탈로그 확인</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="56" t="inlineStr">
+      <c r="A131" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, SL) 2015: 올 뉴 스포티지(QL) 완전변경 출시(2015)로 전환되는 해 — QL 초기부터 확정 ID47(NCF2971X) 확인됨(americankeysupply)</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="56" t="inlineStr">
+      <c r="A132" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2018: 국내 현대모비스 확인 — 2018년 중반 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="56" t="inlineStr">
+      <c r="A133" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2019: 국내 현대모비스(hellowcar) 원문: D9000[2015.8.3~2018.8.7] → D9500[2018.6.26~] → D9600[2019.2.26~], 블랭킹 81996A4040</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="56" t="inlineStr">
+      <c r="A134" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, QL) 2021: 디 올 뉴 스포티지(NQ5) 완전변경 출시(2021)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="56" t="inlineStr">
+      <c r="A135" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, NQ5) 2022: 국내 현대모비스(hellowcar) 원문: 주차보조X P1100→P1110[2023.1.31~], 블랭킹 81999J7020 / 주차보조O P1200→P1210[2023.1.31~], 블랭킹 81996P1060. 이전 블레이드 기재(81926-J7000, 81996-K0000)는 원문과 달라 정정. 칩 ID4A(keyshop-online 등)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="56" t="inlineStr">
+      <c r="A136" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, NQ5) 2023: 국내 현대모비스 확인 — 2023.1.31 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="56" t="inlineStr">
+      <c r="A137" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, NQ5) 2024: 더 뉴 스포티지(NQ5 PE) 출시(2024.11.5, 나무위키). 국내 현대모비스(hellowcar): PE 스마트키 P1AB0·P1AC0·P1AE0·P1AF0, 블랭킹 81996S9600(사양별 구분은 원문 미확인)</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="56" t="inlineStr">
+      <c r="A138" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (Sportage, NQ5) 2025: 이전에 2025~2026년에 초기형 PN(P1110·P1210)을 적었으나 2024.11 페이스리프트 이후 PE 부품으로 정정. 폴딩키 P1000의 PE 적용 여부는 원문 미확인</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="56" t="inlineStr">
+      <c r="A139" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, BL) 2009: 쏘렌토R(XM) 완전변경 출시(2009.5)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="56" t="inlineStr">
+      <c r="A140" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, XM) 2010: 국내 현대모비스 확인 — 2010.7.1 기준 스마트키 전환. 폴딩키 PN 누락분 추가(연식별 적용 날짜는 미확인)</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="56" t="inlineStr">
+      <c r="A141" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, XM) 2012: 뉴 쏘렌토R(페이스리프트) 출시(2012.7)</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="56" t="inlineStr">
+      <c r="A142" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, XM) 2013: 국내 현대모비스(hellowcar) 재확인 — 954402P500용 블레이드는 819962P300(이전 819962J700은 오기)</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="56" t="inlineStr">
+      <c r="A143" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, XM/UM) 2014: 쏘렌토(UM) 완전변경 출시(2014.8)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="56" t="inlineStr">
+      <c r="A144" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, UM) 2015: 국내 현대모비스(hellowcar) 원문: 95440C5000[2014.8.16~2017.7.24, 블레이드 81996C5040] → 95440C5500(더뉴쏘렌토)[2017.6.29~, 블레이드 81996C5050]. 칩: C5000·C5500 모두 HITAG3 ID47(한국 시장용 정품 mk3·tlkeys), 4버튼</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="56" t="inlineStr">
+      <c r="A145" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, UM) 2017: 더 뉴 쏘렌토(UM 페이스리프트) 출시(2017.7)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="56" t="inlineStr">
+      <c r="A146" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, UM 페이스리프트) 2018: 국내 현대모비스 원문: 95440C5500[2017.6.29~] 적용</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="56" t="inlineStr">
+      <c r="A147" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, UM/MQ4) 2020: 쏘렌토(MQ4) 완전변경 출시(2020.3)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="56" t="inlineStr">
+      <c r="A148" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, MQ4) 2023: 2023.8 페이스리프트('더 뉴 쏘렌토')로 전환되는 해 — 하이브리드 공용 신형 스마트키(95440-P2AD0) 등장</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="56" t="inlineStr">
+      <c r="A149" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (Sorento, MQ4 페이스리프트) 2024: 국내 현대모비스(hellowcar): 더 뉴 쏘렌토(MQ4 PE) 스마트키 P2AA0·P2AB0·P2AC0·P2AD0 4종 확인(사양별 구분은 원문 미확인). 카폼: P2AD0 적용 '더 뉴 쏘렌토 2023.8 이후'(종료일 없음). 칩 ID4A</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="56" t="inlineStr">
+      <c r="A150" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2008: 모하비 국내 출시(2008.1). 국내 현대모비스(hellowcar) 원문: 2J800[~2010.12.13] → 2J860[2010.12.13~2011.6.1] → 2J870[2011.6.1~2015.12.23] (블레이드 819962J700) / 1W000[2016.1.15~2019.6.13, 819962J700] / 2J200(더뉴 모하비)[2016.11.15~2019.6.13, 819962J800]</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="56" t="inlineStr">
+      <c r="A151" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2010: 국내 현대모비스 확인 — 2010.12.13 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="56" t="inlineStr">
+      <c r="A152" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2011: 국내 현대모비스 확인 — 2011.6.1 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="56" t="inlineStr">
+      <c r="A153" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2012: 이전에 2012~2013년에 1W000·2J200을 함께 적었으나 원문상 둘 다 2016년부터라 정정</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="56" t="inlineStr">
+      <c r="A154" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2014: 모하비 더 마스터(1차 페이스리프트) 출시(2014.5)</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="56" t="inlineStr">
+      <c r="A155" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM) 2018: 모하비 더 마스터(2차 완전변경급 페이스리프트) 출시(2019)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="56" t="inlineStr">
+      <c r="A156" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM 더마스터) 2019: 국제 판매처(abkeys.com) 확인 — 더마스터부터 ID46에서 ID47로 칩 세대 전환. 초기형(2008-2018)은 abkeys 확인 PCF7952A ID46</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="56" t="inlineStr">
+      <c r="A157" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM 더마스터) 2021: 국내 현대모비스 확인 — 2021.6.8 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="56" t="inlineStr">
+      <c r="A158" s="57" t="inlineStr">
         <is>
           <t>- 모하비 (Mohave, HM 더마스터) 2025: 국내 현대모비스(hellowcar) 원문: 모하비 더마스터[2019.8.22~] 2J500[~2021.6.8] → 2J550·2JAA0[2021.6.8~, 종료일 없음], 블랭킹 819962J900</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="56" t="inlineStr">
+      <c r="A159" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2016: 니로(DE) 국내 출시(2016.3.7, 95440-G5000 출시일과 일치). 칩: 같은 PN(95440-G5000) 정품 Hitag3 ID47 확인. 국내 현대모비스(hellowcar) 원문: G5000[~2019.2.28, 블랭킹 81996G5A20] → G5010[2019.2.28~] · G5025[22년형] · DB000[니로 플러스], 이후 블랭킹 81999J7020</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="56" t="inlineStr">
+      <c r="A160" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2017: 국제 판매처(keyshop-online, dfwkeys4cars) 확인 — Hitag3 ID47</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="56" t="inlineStr">
+      <c r="A161" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2018: 이전에 2018년에 G5010을 함께 적었으나 원문상 G5010은 2019.2.28부터라 정정</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="56" t="inlineStr">
+      <c r="A162" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2019: 니로 플러스(택시형) 출시 — 별도 스마트키 PN(95440-DB000)</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="56" t="inlineStr">
+      <c r="A163" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE) 2020: 니로(DE) 페이스리프트(2019.7)</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="56" t="inlineStr">
+      <c r="A164" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, DE/SG2) 2022: 디 올 뉴 니로(SG2) 완전변경 출시(2022.1)로 전환되는 해 — 이때 칩이 ID47(Hitag3)에서 ID4A(Hitag AES)로 세대 전환. 디지털키2 터치 옵션 최초 도입</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="56" t="inlineStr">
+      <c r="A165" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, SG2) 2023: 블레이드 매칭: 원문 옵션 순서(주차보조X→81999J7020, 주차보조O→81996P1060), 셀토스·스포티지 NQ5 원문과 동일 구성</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="56" t="inlineStr">
+      <c r="A166" s="57" t="inlineStr">
         <is>
           <t>- 니로 (Niro, SG2) 2024: 국내 현대모비스 확인 — 2024.2.7 기준 부품번호 전환</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="56" t="inlineStr">
+      <c r="A167" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RS) 1999: 카렌스(RS) 국내 출시(1999)</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="56" t="inlineStr">
+      <c r="A168" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RS) 2002: 카렌스2/엑스트렉 페이스리프트(2002)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="56" t="inlineStr">
+      <c r="A169" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, UN) 2007: 국내 현대모비스(hellowcar) 폴딩키 원문: D101[2007.7.2~2008.5.27] → D102[2008.5.27~2010.6.16] → D103[2010.6.1~2012.7.17] → D104[2012.7.1~2012.7.17, 블랭킹 819962L001] / RP 95430A4000[2013.2.28~2016.6.30]. D100은 부품만 확인되고 날짜 옵션이 원문에 없음</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="56" t="inlineStr">
+      <c r="A170" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, UN/RP) 2013: 올 뉴 카렌스(RP) 완전변경 출시(2013.3.29). transpondery.com 카탈로그 원문 확인: RP세대는 트림별로 DST80/ID6E-MA(플립) 또는 ID46/PCF7952A(스마트) 혼재 - 이전에 스마트키만 쓰고 플립키 트림을 빠뜨렸던 것 정정</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="56" t="inlineStr">
+      <c r="A171" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RP) 2016: 더 뉴 카렌스(RP 페이스리프트) 출시(2016.7)</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="56" t="inlineStr">
+      <c r="A172" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RP) 2017: 폴딩키 95430A4000은 원문상 2016.6.30까지 — 더 뉴 카렌스(2016.7~) 폴딩키 품번은 원문에서 확인 못해 공란</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="56" t="inlineStr">
+      <c r="A173" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 (Carens, RP) 2018(단종): 카렌스 국내 최종 연식 — 2018년 10월 공식 단종. 4세대(KY, 2022+ 해외)는 인도 등 전략시장 전용, 국내 미판매, 국내 후속 없음(나무위키 확인)</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="56" t="inlineStr">
+      <c r="A174" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, KV-II/GQ) 2005: 그랜드카니발(VQ) 완전변경 출시(2005.7)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="56" t="inlineStr">
+      <c r="A175" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, VQ) 2006: 그랜드카니발(VQ). 칩·블레이드: 정품 81996-4D040 PCF7936 ID46(abkeys), 'Sedona 2006-2012 ID46 81996-4D040'(locksmithkeyless). 폴딩키: 2008.6.2 기준 001/011/021 → 002/012/022 계열 전환, 끝자리는 버튼 수(3/5/6버튼) 구분(hellowcar)</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="56" t="inlineStr">
+      <c r="A176" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, VQ) 2010: 타이거노즈 그릴 적용 페이스리프트(2010)</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="56" t="inlineStr">
+      <c r="A177" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, VQ/YP) 2014: 올 뉴 카니발(YP) 출시(2014.6). 국내 현대모비스(hellowcar) 원문: YP 스마트키 A9300(6버튼, 전동도어O)·A9100(4버튼, 전동도어X)[2014.5.26~], 블랭킹 81996A4040 — 이전 기재 95440-A9200은 국내 원문에 없는 번호라 삭제</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="56" t="inlineStr">
+      <c r="A178" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, YP) 2015: 국제 판매처(abkeys.com) 확인 — Hitag3 ID47</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="56" t="inlineStr">
+      <c r="A179" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, YP) 2018: 더 뉴 카니발(YP PE 페이스리프트) 출시(2018.3.13)</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="56" t="inlineStr">
+      <c r="A180" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, YP) 2020: 카니발(KA4) 출시(2020.8). 국내 현대모비스(hellowcar) 원문: 슬라이딩도어자동X는 P2000[~2020.7.20]→R0000[2020.7.20~]→R0430(22년형), 블랭킹 81996P2700 / 자동O는 R0100→R0420(22년형), 블랭킹 81996R0710 / 주차보조버튼O는 R0510</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="56" t="inlineStr">
+      <c r="A181" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, KA4) 2022: 국제 판매처(Amazon/KEYECU) 확인 — '4A Chip' 명시</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="56" t="inlineStr">
+      <c r="A182" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, KA4) 2023: '더 뉴 카니발'(KA4 PE 페이스리프트) 출시(2023.10)로 전환되는 해</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="56" t="inlineStr">
+      <c r="A183" s="57" t="inlineStr">
         <is>
           <t>- 카니발 (Carnival, KA4 PE) 2024: 국내 현대모비스(hellowcar): 더 뉴 카니발(KA4 PE) 스마트키 R0800·R0810·R0820·R0840·R0850·R0AA0·R0AB0·R0AE0·R0AF0, 블랭킹 81996P2800(케이스 81995P2000). 사양별 구분은 원문 미확인. 이전 기재 R0870은 국내 원문에 없어 삭제, 블레이드도 P2700/R0710 → P2800으로 정정</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="56" t="inlineStr">
+      <c r="A184" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 EV (전기차) 2021: 국내 현대모비스 원문: CP000[~2021.7.5, 블레이드 81996CP000] → CP500[2021.7.5~] → CP600[2023.5.18~, 블레이드 81996CP100]</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="56" t="inlineStr">
+      <c r="A185" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 EV (전기차) 2022: 이전에 2022년에 CP600을 함께 적었으나 원문상 CP600은 2023.5.18부터라 정정</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="56" t="inlineStr">
+      <c r="A186" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2003: 카키넘버원(국내 키 도매) 확인: 81996-4E000 일반키[2004.9.1~2016.8.31], 81996-4E010 이모빌라이저키(4D 칩), 81996-4E020 이모빌라이저키(46 칩), 81996-4E031 폴딩키 블레이드[2013.1.17~2016.8.31], 81996-4F700 폴딩키 블레이드[2016.8.31~]. 이모빌라이저키 4종의 연식 구간은 원문에 없어 차대번호로 확인 필요 — 이전에 연식별로 나눠 적었던 막대키 PN은 근거 없는 배분이라 삭제하고 전 구간 공통 후보로 정리. MK3 릴리즈노트: 봉고3 ID46/BOSCH 95P08</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="56" t="inlineStr">
+      <c r="A187" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2004: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="56" t="inlineStr">
+      <c r="A188" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2005: 이모빌라이저: MK3 릴리즈노트는 봉고3를 ID46·BOSCH 95P08로 분류하나, 국내 정비 자료에 봉고3 133마력 델파이 ECU(39111-4A520)와 델파이형 CRDi 인젝터가 확인됨 → 엔진/ECU 사양에 따라 4D·46 키가 나뉘는 것으로 보이나 연식·사양 매칭 원문은 없음</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="56" t="inlineStr">
+      <c r="A189" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2006: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="56" t="inlineStr">
+      <c r="A190" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2007: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="56" t="inlineStr">
+      <c r="A191" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2008: 페이스리프트(2008) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="56" t="inlineStr">
+      <c r="A192" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2009: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="56" t="inlineStr">
+      <c r="A193" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2010: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="56" t="inlineStr">
+      <c r="A194" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2011: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="56" t="inlineStr">
+      <c r="A195" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2012: 이전에 2012~2015년 폴딩키를 954304E500으로 적었으나 원문상 E500(C타입)은 2016.8.31부터라 정정</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="56" t="inlineStr">
+      <c r="A196" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2013: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="56" t="inlineStr">
+      <c r="A197" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2014: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="56" t="inlineStr">
+      <c r="A198" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2015: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="56" t="inlineStr">
+      <c r="A199" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2016: 3차 페이스리프트(2016) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="56" t="inlineStr">
+      <c r="A200" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2017: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="56" t="inlineStr">
+      <c r="A201" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2018: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="56" t="inlineStr">
+      <c r="A202" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2019: 4차 페이스리프트(2019) — MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="56" t="inlineStr">
+      <c r="A203" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2020: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="56" t="inlineStr">
+      <c r="A204" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2021: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="56" t="inlineStr">
+      <c r="A205" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2022: 2021.12.2~2023.12 구간 폴딩키 PN은 국내 원문에서 확인하지 못해 공란</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="56" t="inlineStr">
+      <c r="A206" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2023: MK3 프로그래머 릴리즈노트 확인: 봉고3은 ID46/BOSCH 95P08 ECU</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="56" t="inlineStr">
+      <c r="A207" s="57" t="inlineStr">
         <is>
           <t>- 봉고3 (Bongo3, J) 2024: 국내 현대모비스(hellowcar): 내연 봉고3 스마트키 954404EGA0·블레이드 81996CP100 리스팅 확인. 버튼시동 스마트키는 LPG 터보 10.25인치 내비 패키지 옵션으로 확인(카눈 가격표)</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="56" t="n"/>
+      <c r="A208" s="57" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="56" t="inlineStr">
+      <c r="A209" s="57" t="inlineStr">
         <is>
           <t>※ 2차 재조사로 확인한 근거 (2026.9, 색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="56" t="inlineStr">
+      <c r="A210" s="57" t="inlineStr">
         <is>
           <t>- 포르테 (TD) 2009-2011: 폴딩키 95430-1M250(Cerato 2010-2013 433MHz) PCF7936 ID46(abkeys·tlkeys), 블랭킹 81996-1M020(카다몰 포르테 키-블랭킹 피아이씨)</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="56" t="inlineStr">
+      <c r="A211" s="57" t="inlineStr">
         <is>
           <t>- K3 (YD) 2012-2015: 폴딩키 95430-A7100(Cerato 2013-2017 OKA-870T) 4D60 Carbon 80bit = DST80(ID6E-MA)(abkeys), 95430-A7200도 4D60 칩 키(keyless2go) — 이전 "4D60·ID46 상충"은 80bit DST80로 정리</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="56" t="inlineStr">
+      <c r="A212" s="57" t="inlineStr">
         <is>
           <t>- K3 (BD) 2019: 95440-M6011·M6501(FCC CQOFD00430) 8A Texas Crypto 128bit AES(검색요약 key4·keydirect·abkeys M6010) — dfwkeys4cars 종합표의 ID47은 품번 근거 없어 제외</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="56" t="inlineStr">
+      <c r="A213" s="57" t="inlineStr">
         <is>
           <t>- 프라이드 JB: 국내 이모빌라이저키 81996-1G100(뉴프라이드 2005.2.15~2009.12.10, 드림열쇠), 칩 없는 키 81996-1G000(Rio 2005-2011) — 같은 플랫폼 베르나 MC 81996-1E010도 ID46</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="56" t="inlineStr">
+      <c r="A214" s="57" t="inlineStr">
         <is>
           <t>- 프라이드 UB 2012: 2011.9 출시 스마트키 95440-1W000 계열(헬로우카 프라이드UB 954401W000/1W040/1W001) — 2013년과 같은 키</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="56" t="inlineStr">
+      <c r="A215" s="57" t="inlineStr">
         <is>
           <t>- 모닝 (SA) 2005-2009: 현대모비스 모닝SA 키 81996-07020·07100(헬로우카), 같은 계열 Picanto 81996-07010 PCF7936 ID46 HYN6(abkeys 2005+)</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="56" t="inlineStr">
+      <c r="A216" s="57" t="inlineStr">
         <is>
           <t>- 모닝 (JA): 폴딩키 95430-G6600 4D-60 Carbon 80bit(DST80, abkeys·tlkeys), 스마트키 95440-G6000·G6100 DST-AES ID8A(mk3·keyshop-online·tlkeys) — 이전 "DST80 vs ID75 상충"은 폴딩키·스마트키 칩이 다른 것</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="56" t="inlineStr">
+      <c r="A217" s="57" t="inlineStr">
         <is>
           <t>- EV4 (CT1): 95440-EZ300(EV4 2025 7버튼) NCF29A HITAG AES(auto-keys.eu) → ID4A</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="56" t="inlineStr">
+      <c r="A218" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (JE/KM): 드림열쇠 "뉴스포티지 81996-2F010(04년6월~), 쎄라토(05년~)", 81996-2F010 PCF7936 ID46 HYN6(abkeys)</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="56" t="inlineStr">
+      <c r="A219" s="57" t="inlineStr">
         <is>
           <t>- 스포티지 (SL) 2013-2014: 플립키 95430-3W200 PCF7936 HITAG2 ID46 HY22(auto-keys.eu OEM) — ID6E-MA 표기는 2011-2012 플립키 해당</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="56" t="inlineStr">
+      <c r="A220" s="57" t="inlineStr">
         <is>
           <t>- 쏘렌토 (BL): 국내 이모빌라이저 키 81996-3EG00(드림열쇠), 뉴 쏘렌토 이모빌라이저 키블레이드 81996-3EC00(카키넘버원·대남열쇠) PCF7936 ID46 HYN7R(abkeys)</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="56" t="inlineStr">
+      <c r="A221" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 (UN) 2008-2011: Carens 2006(후기)-2011 ID46 PCF7936 키(autoecupart), 국내 폴딩키 954301D101~D104(헬로우카) 적용 기간 확인</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="56" t="n"/>
+      <c r="A222" s="57" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="56" t="inlineStr">
+      <c r="A223" s="57" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="56" t="inlineStr">
+      <c r="A224" s="57" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="56" t="inlineStr">
+      <c r="A225" s="57" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="56" t="inlineStr">
+      <c r="A226" s="57" t="inlineStr">
         <is>
           <t>- '키종류' 열(칩코드와 키블레이드(부품번호) 사이)을 추가함: 그 행에 적힌 부품번호·칩 조건(스마트키·카드키·폴딩키 부품번호, [폴딩키]·[플립키], 비상키 '스마트키용' 등)을 근거로 막대키·폴딩키·스마트키·카드키를 모두 적음. 부품 자료가 없는 구형 연식은 기본 이모빌라이저키(막대키)만 적음</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="56" t="inlineStr">
+      <c r="A227" s="57" t="inlineStr">
         <is>
           <t>- CLAUDE.md 규칙(2000년식부터)에 맞춰 스포티지 NB 1993~1999, 카니발 1998~1999, 카렌스 RS 1999 행 삭제</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="56" t="inlineStr">
+      <c r="A228" s="57" t="inlineStr">
         <is>
           <t>- 카렌스 UN 2012: 헬로우카 원문 — 폴딩키 954301D103(2010.6.1~2012.7.17), 954301D104(2012.7.1~2012.7.17) 적용 기간 확인</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="56" t="inlineStr">
+      <c r="A229" s="57" t="inlineStr">
         <is>
           <t>- 셀토스 2026: SP2 PE(~2026.1) 행과 디 올 뉴 셀토스(SP3, 2026.1~) 행으로 나눔 — SP2 PE 스마트키 95440-Q5510·Q5710은 2022-2026 적용(bestkeysupply·royalkeysupply), SP3 키 자료 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="57" t="inlineStr">
+        <is>
+          <t>- 기아·현대 공란 행 보완: 같은 세대 순정 키 번호의 적용 기간이 그 연식을 포함하는 경우 옮겨 적음 — 프라이드 JB 2005(1G100 2005.2.15~)·2011(1G000), 프라이드 UB 2011·2012 폴딩키 95430-1W002(auto-keys.eu 한국 시장 OEM, Rio 2012), 쏘울 AM 2008(2008.9 출시, 2009년식과 같은 키), 모닝 SA 2004(2004.2 출시), 스포티지 NB 2000·2001(0K2AC-76201A), JE 2004(2F010 2004.6~)·2010, 쏘렌토 BL 2009, 카렌스 UN 2013(1D104·2L001)</t>
         </is>
       </c>
     </row>

--- a/기아_트랜스폰더_칩코드_DBnew.xlsx
+++ b/기아_트랜스폰더_칩코드_DBnew.xlsx
@@ -264,7 +264,7 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -430,6 +430,9 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -838,7 +841,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I2" s="19" t="n"/>
+      <c r="I2" s="19" t="inlineStr">
+        <is>
+          <t>81996-3C010[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J2" s="19" t="n"/>
       <c r="K2" s="19" t="n"/>
       <c r="L2" s="19" t="n"/>
@@ -888,7 +895,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I3" s="19" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>81996-3C010[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J3" s="24" t="inlineStr">
         <is>
           <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
@@ -942,7 +953,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I4" s="19" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>81996-3C010[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J4" s="24" t="inlineStr">
         <is>
           <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
@@ -996,7 +1011,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I5" s="19" t="n"/>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>81996-3C010[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J5" s="24" t="inlineStr">
         <is>
           <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
@@ -1050,7 +1069,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I6" s="19" t="n"/>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>81996-3C010[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
           <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
@@ -1104,7 +1127,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I7" s="19" t="n"/>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>81996-3C010[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J7" s="24" t="inlineStr">
         <is>
           <t>HY12[ILCO], HYN7R-HY7R-HY16[Lishi]</t>
@@ -21367,32 +21394,20 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="D319" s="43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E319" s="43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F319" s="43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G319" s="34" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[2001.6.11~]</t>
-        </is>
-      </c>
+      <c r="D319" s="53" t="n"/>
+      <c r="E319" s="53" t="n"/>
+      <c r="F319" s="54" t="n"/>
+      <c r="G319" s="34" t="n"/>
       <c r="H319" s="19" t="inlineStr">
         <is>
           <t>막대키</t>
         </is>
       </c>
-      <c r="I319" s="19" t="n"/>
+      <c r="I319" s="19" t="inlineStr">
+        <is>
+          <t>0K54A-76201A[2001.6.11~, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J319" s="19" t="n"/>
       <c r="K319" s="19" t="n"/>
       <c r="L319" s="19" t="n"/>
@@ -21446,7 +21461,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I320" s="19" t="n"/>
+      <c r="I320" s="19" t="inlineStr">
+        <is>
+          <t>0K54A-76201A[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J320" s="19" t="n"/>
       <c r="K320" s="19" t="n"/>
       <c r="L320" s="19" t="n"/>
@@ -21500,7 +21519,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I321" s="19" t="n"/>
+      <c r="I321" s="19" t="inlineStr">
+        <is>
+          <t>0K54A-76201A[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J321" s="19" t="n"/>
       <c r="K321" s="19" t="n"/>
       <c r="L321" s="19" t="n"/>
@@ -21554,7 +21577,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I322" s="19" t="n"/>
+      <c r="I322" s="19" t="inlineStr">
+        <is>
+          <t>0K54A-76201A[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J322" s="19" t="n"/>
       <c r="K322" s="19" t="n"/>
       <c r="L322" s="19" t="n"/>
@@ -21608,7 +21635,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I323" s="19" t="n"/>
+      <c r="I323" s="19" t="inlineStr">
+        <is>
+          <t>0K54A-76201A[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J323" s="19" t="n"/>
       <c r="K323" s="19" t="n"/>
       <c r="L323" s="19" t="n"/>
@@ -25258,7 +25289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A230"/>
+  <dimension ref="A1:A231"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="14.2"/>
   <cols>
     <col width="118" customWidth="1" style="15" min="1" max="1"/>
@@ -26843,6 +26874,13 @@
       <c r="A230" s="57" t="inlineStr">
         <is>
           <t>- 기아·현대 공란 행 보완: 같은 세대 순정 키 번호의 적용 기간이 그 연식을 포함하는 경우 옮겨 적음 — 프라이드 JB 2005(1G100 2005.2.15~)·2011(1G000), 프라이드 UB 2011·2012 폴딩키 95430-1W002(auto-keys.eu 한국 시장 OEM, Rio 2012), 쏘울 AM 2008(2008.9 출시, 2009년식과 같은 키), 모닝 SA 2004(2004.2 출시), 스포티지 NB 2000·2001(0K2AC-76201A), JE 2004(2F010 2004.6~)·2010, 쏘렌토 BL 2009, 카렌스 UN 2013(1D104·2L001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="58" t="inlineStr">
+        <is>
+          <t>- 기아·현대 구형 순정 키 번호(해외 판매처 OEM 표기): 옵티마 MS 81996-3C010(4D60 트랜스폰더 키, 2000~2005 옵티마, abkeys·eBay), 카니발 KV-II 0K54A-76201A(ID46 PCF7936, 2001.6.11~2005.11.1 카니발·세도나, car-keys-online), 싼타페 SM 81996-38000(칩 없는 키, 2000~2006 싼타페·EF 쏘나타, hyundaipartsdeal), 아반떼 J2·XD 81996-29000(칩 없는 키, 1995~2006 엘란트라, walmart·hyundaipartsdeal) — 국내 사양 동일 여부는 미확인이라 [해외 공용 품번]</t>
         </is>
       </c>
     </row>
